--- a/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
+++ b/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
@@ -385,10 +385,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9902257736789567</v>
+        <v>0.9876275990974327</v>
       </c>
       <c r="C2">
-        <v>0.9801220770429868</v>
+        <v>0.9776834449725377</v>
       </c>
     </row>
     <row r="3">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.949103105300569</v>
+        <v>0.9561955550655005</v>
       </c>
       <c r="C3">
-        <v>0.9317760497428326</v>
+        <v>0.9398230735780467</v>
       </c>
     </row>
     <row r="4">
@@ -411,10 +411,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9868538741007612</v>
+        <v>0.9819747412540549</v>
       </c>
       <c r="C4">
-        <v>0.9704129838262312</v>
+        <v>0.9710836203939552</v>
       </c>
     </row>
     <row r="5">
@@ -424,10 +424,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9075253153216476</v>
+        <v>0.9371381131003151</v>
       </c>
       <c r="C5">
-        <v>0.8641049848905786</v>
+        <v>0.8996423035631067</v>
       </c>
     </row>
   </sheetData>
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.1141841200311187</v>
+        <v>0.08875053735725993</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6136918224662806</v>
+        <v>0.6040822786626801</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2296955242940653</v>
+        <v>0.3464358487520589</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3728525915854844</v>
+        <v>0.3631448680976758</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -566,13 +566,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>286.67</v>
+        <v>246.71</v>
       </c>
       <c r="D2">
-        <v>2.861</v>
+        <v>24.821</v>
       </c>
       <c r="E2">
-        <v>0.03718338677083412</v>
+        <v>4.538938759809384E-14</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.02906998404757953</v>
+        <v>0.2318470108010325</v>
       </c>
     </row>
     <row r="3">
@@ -593,13 +593,13 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>286.67</v>
+        <v>246.71</v>
       </c>
       <c r="D3">
-        <v>41.653</v>
+        <v>56.497</v>
       </c>
       <c r="E3">
-        <v>2.264715506264829E-22</v>
+        <v>7.77740443234144E-28</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3035719057695158</v>
+        <v>0.4072335241866309</v>
       </c>
     </row>
     <row r="4">
@@ -620,13 +620,13 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>286.67</v>
+        <v>246.71</v>
       </c>
       <c r="D4">
-        <v>1.391666666666667</v>
+        <v>0.7653333333333308</v>
       </c>
       <c r="E4">
-        <v>0.1912849661821136</v>
+        <v>0.6486330488962151</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.04186233058707533</v>
+        <v>0.02716109748499585</v>
       </c>
     </row>
     <row r="5">
@@ -647,13 +647,13 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>448.78</v>
+        <v>438.1</v>
       </c>
       <c r="D5">
-        <v>0.295</v>
+        <v>0.279</v>
       </c>
       <c r="E5">
-        <v>0.5873519501402589</v>
+        <v>0.5978466292280042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.000656905862049769</v>
+        <v>0.0006364355956831874</v>
       </c>
     </row>
     <row r="6">
@@ -674,13 +674,13 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>448.78</v>
+        <v>438.1</v>
       </c>
       <c r="D6">
-        <v>10.652</v>
+        <v>8.965999999999999</v>
       </c>
       <c r="E6">
-        <v>8.902115119439742E-07</v>
+        <v>8.942340437776982E-06</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.06647307461891765</v>
+        <v>0.05784541008778531</v>
       </c>
     </row>
     <row r="7">
@@ -701,13 +701,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>448.78</v>
+        <v>438.1</v>
       </c>
       <c r="D7">
-        <v>1.241</v>
+        <v>1.075999999999999</v>
       </c>
       <c r="E7">
-        <v>0.2943173423607374</v>
+        <v>0.3589574785189045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.008227569761968426</v>
+        <v>0.007314287785955112</v>
       </c>
     </row>
     <row r="8">
@@ -728,13 +728,13 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>296.36</v>
+        <v>294.85</v>
       </c>
       <c r="D8">
-        <v>21.446</v>
+        <v>30.111</v>
       </c>
       <c r="E8">
-        <v>1.342445082263964E-12</v>
+        <v>5.207301104791132E-17</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>0.1783708254550899</v>
+        <v>0.2345196958328898</v>
       </c>
     </row>
     <row r="9">
@@ -755,13 +755,13 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>296.36</v>
+        <v>294.85</v>
       </c>
       <c r="D9">
-        <v>1.52</v>
+        <v>1.532</v>
       </c>
       <c r="E9">
-        <v>0.2094242760618644</v>
+        <v>0.2061636942631429</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0.01515352917718995</v>
+        <v>0.01534834327391249</v>
       </c>
     </row>
     <row r="10">
@@ -782,13 +782,13 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>296.36</v>
+        <v>294.85</v>
       </c>
       <c r="D10">
-        <v>0.594000000000002</v>
+        <v>0.9660000000000003</v>
       </c>
       <c r="E10">
-        <v>0.8018055152827974</v>
+        <v>0.4683301010697978</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0.01771923660782357</v>
+        <v>0.02864164668054714</v>
       </c>
     </row>
     <row r="11">
@@ -809,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>482.98</v>
+        <v>444.62</v>
       </c>
       <c r="D11">
-        <v>2.13</v>
+        <v>1.104</v>
       </c>
       <c r="E11">
-        <v>0.1451343698922352</v>
+        <v>0.2939030883765817</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G11">
-        <v>0.004390756735585743</v>
+        <v>0.002476869093878723</v>
       </c>
     </row>
     <row r="12">
@@ -836,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>482.98</v>
+        <v>444.62</v>
       </c>
       <c r="D12">
-        <v>0.492</v>
+        <v>0.391</v>
       </c>
       <c r="E12">
-        <v>0.6877641061675532</v>
+        <v>0.759790582653203</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.003046716316858497</v>
+        <v>0.002631266080894047</v>
       </c>
     </row>
     <row r="13">
@@ -863,13 +863,13 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>482.98</v>
+        <v>444.62</v>
       </c>
       <c r="D13">
-        <v>0.4579999999999999</v>
+        <v>0.7306666666666669</v>
       </c>
       <c r="E13">
-        <v>0.7117655613073258</v>
+        <v>0.5341044446352907</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>0.002836768148915875</v>
+        <v>0.00490586644942392</v>
       </c>
     </row>
   </sheetData>
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3733174382885419</v>
+        <v>0.3746115501114647</v>
       </c>
       <c r="C2">
-        <v>0.01672778414787567</v>
+        <v>0.01202892872714909</v>
       </c>
       <c r="D2">
-        <v>22.31720800486005</v>
+        <v>31.14255297447833</v>
       </c>
       <c r="E2">
-        <v>1.216703886373245E-64</v>
+        <v>1.885124292219418E-87</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.03305029683235654</v>
+        <v>-0.03259496550825047</v>
       </c>
       <c r="C3">
-        <v>0.02361652001904228</v>
+        <v>0.01694466197670757</v>
       </c>
       <c r="D3">
-        <v>-1.399456685646645</v>
+        <v>-1.923612613403329</v>
       </c>
       <c r="E3">
-        <v>0.1627572240467015</v>
+        <v>0.05555385108145913</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0001884907760189803</v>
+        <v>0.02865309563484529</v>
       </c>
       <c r="C4">
-        <v>0.02084845098010241</v>
+        <v>0.01694447704285277</v>
       </c>
       <c r="D4">
-        <v>0.00904099667638974</v>
+        <v>1.690999112122569</v>
       </c>
       <c r="E4">
-        <v>0.9927927150649345</v>
+        <v>0.09209981795566013</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,16 +1001,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.008224580956976629</v>
+        <v>0.05396216924362713</v>
       </c>
       <c r="C5">
-        <v>0.02110918297431259</v>
+        <v>0.017032484072364</v>
       </c>
       <c r="D5">
-        <v>-0.3896209989266275</v>
+        <v>3.168191381501613</v>
       </c>
       <c r="E5">
-        <v>0.6971061179076745</v>
+        <v>0.001727397558351033</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.00745391725528068</v>
+        <v>0.00875195132289148</v>
       </c>
       <c r="C6">
-        <v>0.024102201840134</v>
+        <v>0.0172872256055464</v>
       </c>
       <c r="D6">
-        <v>0.3092629173351591</v>
+        <v>0.5062669697608112</v>
       </c>
       <c r="E6">
-        <v>0.7573461958398517</v>
+        <v>0.6131213501081705</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1049,16 +1049,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.09001970303484656</v>
+        <v>0.09106532814321498</v>
       </c>
       <c r="C7">
-        <v>0.02369010147695408</v>
+        <v>0.01699270717975898</v>
       </c>
       <c r="D7">
-        <v>3.79988676377847</v>
+        <v>5.359082998363455</v>
       </c>
       <c r="E7">
-        <v>0.0001768047388020184</v>
+        <v>1.919040509305783E-07</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.09853543433052243</v>
+        <v>0.09932011624256573</v>
       </c>
       <c r="C8">
-        <v>0.02296055973030477</v>
+        <v>0.01647041649598936</v>
       </c>
       <c r="D8">
-        <v>4.291508372963106</v>
+        <v>6.030212791932173</v>
       </c>
       <c r="E8">
-        <v>2.429866653797499E-05</v>
+        <v>5.943780176063468E-09</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.03106402167666363</v>
+        <v>0.02968528712314809</v>
       </c>
       <c r="C9">
-        <v>0.03371573657517231</v>
+        <v>0.02409809291136045</v>
       </c>
       <c r="D9">
-        <v>0.9213508240403873</v>
+        <v>1.231852131715937</v>
       </c>
       <c r="E9">
-        <v>0.3576420141734726</v>
+        <v>0.2191771389835815</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.009114111132410507</v>
+        <v>-0.004244984307199449</v>
       </c>
       <c r="C10">
-        <v>0.0301581050118881</v>
+        <v>0.02409630344279757</v>
       </c>
       <c r="D10">
-        <v>0.302211001945175</v>
+        <v>-0.1761674489731031</v>
       </c>
       <c r="E10">
-        <v>0.7627103623624699</v>
+        <v>0.8603069124681181</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.0340685324730827</v>
+        <v>0.009551604133398983</v>
       </c>
       <c r="C11">
-        <v>0.03061346848056226</v>
+        <v>0.02443569664402871</v>
       </c>
       <c r="D11">
-        <v>1.11286091266379</v>
+        <v>0.3908873265429527</v>
       </c>
       <c r="E11">
-        <v>0.266700480104336</v>
+        <v>0.6962178617339863</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1169,16 +1169,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.005182290374650913</v>
+        <v>-0.006770827055322568</v>
       </c>
       <c r="C12">
-        <v>0.03342065076596747</v>
+        <v>0.02390107932414266</v>
       </c>
       <c r="D12">
-        <v>-0.1550625214015307</v>
+        <v>-0.2832854099807662</v>
       </c>
       <c r="E12">
-        <v>0.8768811500454246</v>
+        <v>0.7771956246245848</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.007533140990790993</v>
+        <v>-0.003815247961908407</v>
       </c>
       <c r="C13">
-        <v>0.02983301298115895</v>
+        <v>0.02390107932414263</v>
       </c>
       <c r="D13">
-        <v>0.252510230714831</v>
+        <v>-0.1596265971995081</v>
       </c>
       <c r="E13">
-        <v>0.8008276655211477</v>
+        <v>0.8733058334833712</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1217,16 +1217,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.01949053941095822</v>
+        <v>-0.01305105797433353</v>
       </c>
       <c r="C14">
-        <v>0.02974919700894022</v>
+        <v>0.02484215236827948</v>
       </c>
       <c r="D14">
-        <v>-0.6551618655488729</v>
+        <v>-0.5253593883836815</v>
       </c>
       <c r="E14">
-        <v>0.5128889208215966</v>
+        <v>0.5998052127208071</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.002357446139566218</v>
+        <v>0.0002843701202219904</v>
       </c>
       <c r="C15">
-        <v>0.03221599449795869</v>
+        <v>0.02302786082658081</v>
       </c>
       <c r="D15">
-        <v>0.07317626465684904</v>
+        <v>0.01234895947841343</v>
       </c>
       <c r="E15">
-        <v>0.9417168850276856</v>
+        <v>0.990157186423982</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.004698985339020197</v>
+        <v>-0.01553693963518103</v>
       </c>
       <c r="C16">
-        <v>0.02865427216462435</v>
+        <v>0.02301785088070507</v>
       </c>
       <c r="D16">
-        <v>-0.1639889965455628</v>
+        <v>-0.6749952337298792</v>
       </c>
       <c r="E16">
-        <v>0.8698553657082018</v>
+        <v>0.5003108839315853</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.0004080938359420498</v>
+        <v>-0.0208856282605672</v>
       </c>
       <c r="C17">
-        <v>0.02894410701214687</v>
+        <v>0.02324730460441314</v>
       </c>
       <c r="D17">
-        <v>0.01409937559209502</v>
+        <v>-0.8984107455021854</v>
       </c>
       <c r="E17">
-        <v>0.9887605059896738</v>
+        <v>0.3698425703627808</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.3526217876400518</v>
+        <v>0.3538569193536671</v>
       </c>
       <c r="C18">
-        <v>0.01581341886968587</v>
+        <v>0.01716628041972326</v>
       </c>
       <c r="D18">
-        <v>22.29889630736484</v>
+        <v>20.61348822818379</v>
       </c>
       <c r="E18">
-        <v>1.101777595229778E-74</v>
+        <v>1.720371654776551E-66</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.01020341429723992</v>
+        <v>-0.009274300213643458</v>
       </c>
       <c r="C19">
-        <v>0.02307573859342764</v>
+        <v>0.02507576492903485</v>
       </c>
       <c r="D19">
-        <v>-0.4421706484465909</v>
+        <v>-0.3698511387345511</v>
       </c>
       <c r="E19">
-        <v>0.6585787323705681</v>
+        <v>0.7116721305786542</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.006538580539181484</v>
+        <v>0.008249531252494256</v>
       </c>
       <c r="C20">
-        <v>0.02303629698967134</v>
+        <v>0.02499351367378204</v>
       </c>
       <c r="D20">
-        <v>0.2838381768612009</v>
+        <v>0.3300668869598729</v>
       </c>
       <c r="E20">
-        <v>0.7766652988139552</v>
+        <v>0.7415071949217368</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1385,16 +1385,16 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.09003928790601669</v>
+        <v>0.09067204198564903</v>
       </c>
       <c r="C21">
-        <v>0.02295124701275617</v>
+        <v>0.02490290385817264</v>
       </c>
       <c r="D21">
-        <v>3.923067354726887</v>
+        <v>3.641022850268615</v>
       </c>
       <c r="E21">
-        <v>0.0001011223086779246</v>
+        <v>0.0003040041253140457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1409,16 +1409,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.08736704544350198</v>
+        <v>0.08929481026316814</v>
       </c>
       <c r="C22">
-        <v>0.02169613122245069</v>
+        <v>0.02354863547270266</v>
       </c>
       <c r="D22">
-        <v>4.026849051922052</v>
+        <v>3.791931399451054</v>
       </c>
       <c r="E22">
-        <v>6.636564684362805E-05</v>
+        <v>0.0001704447019601174</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.03672606260660938</v>
+        <v>0.03758694299483386</v>
       </c>
       <c r="C23">
-        <v>0.03403248085052737</v>
+        <v>0.03700991685938299</v>
       </c>
       <c r="D23">
-        <v>1.079147381817752</v>
+        <v>1.01559112217526</v>
       </c>
       <c r="E23">
-        <v>0.281101682431363</v>
+        <v>0.3103846772735057</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.01801548238269538</v>
+        <v>-0.01834428592712405</v>
       </c>
       <c r="C24">
-        <v>0.03263489197200301</v>
+        <v>0.03543284379623297</v>
       </c>
       <c r="D24">
-        <v>-0.552031316608941</v>
+        <v>-0.5177198317080693</v>
       </c>
       <c r="E24">
-        <v>0.5812016909451062</v>
+        <v>0.6049150823541165</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.006681295514737766</v>
+        <v>0.00446583275848585</v>
       </c>
       <c r="C25">
-        <v>0.03138178321194472</v>
+        <v>0.03412319780466619</v>
       </c>
       <c r="D25">
-        <v>0.2129036285036438</v>
+        <v>0.1308738056746595</v>
       </c>
       <c r="E25">
-        <v>0.8314988078448524</v>
+        <v>0.8959352115249221</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4014029180526187</v>
+        <v>0.4025334175913302</v>
       </c>
       <c r="C26">
-        <v>0.01732116796714811</v>
+        <v>0.01606948668204964</v>
       </c>
       <c r="D26">
-        <v>23.17412537156459</v>
+        <v>25.04955046516692</v>
       </c>
       <c r="E26">
-        <v>1.669400120304854E-68</v>
+        <v>5.404889316551242E-75</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1529,16 +1529,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.03308664744916994</v>
+        <v>-0.03265216410960747</v>
       </c>
       <c r="C27">
-        <v>0.02445908882121666</v>
+        <v>0.02271606794669441</v>
       </c>
       <c r="D27">
-        <v>-1.352734261321683</v>
+        <v>-1.437403875804084</v>
       </c>
       <c r="E27">
-        <v>0.1771716801975891</v>
+        <v>0.151663656230837</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.08787055225341493</v>
+        <v>-0.1365239363174825</v>
       </c>
       <c r="C28">
-        <v>0.02120127083064853</v>
+        <v>0.02271607859286344</v>
       </c>
       <c r="D28">
-        <v>-4.144588923716278</v>
+        <v>-6.010013381463355</v>
       </c>
       <c r="E28">
-        <v>4.447390035019747E-05</v>
+        <v>5.46556321687286E-09</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1577,16 +1577,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.1044554849685298</v>
+        <v>-0.1113495524579403</v>
       </c>
       <c r="C29">
-        <v>0.02120077327510472</v>
+        <v>0.02271607958371251</v>
       </c>
       <c r="D29">
-        <v>-4.926965805119384</v>
+        <v>-4.901794433656513</v>
       </c>
       <c r="E29">
-        <v>1.391136307424207E-06</v>
+        <v>1.570389635875689E-06</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.03181367421806436</v>
+        <v>-0.03252481271835564</v>
       </c>
       <c r="C30">
-        <v>0.02443316272122617</v>
+        <v>0.02271567993677114</v>
       </c>
       <c r="D30">
-        <v>-1.302069428384988</v>
+        <v>-1.431822107411626</v>
       </c>
       <c r="E30">
-        <v>0.193903730240785</v>
+        <v>0.1532539320318048</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.0224742014002372</v>
+        <v>-0.02264935345465341</v>
       </c>
       <c r="C31">
-        <v>0.02443314191293058</v>
+        <v>0.02271528464549201</v>
       </c>
       <c r="D31">
-        <v>-0.9198244532089155</v>
+        <v>-0.9970974966033858</v>
       </c>
       <c r="E31">
-        <v>0.3584125840481226</v>
+        <v>0.3195347799717553</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1649,16 +1649,16 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.01917714101707324</v>
+        <v>-0.01908099495665671</v>
       </c>
       <c r="C32">
-        <v>0.02591124929802536</v>
+        <v>0.02409203534726483</v>
       </c>
       <c r="D32">
-        <v>-0.7401086993723107</v>
+        <v>-0.7920042736788934</v>
       </c>
       <c r="E32">
-        <v>0.4598199451026016</v>
+        <v>0.4289949142432127</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1673,16 +1673,16 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.01388195067581552</v>
+        <v>-0.01359158087174355</v>
       </c>
       <c r="C33">
-        <v>0.03448569297605517</v>
+        <v>0.03210693804519506</v>
       </c>
       <c r="D33">
-        <v>-0.4025423147348186</v>
+        <v>-0.4233222380973072</v>
       </c>
       <c r="E33">
-        <v>0.6875751543190599</v>
+        <v>0.6723687869115376</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1697,16 +1697,16 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.04463223562940072</v>
+        <v>0.04963272118711809</v>
       </c>
       <c r="C34">
-        <v>0.02989213454696401</v>
+        <v>0.03210693804519512</v>
       </c>
       <c r="D34">
-        <v>1.493109686070705</v>
+        <v>1.545856572098308</v>
       </c>
       <c r="E34">
-        <v>0.1364723077062988</v>
+        <v>0.123211835067649</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1721,16 +1721,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.02696487750343171</v>
+        <v>0.0370202303737124</v>
       </c>
       <c r="C35">
-        <v>0.02989392441168252</v>
+        <v>0.03210693804519519</v>
       </c>
       <c r="D35">
-        <v>0.9020186554326692</v>
+        <v>1.153028990855529</v>
       </c>
       <c r="E35">
-        <v>0.3677794609613206</v>
+        <v>0.2498323794485739</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1745,16 +1745,16 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.01610297892317729</v>
+        <v>0.01730608763000769</v>
       </c>
       <c r="C36">
-        <v>0.03448569297605526</v>
+        <v>0.03210693804519512</v>
       </c>
       <c r="D36">
-        <v>0.4669466533370291</v>
+        <v>0.5390139541069562</v>
       </c>
       <c r="E36">
-        <v>0.6408811480502332</v>
+        <v>0.5902839783788811</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1769,16 +1769,16 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.04095116000273899</v>
+        <v>0.06863955963113214</v>
       </c>
       <c r="C37">
-        <v>0.02989213451241367</v>
+        <v>0.03210693804519516</v>
       </c>
       <c r="D37">
-        <v>1.369964396009683</v>
+        <v>2.137841968440342</v>
       </c>
       <c r="E37">
-        <v>0.1717350039954487</v>
+        <v>0.03335171519025802</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.04094890561918282</v>
+        <v>0.04411948831219967</v>
       </c>
       <c r="C38">
-        <v>0.02989213451241367</v>
+        <v>0.03210693804519516</v>
       </c>
       <c r="D38">
-        <v>1.369888978727078</v>
+        <v>1.37414188329311</v>
       </c>
       <c r="E38">
-        <v>0.1717585240694865</v>
+        <v>0.170441293748321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1817,16 +1817,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.006570875654234966</v>
+        <v>-0.006842182676745263</v>
       </c>
       <c r="C39">
-        <v>0.03554703867822413</v>
+        <v>0.03309507421887541</v>
       </c>
       <c r="D39">
-        <v>-0.1848501562595773</v>
+        <v>-0.2067432340986533</v>
       </c>
       <c r="E39">
-        <v>0.8534730012651827</v>
+        <v>0.8363530902685575</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.03301503599653655</v>
+        <v>0.05093033343885515</v>
       </c>
       <c r="C40">
-        <v>0.03137478721148914</v>
+        <v>0.03309507421887545</v>
       </c>
       <c r="D40">
-        <v>1.052279200301533</v>
+        <v>1.538909781619632</v>
       </c>
       <c r="E40">
-        <v>0.2935286961682939</v>
+        <v>0.1248987902624453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.01830482238709707</v>
+        <v>0.01795441459435246</v>
       </c>
       <c r="C41">
-        <v>0.03111059017368059</v>
+        <v>0.03309507421887544</v>
       </c>
       <c r="D41">
-        <v>0.5883791430798013</v>
+        <v>0.542510177666027</v>
       </c>
       <c r="E41">
-        <v>0.5567259644725229</v>
+        <v>0.5878769118611451</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.3057249274584424</v>
+        <v>0.3045048078918793</v>
       </c>
       <c r="C42">
-        <v>0.01390854107062247</v>
+        <v>0.01341566766122981</v>
       </c>
       <c r="D42">
-        <v>21.98109247447906</v>
+        <v>22.69770059762836</v>
       </c>
       <c r="E42">
-        <v>9.846370941902916E-75</v>
+        <v>2.613263520748264E-76</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1913,16 +1913,16 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.00668338927068995</v>
+        <v>-0.002824757953022443</v>
       </c>
       <c r="C43">
-        <v>0.0196238010898003</v>
+        <v>0.01873045540568325</v>
       </c>
       <c r="D43">
-        <v>-0.3405756733930471</v>
+        <v>-0.1508109595757798</v>
       </c>
       <c r="E43">
-        <v>0.7335711327559991</v>
+        <v>0.8801932360076512</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1937,16 +1937,16 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.01632071643036116</v>
+        <v>0.01261976385629086</v>
       </c>
       <c r="C44">
-        <v>0.01973226042106301</v>
+        <v>0.01891061019151644</v>
       </c>
       <c r="D44">
-        <v>0.8271083029565011</v>
+        <v>0.6673377394216641</v>
       </c>
       <c r="E44">
-        <v>0.4085841290075516</v>
+        <v>0.5049026214177382</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.01946291107848508</v>
+        <v>0.0233210791319629</v>
       </c>
       <c r="C45">
-        <v>0.01956521329969248</v>
+        <v>0.01870931741531259</v>
       </c>
       <c r="D45">
-        <v>0.9947712187114769</v>
+        <v>1.246495455407466</v>
       </c>
       <c r="E45">
-        <v>0.3203456623825511</v>
+        <v>0.2132388600594329</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.03116952268476683</v>
+        <v>0.03336629664688411</v>
       </c>
       <c r="C46">
-        <v>0.02008994738255991</v>
+        <v>0.01916096179047589</v>
       </c>
       <c r="D46">
-        <v>1.55149847290417</v>
+        <v>1.741368570729529</v>
       </c>
       <c r="E46">
-        <v>0.121437269397546</v>
+        <v>0.08231063464544221</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2009,16 +2009,16 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.02590774810318127</v>
+        <v>-0.02326442542763208</v>
       </c>
       <c r="C47">
-        <v>0.02785092804215786</v>
+        <v>0.02659478606201258</v>
       </c>
       <c r="D47">
-        <v>-0.9302292571351587</v>
+        <v>-0.8747739264901433</v>
       </c>
       <c r="E47">
-        <v>0.3527171064889982</v>
+        <v>0.3821692054271787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2033,16 +2033,16 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.01963764196164974</v>
+        <v>-0.02785400861089544</v>
       </c>
       <c r="C48">
-        <v>0.02761972140432581</v>
+        <v>0.02613246361857858</v>
       </c>
       <c r="D48">
-        <v>-0.7110007256834272</v>
+        <v>-1.065877638535884</v>
       </c>
       <c r="E48">
-        <v>0.4774270005597576</v>
+        <v>0.2870574063104031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2057,16 +2057,16 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.03125856818479932</v>
+        <v>-0.03726699359108907</v>
       </c>
       <c r="C49">
-        <v>0.02799642374621488</v>
+        <v>0.02644135638636404</v>
       </c>
       <c r="D49">
-        <v>-1.116520040850771</v>
+        <v>-1.4094206456938</v>
       </c>
       <c r="E49">
-        <v>0.2647547478381362</v>
+        <v>0.1594098595356221</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2123,16 +2123,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.354615122516546</v>
+        <v>4.437030204643323</v>
       </c>
       <c r="C2">
-        <v>4.584251205942191</v>
+        <v>4.734675796301638</v>
       </c>
       <c r="D2">
-        <v>4.875825270443859</v>
+        <v>7.185198633704571</v>
       </c>
       <c r="E2">
-        <v>0.01272484850788075</v>
+        <v>4.745651165205533E-06</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2147,16 +2147,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>3.690850630559153</v>
+        <v>1.383317805994409</v>
       </c>
       <c r="C3">
-        <v>4.202693672129124</v>
+        <v>1.883860479044593</v>
       </c>
       <c r="D3">
-        <v>2.966202180783019</v>
+        <v>1.675983508005414</v>
       </c>
       <c r="E3">
-        <v>0.01579306309571499</v>
+        <v>0.2569959056491588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3.501540825662337</v>
+        <v>4.66893761214026</v>
       </c>
       <c r="C4">
-        <v>3.800127361539922</v>
+        <v>4.912254758367309</v>
       </c>
       <c r="D4">
-        <v>6.278947051324566</v>
+        <v>12.84601443815747</v>
       </c>
       <c r="E4">
-        <v>6.977965415688736E-05</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>2.41691796277352</v>
+        <v>3.74831003098071</v>
       </c>
       <c r="C5">
-        <v>2.770588227697275</v>
+        <v>4.321171578611158</v>
       </c>
       <c r="D5">
-        <v>1.4867112422468</v>
+        <v>3.981930128570848</v>
       </c>
       <c r="E5">
-        <v>0.2495363673722185</v>
+        <v>0.003093393799922461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>2.423919769957195</v>
+        <v>1.000017813863155</v>
       </c>
       <c r="C6">
-        <v>2.802126976961236</v>
+        <v>1.000024793283778</v>
       </c>
       <c r="D6">
-        <v>1.266111047076639</v>
+        <v>0.09870333815635508</v>
       </c>
       <c r="E6">
-        <v>0.2745139073378196</v>
+        <v>0.753675745184935</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2243,16 +2243,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>4.521025149061477</v>
+        <v>4.494712550142255</v>
       </c>
       <c r="C7">
-        <v>4.865551624879938</v>
+        <v>4.858450913432605</v>
       </c>
       <c r="D7">
-        <v>5.799899829755343</v>
+        <v>7.123248672119646</v>
       </c>
       <c r="E7">
-        <v>0.0001627853133629453</v>
+        <v>3.039977636160041E-05</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2267,16 +2267,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.000012521668403</v>
+        <v>2.091194432423091E-06</v>
       </c>
       <c r="C8">
-        <v>1.000019398455533</v>
+        <v>3.530366438491225E-06</v>
       </c>
       <c r="D8">
-        <v>0.3874952314499748</v>
+        <v>0.04154527433430071</v>
       </c>
       <c r="E8">
-        <v>0.5341127007138441</v>
+        <v>0.9996948222912792</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2291,16 +2291,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.426107680454836E-05</v>
+        <v>1.000002537800571</v>
       </c>
       <c r="C9">
-        <v>2.209713067271263E-05</v>
+        <v>1.00000427903631</v>
       </c>
       <c r="D9">
-        <v>0.07424533392102496</v>
+        <v>0.9795963794452118</v>
       </c>
       <c r="E9">
-        <v>0.9989787875877707</v>
+        <v>0.3232672040953517</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.136079457030718</v>
+        <v>2.744605638666821</v>
       </c>
       <c r="C10">
-        <v>1.207670406887922</v>
+        <v>3.329181669008129</v>
       </c>
       <c r="D10">
-        <v>0.1275898570964134</v>
+        <v>2.167567852931014</v>
       </c>
       <c r="E10">
-        <v>0.7458999879266579</v>
+        <v>0.06984114683989839</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>258.286545027931</v>
+        <v>159.8130139390948</v>
       </c>
       <c r="C11">
-        <v>562</v>
+        <v>423</v>
       </c>
       <c r="D11">
-        <v>24.05753909390203</v>
+        <v>13.3871614373032</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -2363,16 +2363,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>2.879303719277803</v>
+        <v>1.000010018739211</v>
       </c>
       <c r="C12">
-        <v>3.47794024027291</v>
+        <v>1.000013313002918</v>
       </c>
       <c r="D12">
-        <v>0.2922067746472708</v>
+        <v>1.03822309312251</v>
       </c>
       <c r="E12">
-        <v>0.8250300188080166</v>
+        <v>0.3087960522252479</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2387,16 +2387,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>4.132944264307588</v>
+        <v>6.17247707600399</v>
       </c>
       <c r="C13">
-        <v>5.537265197294545</v>
+        <v>8.033446755036849</v>
       </c>
       <c r="D13">
-        <v>1.069739568923843</v>
+        <v>1.905903792467365</v>
       </c>
       <c r="E13">
-        <v>0.416046682318188</v>
+        <v>0.05899412557532457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>5.546540990721378</v>
+        <v>5.057883339980297</v>
       </c>
       <c r="C14">
-        <v>6.985553481941484</v>
+        <v>6.498213907275719</v>
       </c>
       <c r="D14">
-        <v>1.978743518517542</v>
+        <v>2.640741763399863</v>
       </c>
       <c r="E14">
-        <v>0.05755808209086527</v>
+        <v>0.01357300910934417</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2435,16 +2435,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>4.224810992483967E-06</v>
+        <v>2.541523562966276E-05</v>
       </c>
       <c r="C15">
-        <v>7.082294880383643E-06</v>
+        <v>4.092772519029586E-05</v>
       </c>
       <c r="D15">
-        <v>0.02617066862849693</v>
+        <v>0.001012851128021072</v>
       </c>
       <c r="E15">
-        <v>0.9996563190246266</v>
+        <v>0.9998377388314241</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.095391249727681</v>
+        <v>1.465684238340331</v>
       </c>
       <c r="C16">
-        <v>1.159422603881333</v>
+        <v>1.726904387451023</v>
       </c>
       <c r="D16">
-        <v>1.262105103917559</v>
+        <v>0.9554520531353746</v>
       </c>
       <c r="E16">
-        <v>0.2858411351868905</v>
+        <v>0.4563646271588468</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,16 +2483,16 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.000023778204578</v>
+        <v>1.000003636133822</v>
       </c>
       <c r="C17">
-        <v>1.000039593177257</v>
+        <v>1.00000582212547</v>
       </c>
       <c r="D17">
-        <v>0.4310770726272458</v>
+        <v>0.5107499612917278</v>
       </c>
       <c r="E17">
-        <v>0.5117996027197642</v>
+        <v>0.4751960658978684</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="B18">
-        <v>2.691851179419301</v>
+        <v>2.507994383146582</v>
       </c>
       <c r="C18">
-        <v>3.476403032630226</v>
+        <v>3.198456842273021</v>
       </c>
       <c r="D18">
-        <v>1.053211519951963</v>
+        <v>0.8572573655423694</v>
       </c>
       <c r="E18">
-        <v>0.3667354573823987</v>
+        <v>0.4500940823286531</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2531,13 +2531,13 @@
         </is>
       </c>
       <c r="B19">
-        <v>128.8774244747259</v>
+        <v>139.7000251804372</v>
       </c>
       <c r="C19">
         <v>591</v>
       </c>
       <c r="D19">
-        <v>1.70059404306452</v>
+        <v>2.17979950488841</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2555,16 +2555,16 @@
         </is>
       </c>
       <c r="B20">
-        <v>4.404003896919796</v>
+        <v>2.801155527955589</v>
       </c>
       <c r="C20">
-        <v>4.649618613073286</v>
+        <v>3.359656955432805</v>
       </c>
       <c r="D20">
-        <v>3.201505634082438</v>
+        <v>1.009623415313417</v>
       </c>
       <c r="E20">
-        <v>0.03275679475865206</v>
+        <v>0.3682502306583644</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2579,16 +2579,16 @@
         </is>
       </c>
       <c r="B21">
-        <v>4.645760358522913E-06</v>
+        <v>1.000009400452073</v>
       </c>
       <c r="C21">
-        <v>6.299605935685905E-06</v>
+        <v>1.000013417737377</v>
       </c>
       <c r="D21">
-        <v>0.02602124736073329</v>
+        <v>0.5082736481865406</v>
       </c>
       <c r="E21">
-        <v>0.9996768195211783</v>
+        <v>0.4764510077760598</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2603,16 +2603,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>3.529240544740285</v>
+        <v>3.138566960297332</v>
       </c>
       <c r="C22">
-        <v>4.068272610301211</v>
+        <v>3.650660183077969</v>
       </c>
       <c r="D22">
-        <v>1.688652723149084</v>
+        <v>3.560646960295764</v>
       </c>
       <c r="E22">
-        <v>0.1387815457576441</v>
+        <v>0.01248430383484589</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2627,16 +2627,16 @@
         </is>
       </c>
       <c r="B23">
-        <v>3.370661345376324</v>
+        <v>4.228792691358922</v>
       </c>
       <c r="C23">
-        <v>3.886119458835592</v>
+        <v>4.707355640127314</v>
       </c>
       <c r="D23">
-        <v>2.027673782826949</v>
+        <v>9.818578276410586</v>
       </c>
       <c r="E23">
-        <v>0.1727822429713072</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2651,16 +2651,16 @@
         </is>
       </c>
       <c r="B24">
-        <v>3.074996722828799</v>
+        <v>4.237436626924838</v>
       </c>
       <c r="C24">
-        <v>3.5817582750347</v>
+        <v>4.712572073147745</v>
       </c>
       <c r="D24">
-        <v>0.4866452508942342</v>
+        <v>4.957369093862262</v>
       </c>
       <c r="E24">
-        <v>0.7509750508660828</v>
+        <v>0.001348826517476476</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.000025649536276</v>
+        <v>3.491454931381493</v>
       </c>
       <c r="C25">
-        <v>1.000037293220358</v>
+        <v>4.177390719146416</v>
       </c>
       <c r="D25">
-        <v>0.7157944497671779</v>
+        <v>0.9523680971936778</v>
       </c>
       <c r="E25">
-        <v>0.3982225328969898</v>
+        <v>0.5699965911038032</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2699,16 +2699,16 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.000005127736046</v>
+        <v>1.118966158648497</v>
       </c>
       <c r="C26">
-        <v>1.000007458305846</v>
+        <v>1.644244645221571</v>
       </c>
       <c r="D26">
-        <v>0.1274026191904339</v>
+        <v>1.561059248090922</v>
       </c>
       <c r="E26">
-        <v>0.7213997993763057</v>
+        <v>0.3182973976288117</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2723,16 +2723,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.000005767870769</v>
+        <v>1.000002909285121</v>
       </c>
       <c r="C27">
-        <v>1.000008386222679</v>
+        <v>1.000005268846509</v>
       </c>
       <c r="D27">
-        <v>0.2509032293085269</v>
+        <v>0.4082990159855311</v>
       </c>
       <c r="E27">
-        <v>0.6168148019316293</v>
+        <v>0.5233303666739768</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2747,16 +2747,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.057499185835486E-05</v>
+        <v>1.000007301703944</v>
       </c>
       <c r="C28">
-        <v>1.537638345555474E-05</v>
+        <v>1.000013299010062</v>
       </c>
       <c r="D28">
-        <v>3.048454885404507E-05</v>
+        <v>0.02757492996965299</v>
       </c>
       <c r="E28">
-        <v>0.5</v>
+        <v>0.8682441408019377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="B29">
-        <v>338.2625059084224</v>
+        <v>141.1383541031473</v>
       </c>
       <c r="C29">
-        <v>645</v>
+        <v>451</v>
       </c>
       <c r="D29">
-        <v>12.78958369995512</v>
+        <v>7.648838244423077</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2795,16 +2795,16 @@
         </is>
       </c>
       <c r="B30">
-        <v>8.633680561559787</v>
+        <v>4.008344643684963</v>
       </c>
       <c r="C30">
-        <v>10.0323392951178</v>
+        <v>4.959087085963268</v>
       </c>
       <c r="D30">
-        <v>3.105930732385316</v>
+        <v>0.8160421247309599</v>
       </c>
       <c r="E30">
-        <v>0.0005479431039085991</v>
+        <v>0.5579805333359519</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2819,16 +2819,16 @@
         </is>
       </c>
       <c r="B31">
-        <v>3.358420725772095</v>
+        <v>7.340995727173136</v>
       </c>
       <c r="C31">
-        <v>4.486164877043023</v>
+        <v>8.767997094983052</v>
       </c>
       <c r="D31">
-        <v>2.187703763439625</v>
+        <v>1.445138756754841</v>
       </c>
       <c r="E31">
-        <v>0.05239930454778974</v>
+        <v>0.1301935756368453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2843,16 +2843,16 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.000032484856546</v>
+        <v>3.05776479679749E-05</v>
       </c>
       <c r="C32">
-        <v>1.000043660367288</v>
+        <v>4.124539769993795E-05</v>
       </c>
       <c r="D32">
-        <v>0.9637430417827135</v>
+        <v>0.0001460227699824172</v>
       </c>
       <c r="E32">
-        <v>0.3267443815613286</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.149923195326338</v>
+        <v>7.341516289106171</v>
       </c>
       <c r="C33">
-        <v>1.637256381711699</v>
+        <v>8.310088074927609</v>
       </c>
       <c r="D33">
-        <v>0.6780683858525717</v>
+        <v>5.350701649478624</v>
       </c>
       <c r="E33">
-        <v>0.543922370787646</v>
+        <v>1.800113473560128E-06</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="B34">
-        <v>2.030830197758534</v>
+        <v>9.283553362168588E-06</v>
       </c>
       <c r="C34">
-        <v>2.469380000901918</v>
+        <v>1.332884555695676E-05</v>
       </c>
       <c r="D34">
-        <v>0.3677141681706575</v>
+        <v>0.001029759075854352</v>
       </c>
       <c r="E34">
-        <v>0.7557166009364098</v>
+        <v>0.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.000004883745373</v>
+        <v>1.000013681494936</v>
       </c>
       <c r="C35">
-        <v>1.000007067141596</v>
+        <v>1.000019430587598</v>
       </c>
       <c r="D35">
-        <v>0.5695067670990851</v>
+        <v>1.122348758797891</v>
       </c>
       <c r="E35">
-        <v>0.4508234143627841</v>
+        <v>0.2899843016523977</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2939,16 +2939,16 @@
         </is>
       </c>
       <c r="B36">
-        <v>3.231002650007113</v>
+        <v>8.117390570266311</v>
       </c>
       <c r="C36">
-        <v>4.072402292994868</v>
+        <v>9.635773918248049</v>
       </c>
       <c r="D36">
-        <v>0.9131335113760902</v>
+        <v>3.062906944067775</v>
       </c>
       <c r="E36">
-        <v>0.4618770161337808</v>
+        <v>0.001279714407574351</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="B37">
-        <v>199.6192635962483</v>
+        <v>230.5705193045784</v>
       </c>
       <c r="C37">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D37">
-        <v>2.196998984869905</v>
+        <v>2.917038288214228</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3032,13 +3032,13 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>4.354615122516546</v>
+        <v>4.437030204643323</v>
       </c>
       <c r="D2">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E2">
-        <v>0.6725</v>
+        <v>0.9125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3056,13 +3056,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>3.690850630559153</v>
+        <v>1.383317805994409</v>
       </c>
       <c r="D3">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E3">
-        <v>0.6575</v>
+        <v>0.905</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3080,13 +3080,13 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>3.501540825662337</v>
+        <v>4.66893761214026</v>
       </c>
       <c r="D4">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E4">
-        <v>0.6975</v>
+        <v>0.91</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3104,13 +3104,13 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>2.41691796277352</v>
+        <v>3.74831003098071</v>
       </c>
       <c r="D5">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E5">
-        <v>0.665</v>
+        <v>0.8825</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3128,13 +3128,13 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>2.423919769957195</v>
+        <v>1.000017813863155</v>
       </c>
       <c r="D6">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E6">
-        <v>0.645</v>
+        <v>0.8975</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3152,13 +3152,13 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>4.521025149061477</v>
+        <v>4.494712550142255</v>
       </c>
       <c r="D7">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E7">
-        <v>0.675</v>
+        <v>0.91</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3176,13 +3176,13 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>1.000012521668403</v>
+        <v>2.091194432423091E-06</v>
       </c>
       <c r="D8">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E8">
-        <v>0.655</v>
+        <v>0.905</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>1.426107680454836E-05</v>
+        <v>1.000002537800571</v>
       </c>
       <c r="D9">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E9">
-        <v>0.6875</v>
+        <v>0.9075</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3224,13 +3224,13 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>1.136079457030718</v>
+        <v>2.744605638666821</v>
       </c>
       <c r="D10">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E10">
-        <v>0.6625</v>
+        <v>0.895</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3245,16 +3245,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>684</v>
+        <v>504</v>
       </c>
       <c r="C11">
-        <v>258.286545027931</v>
+        <v>159.8130139390948</v>
       </c>
       <c r="D11">
-        <v>1.019220234573694</v>
+        <v>1.064707443497011</v>
       </c>
       <c r="E11">
-        <v>0.6725</v>
+        <v>0.875</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3272,13 +3272,13 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <v>2.879303719277803</v>
+        <v>1.000010018739211</v>
       </c>
       <c r="D12">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E12">
-        <v>0.995</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3296,13 +3296,13 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>4.132944264307588</v>
+        <v>6.17247707600399</v>
       </c>
       <c r="D13">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.955</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3320,13 +3320,13 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>5.546540990721378</v>
+        <v>5.057883339980297</v>
       </c>
       <c r="D14">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E14">
-        <v>0.9975000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3344,13 +3344,13 @@
         <v>13</v>
       </c>
       <c r="C15">
-        <v>4.224810992483967E-06</v>
+        <v>2.541523562966276E-05</v>
       </c>
       <c r="D15">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3368,13 +3368,13 @@
         <v>13</v>
       </c>
       <c r="C16">
-        <v>1.095391249727681</v>
+        <v>1.465684238340331</v>
       </c>
       <c r="D16">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E16">
-        <v>0.9975000000000001</v>
+        <v>0.9525</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         <v>13</v>
       </c>
       <c r="C17">
-        <v>1.000023778204578</v>
+        <v>1.000003636133822</v>
       </c>
       <c r="D17">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.9475</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3416,13 +3416,13 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>2.691851179419301</v>
+        <v>2.507994383146582</v>
       </c>
       <c r="D18">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3440,13 +3440,13 @@
         <v>1008</v>
       </c>
       <c r="C19">
-        <v>128.8774244747259</v>
+        <v>139.7000251804372</v>
       </c>
       <c r="D19">
-        <v>1.127813859477557</v>
+        <v>1.065287460024849</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0.9425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3464,13 +3464,13 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>4.404003896919796</v>
+        <v>2.801155527955589</v>
       </c>
       <c r="D20">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.2425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3488,13 +3488,13 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>4.645760358522913E-06</v>
+        <v>1.000009400452073</v>
       </c>
       <c r="D21">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>3.529240544740285</v>
+        <v>3.138566960297332</v>
       </c>
       <c r="D22">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3536,13 +3536,13 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>3.370661345376324</v>
+        <v>4.228792691358922</v>
       </c>
       <c r="D23">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0.27</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3560,13 +3560,13 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>3.074996722828799</v>
+        <v>4.237436626924838</v>
       </c>
       <c r="D24">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0.22</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3584,13 +3584,13 @@
         <v>5</v>
       </c>
       <c r="C25">
-        <v>1.000025649536276</v>
+        <v>3.491454931381493</v>
       </c>
       <c r="D25">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0.235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3608,13 +3608,13 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>1.000005127736046</v>
+        <v>1.118966158648497</v>
       </c>
       <c r="D26">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.2375</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3632,13 +3632,13 @@
         <v>5</v>
       </c>
       <c r="C27">
-        <v>1.000005767870769</v>
+        <v>1.000002909285121</v>
       </c>
       <c r="D27">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0.2425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3656,13 +3656,13 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>1.057499185835486E-05</v>
+        <v>1.000007301703944</v>
       </c>
       <c r="D28">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3677,16 +3677,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>708</v>
+        <v>474</v>
       </c>
       <c r="C29">
-        <v>338.2625059084224</v>
+        <v>141.1383541031473</v>
       </c>
       <c r="D29">
-        <v>1.245990328778347</v>
+        <v>0.9681828890394807</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0.185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3704,13 +3704,13 @@
         <v>12</v>
       </c>
       <c r="C30">
-        <v>8.633680561559787</v>
+        <v>4.008344643684963</v>
       </c>
       <c r="D30">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0.9875</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,13 +3728,13 @@
         <v>12</v>
       </c>
       <c r="C31">
-        <v>3.358420725772095</v>
+        <v>7.340995727173136</v>
       </c>
       <c r="D31">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3752,13 +3752,13 @@
         <v>12</v>
       </c>
       <c r="C32">
-        <v>1.000032484856546</v>
+        <v>3.05776479679749E-05</v>
       </c>
       <c r="D32">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3776,13 +3776,13 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>1.149923195326338</v>
+        <v>7.341516289106171</v>
       </c>
       <c r="D33">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3800,13 +3800,13 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>2.030830197758534</v>
+        <v>9.283553362168588E-06</v>
       </c>
       <c r="D34">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0.9725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3824,13 +3824,13 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>1.000004883745373</v>
+        <v>1.000013681494936</v>
       </c>
       <c r="D35">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3848,13 +3848,13 @@
         <v>12</v>
       </c>
       <c r="C36">
-        <v>3.231002650007113</v>
+        <v>8.117390570266311</v>
       </c>
       <c r="D36">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0.9875</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         <v>1027</v>
       </c>
       <c r="C37">
-        <v>199.6192635962483</v>
+        <v>230.5705193045784</v>
       </c>
       <c r="D37">
-        <v>1.193268229371967</v>
+        <v>1.08353750439666</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3950,19 +3950,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.3729804676978841</v>
+        <v>0.3732175812683861</v>
       </c>
       <c r="D2">
-        <v>0.01673913177257566</v>
+        <v>0.01215248352209591</v>
       </c>
       <c r="E2">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F2">
-        <v>0.3400332740067554</v>
+        <v>0.3492817319084278</v>
       </c>
       <c r="G2">
-        <v>0.4059276613890127</v>
+        <v>0.3971534306283444</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3982,19 +3982,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.3395328635842514</v>
+        <v>0.3403617661162668</v>
       </c>
       <c r="D3">
-        <v>0.01667944346840272</v>
+        <v>0.01210862279336495</v>
       </c>
       <c r="E3">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F3">
-        <v>0.3067031528154989</v>
+        <v>0.3165123059946739</v>
       </c>
       <c r="G3">
-        <v>0.372362574353004</v>
+        <v>0.3642112262378597</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.3725573233683732</v>
+        <v>0.4013417754722128</v>
       </c>
       <c r="D4">
-        <v>0.01245518111310756</v>
+        <v>0.01210834547179447</v>
       </c>
       <c r="E4">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F4">
-        <v>0.3480421173130654</v>
+        <v>0.3774928615704377</v>
       </c>
       <c r="G4">
-        <v>0.397072529423681</v>
+        <v>0.4251906893739879</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4046,19 +4046,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.3646763946774987</v>
+        <v>0.4264155762422724</v>
       </c>
       <c r="D5">
-        <v>0.01291169051443237</v>
+        <v>0.01226206148492999</v>
       </c>
       <c r="E5">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F5">
-        <v>0.3392626531502431</v>
+        <v>0.4022638992610054</v>
       </c>
       <c r="G5">
-        <v>0.3900901362047544</v>
+        <v>0.4505672532235395</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4078,19 +4078,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3803792121428735</v>
+        <v>0.3806387685532792</v>
       </c>
       <c r="D6">
-        <v>0.01739404988907161</v>
+        <v>0.01266983462286476</v>
       </c>
       <c r="E6">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F6">
-        <v>0.3461429603136536</v>
+        <v>0.3556839309353491</v>
       </c>
       <c r="G6">
-        <v>0.4146154639720934</v>
+        <v>0.4055936061712093</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4110,19 +4110,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.3779956297059045</v>
+        <v>0.377468240524308</v>
       </c>
       <c r="D7">
-        <v>0.01668834489123549</v>
+        <v>0.01211812589292278</v>
       </c>
       <c r="E7">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F7">
-        <v>0.3451483985002391</v>
+        <v>0.3536000628492986</v>
       </c>
       <c r="G7">
-        <v>0.4108428609115699</v>
+        <v>0.4013364181993174</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4142,19 +4142,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.3890701789457732</v>
+        <v>0.4045179784499064</v>
       </c>
       <c r="D8">
-        <v>0.01320380553932205</v>
+        <v>0.01211100592507629</v>
       </c>
       <c r="E8">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F8">
-        <v>0.3630814750826037</v>
+        <v>0.3806638244497706</v>
       </c>
       <c r="G8">
-        <v>0.4150588828089427</v>
+        <v>0.4283721324500422</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.4061436715955709</v>
+        <v>0.4433883676605646</v>
       </c>
       <c r="D9">
-        <v>0.01396662276222915</v>
+        <v>0.01295474254447819</v>
       </c>
       <c r="E9">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F9">
-        <v>0.378653534615349</v>
+        <v>0.4178723679492403</v>
       </c>
       <c r="G9">
-        <v>0.4336338085757928</v>
+        <v>0.4689043673718888</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4206,19 +4206,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.4631303193870439</v>
+        <v>0.463886992323507</v>
       </c>
       <c r="D10">
-        <v>0.01680317847917396</v>
+        <v>0.01220322141461767</v>
       </c>
       <c r="E10">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F10">
-        <v>0.4300570642444468</v>
+        <v>0.4398512082835276</v>
       </c>
       <c r="G10">
-        <v>0.496203574529641</v>
+        <v>0.4879227763634864</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -4238,19 +4238,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.4245004248987604</v>
+        <v>0.4242603501160651</v>
       </c>
       <c r="D11">
-        <v>0.0166794093228485</v>
+        <v>0.01211310050305596</v>
       </c>
       <c r="E11">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F11">
-        <v>0.391670781337806</v>
+        <v>0.4004020705803626</v>
       </c>
       <c r="G11">
-        <v>0.4573300684597148</v>
+        <v>0.4481186296517676</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -4270,19 +4270,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.4702403160483241</v>
+        <v>0.4881959385654253</v>
       </c>
       <c r="D12">
-        <v>0.01320357703316289</v>
+        <v>0.01211287961042076</v>
       </c>
       <c r="E12">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F12">
-        <v>0.4442520619478297</v>
+        <v>0.4643380941056339</v>
       </c>
       <c r="G12">
-        <v>0.4962285701488184</v>
+        <v>0.5120537830252166</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.4353357069557003</v>
+        <v>0.50403392932306</v>
       </c>
       <c r="D13">
-        <v>0.01270509219919146</v>
+        <v>0.01429861918722489</v>
       </c>
       <c r="E13">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F13">
-        <v>0.4103286074694408</v>
+        <v>0.4758709950307782</v>
       </c>
       <c r="G13">
-        <v>0.4603428064419599</v>
+        <v>0.5321968636153418</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -4334,19 +4334,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.4717679675309258</v>
+        <v>0.4724520625006397</v>
       </c>
       <c r="D14">
-        <v>0.01576605822118161</v>
+        <v>0.0114977997635647</v>
       </c>
       <c r="E14">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F14">
-        <v>0.4407360489693005</v>
+        <v>0.4498056953929406</v>
       </c>
       <c r="G14">
-        <v>0.502799886092551</v>
+        <v>0.4950984296083388</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -4366,19 +4366,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.4406778095568594</v>
+        <v>0.4398806174687424</v>
       </c>
       <c r="D15">
-        <v>0.01527799293932859</v>
+        <v>0.01110660351299358</v>
       </c>
       <c r="E15">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F15">
-        <v>0.4106065370785317</v>
+        <v>0.4180047607268318</v>
       </c>
       <c r="G15">
-        <v>0.470749082035187</v>
+        <v>0.4617564742106529</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -4398,19 +4398,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.4666458378623947</v>
+        <v>0.4850393170692853</v>
       </c>
       <c r="D16">
-        <v>0.01181200814204686</v>
+        <v>0.01106828999741064</v>
       </c>
       <c r="E16">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F16">
-        <v>0.4433965722837103</v>
+        <v>0.4632389236296518</v>
       </c>
       <c r="G16">
-        <v>0.4898951034410791</v>
+        <v>0.5068397105089189</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -4430,19 +4430,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.4638719883464825</v>
+        <v>0.5047644292139591</v>
       </c>
       <c r="D17">
-        <v>0.01211908112696623</v>
+        <v>0.01160852986639891</v>
       </c>
       <c r="E17">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F17">
-        <v>0.4400183190717816</v>
+        <v>0.4818999651998759</v>
       </c>
       <c r="G17">
-        <v>0.4877256576211834</v>
+        <v>0.5276288932280423</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -4462,19 +4462,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.3379834880746022</v>
+        <v>0.3345443091112434</v>
       </c>
       <c r="D18">
-        <v>0.01679878266031015</v>
+        <v>0.01828529442135339</v>
       </c>
       <c r="E18">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F18">
-        <v>0.3049694433675152</v>
+        <v>0.2986065070221351</v>
       </c>
       <c r="G18">
-        <v>0.3709975327816892</v>
+        <v>0.3704821112003517</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -4494,19 +4494,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.3242386214342248</v>
+        <v>0.3207945540118847</v>
       </c>
       <c r="D19">
-        <v>0.01890343021541626</v>
+        <v>0.02065822670073463</v>
       </c>
       <c r="E19">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F19">
-        <v>0.2870883884162372</v>
+        <v>0.2801930058182743</v>
       </c>
       <c r="G19">
-        <v>0.3613888544522125</v>
+        <v>0.361396102205495</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4526,19 +4526,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.338155667106829</v>
+        <v>0.3356101593833198</v>
       </c>
       <c r="D20">
-        <v>0.01794076786034005</v>
+        <v>0.01960456981767319</v>
       </c>
       <c r="E20">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F20">
-        <v>0.302897319868363</v>
+        <v>0.2970794617683619</v>
       </c>
       <c r="G20">
-        <v>0.373414014345295</v>
+        <v>0.3741408569982778</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4558,19 +4558,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.361136863073061</v>
+        <v>0.3594473472787949</v>
       </c>
       <c r="D21">
-        <v>0.02185635192122892</v>
+        <v>0.02366868128322254</v>
       </c>
       <c r="E21">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F21">
-        <v>0.3181833589976677</v>
+        <v>0.3129290706754217</v>
       </c>
       <c r="G21">
-        <v>0.4040903671484544</v>
+        <v>0.4059656238821681</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4590,19 +4590,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.4245757217669021</v>
+        <v>0.4205375222574575</v>
       </c>
       <c r="D22">
-        <v>0.01748411157731142</v>
+        <v>0.01890777026537066</v>
       </c>
       <c r="E22">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F22">
-        <v>0.3902148247335214</v>
+        <v>0.3833763100786862</v>
       </c>
       <c r="G22">
-        <v>0.4589366188002827</v>
+        <v>0.4576987344362288</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -4622,19 +4622,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.3928153727438292</v>
+        <v>0.3884434812309747</v>
       </c>
       <c r="D23">
-        <v>0.01816851060272942</v>
+        <v>0.0195193272895778</v>
       </c>
       <c r="E23">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F23">
-        <v>0.3571094508667126</v>
+        <v>0.350080318741986</v>
       </c>
       <c r="G23">
-        <v>0.4285212946209458</v>
+        <v>0.4268066437199633</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4654,19 +4654,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.41870843230658</v>
+        <v>0.4163521335917623</v>
       </c>
       <c r="D24">
-        <v>0.01559098630087916</v>
+        <v>0.01687042618500841</v>
       </c>
       <c r="E24">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F24">
-        <v>0.3880680264406883</v>
+        <v>0.3831951045921238</v>
       </c>
       <c r="G24">
-        <v>0.4493488381724717</v>
+        <v>0.4495091625914008</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -4686,19 +4686,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.4116448611809405</v>
+        <v>0.4070682112508894</v>
       </c>
       <c r="D25">
-        <v>0.0167870571536159</v>
+        <v>0.01812660112940791</v>
       </c>
       <c r="E25">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F25">
-        <v>0.3786538601913683</v>
+        <v>0.3714423039547982</v>
       </c>
       <c r="G25">
-        <v>0.4446358621705127</v>
+        <v>0.4426941185469805</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4718,19 +4718,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.4027284975761965</v>
+        <v>0.4025334175913299</v>
       </c>
       <c r="D26">
-        <v>0.01725986490850642</v>
+        <v>0.01606948668204964</v>
       </c>
       <c r="E26">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F26">
-        <v>0.3687610669825527</v>
+        <v>0.370907986942467</v>
       </c>
       <c r="G26">
-        <v>0.4366959281698403</v>
+        <v>0.4341588482401928</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4750,19 +4750,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.3704878537345567</v>
+        <v>0.3698812534817219</v>
       </c>
       <c r="D27">
-        <v>0.01725955725302746</v>
+        <v>0.01606946975786758</v>
       </c>
       <c r="E27">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F27">
-        <v>0.3365210286071889</v>
+        <v>0.3382558561403664</v>
       </c>
       <c r="G27">
-        <v>0.4044546788619246</v>
+        <v>0.4015066508230775</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.3147282072212181</v>
+        <v>0.2660094812738468</v>
       </c>
       <c r="D28">
-        <v>0.0122435752362407</v>
+        <v>0.01606947613996428</v>
       </c>
       <c r="E28">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F28">
-        <v>0.2906328394845856</v>
+        <v>0.2343840713722546</v>
       </c>
       <c r="G28">
-        <v>0.3388235749578506</v>
+        <v>0.2976348911754391</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4814,19 +4814,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.2987224571922587</v>
+        <v>0.2911838651333893</v>
       </c>
       <c r="D29">
-        <v>0.01224314534283525</v>
+        <v>0.01606947673813314</v>
       </c>
       <c r="E29">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F29">
-        <v>0.2746279354862579</v>
+        <v>0.2595584540545754</v>
       </c>
       <c r="G29">
-        <v>0.3228169788982595</v>
+        <v>0.3228092762122032</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4846,19 +4846,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.3699093358946969</v>
+        <v>0.3700086048729745</v>
       </c>
       <c r="D30">
-        <v>0.01725986773983645</v>
+        <v>0.0160691522517243</v>
       </c>
       <c r="E30">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F30">
-        <v>0.335941899728993</v>
+        <v>0.3383838323971616</v>
       </c>
       <c r="G30">
-        <v>0.4038767720604008</v>
+        <v>0.4016333773487874</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4878,19 +4878,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.3237867413772416</v>
+        <v>0.323764859891623</v>
       </c>
       <c r="D31">
-        <v>0.01725956029452297</v>
+        <v>0.01606918401815179</v>
       </c>
       <c r="E31">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F31">
-        <v>0.2898199102642077</v>
+        <v>0.2921400248981348</v>
       </c>
       <c r="G31">
-        <v>0.3577535724902755</v>
+        <v>0.3553896948851111</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4910,19 +4910,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.3265412811691192</v>
+        <v>0.2831173897426095</v>
       </c>
       <c r="D32">
-        <v>0.01224357860875993</v>
+        <v>0.01606919112499654</v>
       </c>
       <c r="E32">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F32">
-        <v>0.3024459067953656</v>
+        <v>0.2514925407625497</v>
       </c>
       <c r="G32">
-        <v>0.3506366555428728</v>
+        <v>0.3147422387226693</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4942,19 +4942,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.2928681730141909</v>
+        <v>0.2956792827887463</v>
       </c>
       <c r="D33">
-        <v>0.01224816846982174</v>
+        <v>0.01606919179158742</v>
       </c>
       <c r="E33">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F33">
-        <v>0.2687637657894922</v>
+        <v>0.2640544324968075</v>
       </c>
       <c r="G33">
-        <v>0.3169725802388896</v>
+        <v>0.3273041330806852</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4974,19 +4974,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.3799658381038547</v>
+        <v>0.3798840641366767</v>
       </c>
       <c r="D34">
-        <v>0.01725986490732597</v>
+        <v>0.01606855226231776</v>
       </c>
       <c r="E34">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F34">
-        <v>0.3459984075125341</v>
+        <v>0.3482604724654372</v>
       </c>
       <c r="G34">
-        <v>0.4139332686951753</v>
+        <v>0.4115076558079162</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -5006,19 +5006,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.3638281731853922</v>
+        <v>0.3645379876570764</v>
       </c>
       <c r="D35">
-        <v>0.01725955725189185</v>
+        <v>0.01606869715734219</v>
       </c>
       <c r="E35">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F35">
-        <v>0.3298613480602592</v>
+        <v>0.3329141108262896</v>
       </c>
       <c r="G35">
-        <v>0.3977949983105252</v>
+        <v>0.3961618644878632</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5038,19 +5038,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.3329167077516153</v>
+        <v>0.3119996874503258</v>
       </c>
       <c r="D36">
-        <v>0.01224357520711736</v>
+        <v>0.01606870478898676</v>
       </c>
       <c r="E36">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F36">
-        <v>0.3088213400722976</v>
+        <v>0.2803757956001392</v>
       </c>
       <c r="G36">
-        <v>0.3570120754309331</v>
+        <v>0.3436235793005124</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -5070,19 +5070,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.3169087033390998</v>
+        <v>0.3126539999909358</v>
       </c>
       <c r="D37">
-        <v>0.01224314531339592</v>
+        <v>0.01606870550445572</v>
       </c>
       <c r="E37">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F37">
-        <v>0.2928141816910356</v>
+        <v>0.2810301067326759</v>
       </c>
       <c r="G37">
-        <v>0.3410032249871639</v>
+        <v>0.3442778932491957</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -5102,19 +5102,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.382844253802724</v>
+        <v>0.3834524226346734</v>
       </c>
       <c r="D38">
-        <v>0.01929427764278528</v>
+        <v>0.01796275864061999</v>
       </c>
       <c r="E38">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F38">
-        <v>0.3448730970086287</v>
+        <v>0.3481009525540664</v>
       </c>
       <c r="G38">
-        <v>0.4208154105968194</v>
+        <v>0.4188038927152804</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5134,19 +5134,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.3440327343068493</v>
+        <v>0.3439580758483202</v>
       </c>
       <c r="D39">
-        <v>0.01725982395171436</v>
+        <v>0.01606890787243427</v>
       </c>
       <c r="E39">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F39">
-        <v>0.3100653843162113</v>
+        <v>0.3123337843213043</v>
       </c>
       <c r="G39">
-        <v>0.3780000842974872</v>
+        <v>0.3755823673753361</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5166,19 +5166,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.3278589994442822</v>
+        <v>0.2978588197560455</v>
       </c>
       <c r="D40">
-        <v>0.01290002889273676</v>
+        <v>0.01606891550397321</v>
       </c>
       <c r="E40">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F40">
-        <v>0.3024717302858729</v>
+        <v>0.2662345132098376</v>
       </c>
       <c r="G40">
-        <v>0.3532462686026914</v>
+        <v>0.3294831263022534</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5198,19 +5198,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.2971430358058833</v>
+        <v>0.2900572847710853</v>
       </c>
       <c r="D41">
-        <v>0.01224345414547062</v>
+        <v>0.01606891621943225</v>
       </c>
       <c r="E41">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F41">
-        <v>0.2730479063760017</v>
+        <v>0.2584329768168238</v>
       </c>
       <c r="G41">
-        <v>0.3212381652357649</v>
+        <v>0.3216815927253469</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5230,19 +5230,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.297652096676544</v>
+        <v>0.2968574572989477</v>
       </c>
       <c r="D42">
-        <v>0.01580793564752364</v>
+        <v>0.02311028399607272</v>
       </c>
       <c r="E42">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F42">
-        <v>0.2665912755579222</v>
+        <v>0.2514384977066959</v>
       </c>
       <c r="G42">
-        <v>0.3287129177951658</v>
+        <v>0.3422764168911996</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5262,19 +5262,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.2997594949493386</v>
+        <v>0.3060104127395203</v>
       </c>
       <c r="D43">
-        <v>0.01585842270931748</v>
+        <v>0.02297076245696961</v>
       </c>
       <c r="E43">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F43">
-        <v>0.2685994724150386</v>
+        <v>0.2608656567506448</v>
       </c>
       <c r="G43">
-        <v>0.3309195174836385</v>
+        <v>0.3511551687283959</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5294,19 +5294,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.3092355412869496</v>
+        <v>0.2997259361485174</v>
       </c>
       <c r="D44">
-        <v>0.01591839331914273</v>
+        <v>0.01573980216509912</v>
       </c>
       <c r="E44">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F44">
-        <v>0.277957683228411</v>
+        <v>0.2687922860623411</v>
       </c>
       <c r="G44">
-        <v>0.3405133993454881</v>
+        <v>0.3306595862346937</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5326,19 +5326,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.2854351914565629</v>
+        <v>0.285614466161458</v>
       </c>
       <c r="D45">
-        <v>0.01611913634850436</v>
+        <v>0.01524420609786027</v>
       </c>
       <c r="E45">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F45">
-        <v>0.2537628958531834</v>
+        <v>0.255654817855434</v>
       </c>
       <c r="G45">
-        <v>0.3171074870599424</v>
+        <v>0.3155741144674821</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5358,19 +5358,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.3085870539629421</v>
+        <v>0.3034023236333847</v>
       </c>
       <c r="D46">
-        <v>0.01504040029460441</v>
+        <v>0.01491284158448591</v>
       </c>
       <c r="E46">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F46">
-        <v>0.2790343537546542</v>
+        <v>0.2740939105716274</v>
       </c>
       <c r="G46">
-        <v>0.33813975417123</v>
+        <v>0.332710736695142</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.2910568102740869</v>
+        <v>0.2847012704630619</v>
       </c>
       <c r="D47">
-        <v>0.01492289510351764</v>
+        <v>0.0140241218223688</v>
       </c>
       <c r="E47">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F47">
-        <v>0.2617349945912827</v>
+        <v>0.2571394705961615</v>
       </c>
       <c r="G47">
-        <v>0.3203786259568911</v>
+        <v>0.3122630703299622</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5422,19 +5422,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.3291182851857896</v>
+        <v>0.3227497500864411</v>
       </c>
       <c r="D48">
-        <v>0.01575576870707652</v>
+        <v>0.01567366373508314</v>
       </c>
       <c r="E48">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F48">
-        <v>0.2981599662560471</v>
+        <v>0.2919460827681486</v>
       </c>
       <c r="G48">
-        <v>0.3600766041155322</v>
+        <v>0.3535534174047337</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5454,19 +5454,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.2999671152737847</v>
+        <v>0.2946357119359247</v>
       </c>
       <c r="D49">
-        <v>0.01510007959992549</v>
+        <v>0.01514431202541271</v>
       </c>
       <c r="E49">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F49">
-        <v>0.270297151921947</v>
+        <v>0.2648723868270009</v>
       </c>
       <c r="G49">
-        <v>0.3296370786256225</v>
+        <v>0.3243990370448486</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5538,19 +5538,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.03344760411363264</v>
+        <v>0.03285581515211929</v>
       </c>
       <c r="D2">
-        <v>0.02362489755485346</v>
+        <v>0.01704040319790176</v>
       </c>
       <c r="E2">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F2">
-        <v>1.415777741934005</v>
+        <v>1.928112543496913</v>
       </c>
       <c r="G2">
-        <v>0.4905037017184845</v>
+        <v>0.2189537069517459</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -5570,19 +5570,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.0004231443295108475</v>
+        <v>-0.02812419420382665</v>
       </c>
       <c r="D3">
-        <v>0.0208573636910365</v>
+        <v>0.01703990916726058</v>
       </c>
       <c r="E3">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F3">
-        <v>0.02028752702301944</v>
+        <v>-1.650489678540231</v>
       </c>
       <c r="G3">
-        <v>0.9999969935195621</v>
+        <v>0.3523842813578689</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -5602,19 +5602,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.008304073020385275</v>
+        <v>-0.05319799497388642</v>
       </c>
       <c r="D4">
-        <v>0.0211243513130076</v>
+        <v>0.01714486306712741</v>
       </c>
       <c r="E4">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F4">
-        <v>0.3931042850661138</v>
+        <v>-3.102853301633259</v>
       </c>
       <c r="G4">
-        <v>0.9793605636520324</v>
+        <v>0.01142599094437158</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5634,19 +5634,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.03302445978412178</v>
+        <v>-0.06098000935594595</v>
       </c>
       <c r="D5">
-        <v>0.02081156008278523</v>
+        <v>0.01701069925300079</v>
       </c>
       <c r="E5">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F5">
-        <v>-1.586832493708088</v>
+        <v>-3.584803214082378</v>
       </c>
       <c r="G5">
-        <v>0.3877479277077435</v>
+        <v>0.002285422953939742</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -5666,19 +5666,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.02514353109324736</v>
+        <v>-0.08605381012600571</v>
       </c>
       <c r="D6">
-        <v>0.02108084905195313</v>
+        <v>0.01711747012047012</v>
       </c>
       <c r="E6">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F6">
-        <v>-1.192719089790068</v>
+        <v>-5.027250494399713</v>
       </c>
       <c r="G6">
-        <v>0.6319475926711973</v>
+        <v>5.69062427868694E-06</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -5698,19 +5698,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.007880928690874426</v>
+        <v>-0.02507380077005976</v>
       </c>
       <c r="D7">
-        <v>0.01792026162502372</v>
+        <v>0.01711689887530077</v>
       </c>
       <c r="E7">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F7">
-        <v>0.4397775465437153</v>
+        <v>-1.464856511259793</v>
       </c>
       <c r="G7">
-        <v>0.9715179990939278</v>
+        <v>0.4603736474920216</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -5730,19 +5730,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.002383582436969003</v>
+        <v>0.003170528028971202</v>
       </c>
       <c r="D8">
-        <v>0.02409295572921193</v>
+        <v>0.01737912003652278</v>
       </c>
       <c r="E8">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F8">
-        <v>0.09893275294898693</v>
+        <v>0.182433173964403</v>
       </c>
       <c r="G8">
-        <v>0.9996525846368518</v>
+        <v>0.9978399942868967</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5762,19 +5762,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.00869096680289966</v>
+        <v>-0.0238792098966272</v>
       </c>
       <c r="D9">
-        <v>0.02182442898825267</v>
+        <v>0.01737514755348094</v>
       </c>
       <c r="E9">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F9">
-        <v>-0.3982219561198005</v>
+        <v>-1.37433134441746</v>
       </c>
       <c r="G9">
-        <v>0.978576398928022</v>
+        <v>0.5166577856943719</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -5794,19 +5794,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.02576445945269742</v>
+        <v>-0.06274959910728539</v>
       </c>
       <c r="D10">
-        <v>0.02226134932123452</v>
+        <v>0.01788956343976646</v>
       </c>
       <c r="E10">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F10">
-        <v>-1.157362884024347</v>
+        <v>-3.507609300727831</v>
       </c>
       <c r="G10">
-        <v>0.6542180614428874</v>
+        <v>0.003000012767053528</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5826,19 +5826,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.01107454923986866</v>
+        <v>-0.0270497379255984</v>
       </c>
       <c r="D11">
-        <v>0.02127464671553604</v>
+        <v>0.01701465539391158</v>
       </c>
       <c r="E11">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F11">
-        <v>-0.5205514990658503</v>
+        <v>-1.589790524660153</v>
       </c>
       <c r="G11">
-        <v>0.9541068875314529</v>
+        <v>0.3863192953919052</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5858,19 +5858,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.02814804188966642</v>
+        <v>-0.06592012713625658</v>
       </c>
       <c r="D12">
-        <v>0.02174338030773234</v>
+        <v>0.01757133254880278</v>
       </c>
       <c r="E12">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F12">
-        <v>-1.294556848626544</v>
+        <v>-3.751572452070406</v>
       </c>
       <c r="G12">
-        <v>0.5671398115836701</v>
+        <v>0.001247051241080044</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5890,19 +5890,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.01707349264979776</v>
+        <v>-0.0388703892106582</v>
       </c>
       <c r="D13">
-        <v>0.0191981410936475</v>
+        <v>0.01756771459402441</v>
       </c>
       <c r="E13">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F13">
-        <v>-0.8893305120800071</v>
+        <v>-2.212603637349607</v>
       </c>
       <c r="G13">
-        <v>0.8104131514470407</v>
+        <v>0.1226497487509502</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.03862989448828355</v>
+        <v>0.03962664220744186</v>
       </c>
       <c r="D14">
-        <v>0.02366976396186377</v>
+        <v>0.01706819526270827</v>
       </c>
       <c r="E14">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F14">
-        <v>1.63203547574548</v>
+        <v>2.321665624134309</v>
       </c>
       <c r="G14">
-        <v>0.3622581946655021</v>
+        <v>0.09589511125327643</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -5954,19 +5954,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.007109996661280146</v>
+        <v>-0.02430894624191824</v>
       </c>
       <c r="D15">
-        <v>0.02136322004315347</v>
+        <v>0.01706767662974674</v>
       </c>
       <c r="E15">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F15">
-        <v>-0.3328148400343221</v>
+        <v>-1.424268034206302</v>
       </c>
       <c r="G15">
-        <v>0.98726778287164</v>
+        <v>0.485401574949336</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -5986,19 +5986,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.0277946124313435</v>
+        <v>-0.04014693699955289</v>
       </c>
       <c r="D16">
-        <v>0.02104281346212056</v>
+        <v>0.01852811226716494</v>
       </c>
       <c r="E16">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F16">
-        <v>1.320860087524748</v>
+        <v>-2.166812054064477</v>
       </c>
       <c r="G16">
-        <v>0.5503850999783002</v>
+        <v>0.1354698072124252</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -6018,19 +6018,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.04573989114956369</v>
+        <v>-0.06393558844936012</v>
       </c>
       <c r="D17">
-        <v>0.02126799354958007</v>
+        <v>0.01701069925300076</v>
       </c>
       <c r="E17">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F17">
-        <v>-2.150644396375924</v>
+        <v>-3.758551456259601</v>
       </c>
       <c r="G17">
-        <v>0.1398266551506695</v>
+        <v>0.001215191508504465</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -6050,19 +6050,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.01083528205694005</v>
+        <v>-0.07977357920699474</v>
       </c>
       <c r="D18">
-        <v>0.02095131913507843</v>
+        <v>0.01849256168114715</v>
       </c>
       <c r="E18">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F18">
-        <v>-0.5171646704955548</v>
+        <v>-4.313819825639545</v>
       </c>
       <c r="G18">
-        <v>0.9549382365480115</v>
+        <v>0.0001359181126431297</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -6082,19 +6082,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.03490460909262365</v>
+        <v>-0.01583799075763464</v>
       </c>
       <c r="D19">
-        <v>0.01830138512740206</v>
+        <v>0.01849165034613318</v>
       </c>
       <c r="E19">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F19">
-        <v>1.907211331253946</v>
+        <v>-0.8564941722979609</v>
       </c>
       <c r="G19">
-        <v>0.2272705067546905</v>
+        <v>0.8271637434240284</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -6114,19 +6114,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.03109015797406642</v>
+        <v>0.0325714450318973</v>
       </c>
       <c r="D20">
-        <v>0.02194342400326457</v>
+        <v>0.01585599065702707</v>
       </c>
       <c r="E20">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F20">
-        <v>1.416832576786607</v>
+        <v>2.054204353195823</v>
       </c>
       <c r="G20">
-        <v>0.4898461877732347</v>
+        <v>0.1712757145592638</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -6146,19 +6146,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.005122129668531045</v>
+        <v>-0.01258725456864562</v>
       </c>
       <c r="D21">
-        <v>0.01968977835941105</v>
+        <v>0.01583577433426332</v>
       </c>
       <c r="E21">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F21">
-        <v>0.2601415605109054</v>
+        <v>-0.7948619564128931</v>
       </c>
       <c r="G21">
-        <v>0.9938203600912145</v>
+        <v>0.8567338351606575</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -6178,19 +6178,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.007895979184443225</v>
+        <v>-0.03231236671331923</v>
       </c>
       <c r="D22">
-        <v>0.01986598503810964</v>
+        <v>0.01617764004468977</v>
       </c>
       <c r="E22">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F22">
-        <v>0.3974622536610232</v>
+        <v>-1.997347364885004</v>
       </c>
       <c r="G22">
-        <v>0.9786939624922482</v>
+        <v>0.1917624936946285</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>-0.02596802830553537</v>
+        <v>-0.04515869960054293</v>
       </c>
       <c r="D23">
-        <v>0.01930637155849235</v>
+        <v>0.01557638694358613</v>
       </c>
       <c r="E23">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F23">
-        <v>-1.345049649897199</v>
+        <v>-2.899176796525196</v>
       </c>
       <c r="G23">
-        <v>0.5350178394062474</v>
+        <v>0.0211157967482144</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -6242,19 +6242,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.02319417878962319</v>
+        <v>-0.06488381174521651</v>
       </c>
       <c r="D24">
-        <v>0.01949128110762277</v>
+        <v>0.0159379591820584</v>
       </c>
       <c r="E24">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F24">
-        <v>-1.189977131906033</v>
+        <v>-4.071023837120701</v>
       </c>
       <c r="G24">
-        <v>0.6336814405089857</v>
+        <v>0.0003655385151628554</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -6274,19 +6274,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.002773849515912179</v>
+        <v>-0.0197251121446736</v>
       </c>
       <c r="D25">
-        <v>0.01691209957373565</v>
+        <v>0.01591719466093115</v>
       </c>
       <c r="E25">
-        <v>286.6684792717628</v>
+        <v>246.7100497754794</v>
       </c>
       <c r="F25">
-        <v>0.1640156802423245</v>
+        <v>-1.239232953096252</v>
       </c>
       <c r="G25">
-        <v>0.9984272020188878</v>
+        <v>0.6025114420471054</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -6306,19 +6306,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.01374486664037734</v>
+        <v>0.01374975509935885</v>
       </c>
       <c r="D26">
-        <v>0.02405213732107125</v>
+        <v>0.02627717400900048</v>
       </c>
       <c r="E26">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F26">
-        <v>0.5714613407073781</v>
+        <v>0.5232585168652183</v>
       </c>
       <c r="G26">
-        <v>0.5679730420098974</v>
+        <v>0.6010589199947798</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -6338,19 +6338,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.02298119596623207</v>
+        <v>-0.02383718789547499</v>
       </c>
       <c r="D27">
-        <v>0.02645236991924388</v>
+        <v>0.02870964398437053</v>
       </c>
       <c r="E27">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F27">
-        <v>-0.8687764474937815</v>
+        <v>-0.8302850397048428</v>
       </c>
       <c r="G27">
-        <v>0.3854337879186768</v>
+        <v>0.4068298678469544</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -6370,19 +6370,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.03176034902307272</v>
+        <v>0.03209404102648289</v>
       </c>
       <c r="D28">
-        <v>0.02420285060771441</v>
+        <v>0.02619232110419312</v>
       </c>
       <c r="E28">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F28">
-        <v>1.312256541093115</v>
+        <v>1.225322524827514</v>
       </c>
       <c r="G28">
-        <v>0.1901043631552284</v>
+        <v>0.2211120680440994</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -6402,19 +6402,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.007063571125639573</v>
+        <v>0.009283922340873</v>
       </c>
       <c r="D29">
-        <v>0.02227743466289032</v>
+        <v>0.02416278051921781</v>
       </c>
       <c r="E29">
-        <v>448.7765161188047</v>
+        <v>438.0958967119831</v>
       </c>
       <c r="F29">
-        <v>0.3170729140283844</v>
+        <v>0.3842240893381064</v>
       </c>
       <c r="G29">
-        <v>0.7513357288650778</v>
+        <v>0.7009987884158191</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -6434,19 +6434,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.03224064384163975</v>
+        <v>0.032652164109608</v>
       </c>
       <c r="D30">
-        <v>0.0244012161525289</v>
+        <v>0.02271606794669441</v>
       </c>
       <c r="E30">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F30">
-        <v>1.321272007104383</v>
+        <v>1.437403875804107</v>
       </c>
       <c r="G30">
-        <v>0.550095836605623</v>
+        <v>0.4770371353325439</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -6466,19 +6466,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.0880002903549784</v>
+        <v>0.1365239363174831</v>
       </c>
       <c r="D31">
-        <v>0.02115348620580767</v>
+        <v>0.02271607859286344</v>
       </c>
       <c r="E31">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F31">
-        <v>4.160084512727647</v>
+        <v>6.010013381463381</v>
       </c>
       <c r="G31">
-        <v>0.0002430108384752216</v>
+        <v>3.273610404974647E-08</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -6498,19 +6498,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.1040060403839378</v>
+        <v>0.1113495524579406</v>
       </c>
       <c r="D32">
-        <v>0.02115314969999711</v>
+        <v>0.02271607958371251</v>
       </c>
       <c r="E32">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F32">
-        <v>4.916811059298274</v>
+        <v>4.901794433656523</v>
       </c>
       <c r="G32">
-        <v>8.670455483583694E-06</v>
+        <v>9.326967939427E-06</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.05575964651333866</v>
+        <v>0.1038717722078751</v>
       </c>
       <c r="D33">
-        <v>0.02115317569906084</v>
+        <v>0.02271601630760882</v>
       </c>
       <c r="E33">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F33">
-        <v>2.635994108242304</v>
+        <v>4.572622716998264</v>
       </c>
       <c r="G33">
-        <v>0.04356043091751571</v>
+        <v>4.188748403699538E-05</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -6562,19 +6562,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.07176539654229799</v>
+        <v>0.07869738834833256</v>
       </c>
       <c r="D34">
-        <v>0.02115285169450206</v>
+        <v>0.02271601682080321</v>
       </c>
       <c r="E34">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F34">
-        <v>3.392705512181646</v>
+        <v>3.46440086609999</v>
       </c>
       <c r="G34">
-        <v>0.004351075725429698</v>
+        <v>0.003400800115460401</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -6594,19 +6594,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.01600575002895935</v>
+        <v>-0.02517438385954255</v>
       </c>
       <c r="D35">
-        <v>0.01730519272768273</v>
+        <v>0.02271602224153445</v>
       </c>
       <c r="E35">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F35">
-        <v>0.9249102440422585</v>
+        <v>-1.108221483139473</v>
       </c>
       <c r="G35">
-        <v>0.79153603817809</v>
+        <v>0.6847595271780393</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -6626,19 +6626,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.04612259451745528</v>
+        <v>0.04624374498135156</v>
       </c>
       <c r="D36">
-        <v>0.02440121615252867</v>
+        <v>0.02271606794669435</v>
       </c>
       <c r="E36">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F36">
-        <v>1.890176056355111</v>
+        <v>2.035728414348266</v>
       </c>
       <c r="G36">
-        <v>0.2344539628992179</v>
+        <v>0.177283096246857</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -6658,19 +6658,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.04336805472557769</v>
+        <v>0.08689121513036502</v>
       </c>
       <c r="D37">
-        <v>0.02115348620606742</v>
+        <v>0.02271607859286329</v>
       </c>
       <c r="E37">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F37">
-        <v>2.050161108344331</v>
+        <v>3.825097486573392</v>
       </c>
       <c r="G37">
-        <v>0.1721952266189757</v>
+        <v>0.0009139096716971329</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -6690,19 +6690,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.07704116288050605</v>
+        <v>0.07432932208422817</v>
       </c>
       <c r="D38">
-        <v>0.02115588049033584</v>
+        <v>0.02271607958371241</v>
       </c>
       <c r="E38">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F38">
-        <v>3.641595674342131</v>
+        <v>3.272101676273524</v>
       </c>
       <c r="G38">
-        <v>0.001808322786657102</v>
+        <v>0.006524982254416889</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -6722,19 +6722,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.002754539791877592</v>
+        <v>0.04064747014901345</v>
       </c>
       <c r="D39">
-        <v>0.02115317571597685</v>
+        <v>0.0227160163076088</v>
       </c>
       <c r="E39">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F39">
-        <v>-0.1302187354212307</v>
+        <v>1.789374932584392</v>
       </c>
       <c r="G39">
-        <v>0.9992099862529791</v>
+        <v>0.2804771036216859</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -6754,19 +6754,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.03091856836305077</v>
+        <v>0.02808557710287658</v>
       </c>
       <c r="D40">
-        <v>0.02115557873498655</v>
+        <v>0.02271601682080321</v>
       </c>
       <c r="E40">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F40">
-        <v>1.46148534863376</v>
+        <v>1.236377720813975</v>
       </c>
       <c r="G40">
-        <v>0.4621944336145122</v>
+        <v>0.6042145163386584</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -6786,19 +6786,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.03367310815492836</v>
+        <v>-0.01256189304613687</v>
       </c>
       <c r="D41">
-        <v>0.01730854889298282</v>
+        <v>0.02271602224153442</v>
       </c>
       <c r="E41">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F41">
-        <v>1.945461076091711</v>
+        <v>-0.552997039383438</v>
       </c>
       <c r="G41">
-        <v>0.2114412392699156</v>
+        <v>0.9456856812407179</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -6818,19 +6818,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.01613766491846247</v>
+        <v>0.01534607647960032</v>
       </c>
       <c r="D42">
-        <v>0.02440121615252871</v>
+        <v>0.02271606794669438</v>
       </c>
       <c r="E42">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F42">
-        <v>0.6613467467190203</v>
+        <v>0.6755604233801152</v>
       </c>
       <c r="G42">
-        <v>0.9114756486524406</v>
+        <v>0.9062952998052286</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -6850,19 +6850,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.04704913035223942</v>
+        <v>0.06788437668635097</v>
       </c>
       <c r="D43">
-        <v>0.02115348619388568</v>
+        <v>0.02271607859286331</v>
       </c>
       <c r="E43">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F43">
-        <v>2.224178554825576</v>
+        <v>2.988384478810446</v>
       </c>
       <c r="G43">
-        <v>0.1190807717005602</v>
+        <v>0.01599662661905588</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.06305713476475494</v>
+        <v>0.0672300641457409</v>
       </c>
       <c r="D44">
-        <v>0.02115314968792109</v>
+        <v>0.02271607958371239</v>
       </c>
       <c r="E44">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F44">
-        <v>2.980980879682516</v>
+        <v>2.959580410782914</v>
       </c>
       <c r="G44">
-        <v>0.01635226841536652</v>
+        <v>0.01744408229681615</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -6914,19 +6914,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.03091146543377695</v>
+        <v>0.05253830020675065</v>
       </c>
       <c r="D45">
-        <v>0.02115317568702982</v>
+        <v>0.0227160163076088</v>
       </c>
       <c r="E45">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F45">
-        <v>1.461315591149299</v>
+        <v>2.312830713594477</v>
       </c>
       <c r="G45">
-        <v>0.4622985258313045</v>
+        <v>0.09741781195728771</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -6946,19 +6946,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.04691946984629248</v>
+        <v>0.05188398766614056</v>
       </c>
       <c r="D46">
-        <v>0.02115285168231704</v>
+        <v>0.02271601682080321</v>
       </c>
       <c r="E46">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F46">
-        <v>2.218115578502133</v>
+        <v>2.28402664408249</v>
       </c>
       <c r="G46">
-        <v>0.1206898728267261</v>
+        <v>0.1040878603186778</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -6978,19 +6978,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.01600800441251552</v>
+        <v>-0.0006543125406100858</v>
       </c>
       <c r="D47">
-        <v>0.01730519272768273</v>
+        <v>0.02271602224153441</v>
       </c>
       <c r="E47">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F47">
-        <v>0.9250405161283106</v>
+        <v>-0.02880401038759894</v>
       </c>
       <c r="G47">
-        <v>0.791465612175141</v>
+        <v>0.9999913973986267</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -7010,19 +7010,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.03881151949587472</v>
+        <v>0.03949434678635326</v>
       </c>
       <c r="D48">
-        <v>0.02587949552203154</v>
+        <v>0.02409249281153172</v>
       </c>
       <c r="E48">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F48">
-        <v>1.499701548000964</v>
+        <v>1.639280214600689</v>
       </c>
       <c r="G48">
-        <v>0.438958350022199</v>
+        <v>0.3582011528508798</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -7042,19 +7042,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.05498525435844186</v>
+        <v>0.08559360287862795</v>
       </c>
       <c r="D49">
-        <v>0.02320091161540244</v>
+        <v>0.02409250284947616</v>
       </c>
       <c r="E49">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F49">
-        <v>2.369960942480324</v>
+        <v>3.552706973343328</v>
       </c>
       <c r="G49">
-        <v>0.08518491774707304</v>
+        <v>0.002492357787253097</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -7074,19 +7074,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>0.08570121799684069</v>
+        <v>0.09339513786358809</v>
       </c>
       <c r="D50">
-        <v>0.02284266856669719</v>
+        <v>0.02409250378371723</v>
       </c>
       <c r="E50">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F50">
-        <v>3.751804118096181</v>
+        <v>3.876522701916462</v>
       </c>
       <c r="G50">
-        <v>0.001203920465948749</v>
+        <v>0.000750625093558055</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -7106,19 +7106,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>0.01617373486256713</v>
+        <v>0.04609925609227469</v>
       </c>
       <c r="D51">
-        <v>0.02153920713483702</v>
+        <v>0.0227160163076088</v>
       </c>
       <c r="E51">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F51">
-        <v>0.7508974105369042</v>
+        <v>2.029372380615592</v>
       </c>
       <c r="G51">
-        <v>0.8762377462650666</v>
+        <v>0.1795519580647085</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>0.04688969850096598</v>
+        <v>0.05390079107723482</v>
       </c>
       <c r="D52">
-        <v>0.02115285359175413</v>
+        <v>0.02271601682080319</v>
       </c>
       <c r="E52">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F52">
-        <v>2.216707939549332</v>
+        <v>2.372809964987911</v>
       </c>
       <c r="G52">
-        <v>0.1210658472263647</v>
+        <v>0.08462097941174296</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -7170,19 +7170,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.03071596363839883</v>
+        <v>0.007801534984960137</v>
       </c>
       <c r="D53">
-        <v>0.0177751139134337</v>
+        <v>0.02271602224153444</v>
       </c>
       <c r="E53">
-        <v>296.3585398158181</v>
+        <v>294.8452533888442</v>
       </c>
       <c r="F53">
-        <v>1.72803188705221</v>
+        <v>0.3434375482647508</v>
       </c>
       <c r="G53">
-        <v>0.3109576015411761</v>
+        <v>0.986047802338063</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -7202,19 +7202,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.002107398272794517</v>
+        <v>-0.009152955440572645</v>
       </c>
       <c r="D54">
-        <v>0.02065749092687895</v>
+        <v>0.02047523050283754</v>
       </c>
       <c r="E54">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F54">
-        <v>-0.1020161780660608</v>
+        <v>-0.4470257582352585</v>
       </c>
       <c r="G54">
-        <v>0.91878617335446</v>
+        <v>0.6550741352924401</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -7234,19 +7234,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.02380034983038674</v>
+        <v>0.01411146998705944</v>
       </c>
       <c r="D55">
-        <v>0.02091629733522389</v>
+        <v>0.0207977150239765</v>
       </c>
       <c r="E55">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F55">
-        <v>1.137885422498082</v>
+        <v>0.6785105945913353</v>
       </c>
       <c r="G55">
-        <v>0.2557324799875281</v>
+        <v>0.4978009972905388</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -7266,19 +7266,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.01753024368885521</v>
+        <v>0.0187010531703228</v>
       </c>
       <c r="D56">
-        <v>0.02037654098816715</v>
+        <v>0.01981084737210676</v>
       </c>
       <c r="E56">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F56">
-        <v>0.860314991589357</v>
+        <v>0.9439804779200649</v>
       </c>
       <c r="G56">
-        <v>0.3900422812034849</v>
+        <v>0.3456922885594463</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -7298,19 +7298,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.02915116991200478</v>
+        <v>0.02811403815051643</v>
       </c>
       <c r="D57">
-        <v>0.02087343728157944</v>
+        <v>0.0201901416665745</v>
       </c>
       <c r="E57">
-        <v>482.9768417047259</v>
+        <v>444.6211799224947</v>
       </c>
       <c r="F57">
-        <v>1.396567777446523</v>
+        <v>1.392463639671247</v>
       </c>
       <c r="G57">
-        <v>0.1631850240871996</v>
+        <v>0.1644780145462774</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>

--- a/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
+++ b/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
@@ -15,6 +15,7 @@
     <sheet name="k.check" sheetId="6" r:id="rId6"/>
     <sheet name="Estimated marginal means" sheetId="7" r:id="rId7"/>
     <sheet name="Pairwise contrasts" sheetId="8" r:id="rId8"/>
+    <sheet name="Urban vs reef contrasts" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -385,10 +386,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9876275990974327</v>
+        <v>0.9894466613071081</v>
       </c>
       <c r="C2">
-        <v>0.9776834449725377</v>
+        <v>0.9809056986485363</v>
       </c>
     </row>
     <row r="3">
@@ -398,10 +399,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9561955550655005</v>
+        <v>0.9453687883060539</v>
       </c>
       <c r="C3">
-        <v>0.9398230735780467</v>
+        <v>0.9284599001278659</v>
       </c>
     </row>
     <row r="4">
@@ -411,10 +412,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9819747412540549</v>
+        <v>0.9818942192876795</v>
       </c>
       <c r="C4">
-        <v>0.9710836203939552</v>
+        <v>0.9710235261278897</v>
       </c>
     </row>
     <row r="5">
@@ -424,10 +425,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9371381131003151</v>
+        <v>0.9364195852024547</v>
       </c>
       <c r="C5">
-        <v>0.8996423035631067</v>
+        <v>0.8987172245340105</v>
       </c>
     </row>
   </sheetData>
@@ -464,7 +465,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.08875053735725993</v>
+        <v>0.1503993127597375</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -477,7 +478,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6040822786626801</v>
+        <v>0.6195395654087178</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -566,13 +567,13 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>246.71</v>
+        <v>175.2</v>
       </c>
       <c r="D2">
-        <v>24.821</v>
+        <v>11.214</v>
       </c>
       <c r="E2">
-        <v>4.538938759809384E-14</v>
+        <v>9.098178860052314E-07</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -580,7 +581,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.2318470108010325</v>
+        <v>0.1610882868388543</v>
       </c>
     </row>
     <row r="3">
@@ -593,13 +594,13 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>246.71</v>
+        <v>175.2</v>
       </c>
       <c r="D3">
-        <v>56.497</v>
+        <v>37.297</v>
       </c>
       <c r="E3">
-        <v>7.77740443234144E-28</v>
+        <v>1.086170188016442E-18</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -607,7 +608,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.4072335241866309</v>
+        <v>0.3897405352309894</v>
       </c>
     </row>
     <row r="4">
@@ -620,13 +621,13 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>246.71</v>
+        <v>175.2</v>
       </c>
       <c r="D4">
-        <v>0.7653333333333308</v>
+        <v>3.893666666666667</v>
       </c>
       <c r="E4">
-        <v>0.6486330488962151</v>
+        <v>0.0001586072544670175</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -634,7 +635,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.02716109748499585</v>
+        <v>0.1666785576689831</v>
       </c>
     </row>
     <row r="5">
@@ -647,13 +648,13 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>438.1</v>
+        <v>412.77</v>
       </c>
       <c r="D5">
-        <v>0.279</v>
+        <v>0.867</v>
       </c>
       <c r="E5">
-        <v>0.5978466292280042</v>
+        <v>0.3522617877449978</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -661,7 +662,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.0006364355956831874</v>
+        <v>0.002096040731365908</v>
       </c>
     </row>
     <row r="6">
@@ -674,13 +675,13 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>438.1</v>
+        <v>412.77</v>
       </c>
       <c r="D6">
-        <v>8.965999999999999</v>
+        <v>7.254</v>
       </c>
       <c r="E6">
-        <v>8.942340437776982E-06</v>
+        <v>9.414990521751983E-05</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -688,7 +689,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.05784541008778531</v>
+        <v>0.05008146695755434</v>
       </c>
     </row>
     <row r="7">
@@ -701,13 +702,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>438.1</v>
+        <v>412.77</v>
       </c>
       <c r="D7">
-        <v>1.075999999999999</v>
+        <v>3.002333333333333</v>
       </c>
       <c r="E7">
-        <v>0.3589574785189045</v>
+        <v>0.03036127443420184</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -715,7 +716,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.007314287785955112</v>
+        <v>0.02135488658698791</v>
       </c>
     </row>
     <row r="8">
@@ -728,13 +729,13 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>294.85</v>
+        <v>295.55</v>
       </c>
       <c r="D8">
-        <v>30.111</v>
+        <v>30.036</v>
       </c>
       <c r="E8">
-        <v>5.207301104791132E-17</v>
+        <v>5.605917226991051E-17</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -742,7 +743,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>0.2345196958328898</v>
+        <v>0.2336474285506848</v>
       </c>
     </row>
     <row r="9">
@@ -755,13 +756,13 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>294.85</v>
+        <v>295.55</v>
       </c>
       <c r="D9">
-        <v>1.532</v>
+        <v>1.517</v>
       </c>
       <c r="E9">
-        <v>0.2061636942631429</v>
+        <v>0.2101118976470116</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -769,7 +770,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0.01534834327391249</v>
+        <v>0.01516489448552321</v>
       </c>
     </row>
     <row r="10">
@@ -782,13 +783,13 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>294.85</v>
+        <v>295.55</v>
       </c>
       <c r="D10">
-        <v>0.9660000000000003</v>
+        <v>0.9656666666666669</v>
       </c>
       <c r="E10">
-        <v>0.4683301010697978</v>
+        <v>0.4686063495239394</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -796,7 +797,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0.02864164668054714</v>
+        <v>0.02856616958266638</v>
       </c>
     </row>
     <row r="11">
@@ -809,13 +810,13 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>444.62</v>
+        <v>445.59</v>
       </c>
       <c r="D11">
-        <v>1.104</v>
+        <v>1.298</v>
       </c>
       <c r="E11">
-        <v>0.2939030883765817</v>
+        <v>0.2551891689128769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -823,7 +824,7 @@
         </is>
       </c>
       <c r="G11">
-        <v>0.002476869093878723</v>
+        <v>0.002904530889171336</v>
       </c>
     </row>
     <row r="12">
@@ -836,13 +837,13 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>444.62</v>
+        <v>445.59</v>
       </c>
       <c r="D12">
-        <v>0.391</v>
+        <v>0.428</v>
       </c>
       <c r="E12">
-        <v>0.759790582653203</v>
+        <v>0.7328822458621018</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -850,7 +851,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.002631266080894047</v>
+        <v>0.002873293143033607</v>
       </c>
     </row>
     <row r="13">
@@ -863,13 +864,13 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>444.62</v>
+        <v>445.59</v>
       </c>
       <c r="D13">
-        <v>0.7306666666666669</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="E13">
-        <v>0.5341044446352907</v>
+        <v>0.5247183317044345</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -877,7 +878,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>0.00490586644942392</v>
+        <v>0.005001898041667598</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +888,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -929,16 +930,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3746115501114647</v>
+        <v>0.4386256879721936</v>
       </c>
       <c r="C2">
-        <v>0.01202892872714909</v>
+        <v>0.01162963068231404</v>
       </c>
       <c r="D2">
-        <v>31.14255297447833</v>
+        <v>37.71621816325098</v>
       </c>
       <c r="E2">
-        <v>1.885124292219418E-87</v>
+        <v>5.131663032553078E-86</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -949,20 +950,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>treatmentLC</t>
+          <t>treatmentLC:siteRainbow</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.03259496550825047</v>
+        <v>0.05103480058539134</v>
       </c>
       <c r="C3">
-        <v>0.01694466197670757</v>
+        <v>0.03899314648083595</v>
       </c>
       <c r="D3">
-        <v>-1.923612613403329</v>
+        <v>1.3088146300395</v>
       </c>
       <c r="E3">
-        <v>0.05555385108145913</v>
+        <v>0.1923112665405252</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -973,20 +974,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>treatmentCH</t>
+          <t>treatmentCH:siteRainbow</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.02865309563484529</v>
+        <v>-0.03156642279546758</v>
       </c>
       <c r="C4">
-        <v>0.01694447704285277</v>
+        <v>0.02678917137592421</v>
       </c>
       <c r="D4">
-        <v>1.690999112122569</v>
+        <v>-1.178327703851145</v>
       </c>
       <c r="E4">
-        <v>0.09209981795566013</v>
+        <v>0.2402638944666043</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -997,20 +998,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>treatmentLH</t>
+          <t>treatmentLH:siteRainbow</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.05396216924362713</v>
+        <v>-0.03836506878535723</v>
       </c>
       <c r="C5">
-        <v>0.017032484072364</v>
+        <v>0.03740091221718866</v>
       </c>
       <c r="D5">
-        <v>3.168191381501613</v>
+        <v>-1.025778958613888</v>
       </c>
       <c r="E5">
-        <v>0.001727397558351033</v>
+        <v>0.3064099342031821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1021,20 +1022,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>siteRainbow</t>
+          <t>treatmentLC:siteStar</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.00875195132289148</v>
+        <v>0.02503130922524261</v>
       </c>
       <c r="C6">
-        <v>0.0172872256055464</v>
+        <v>0.03119451718466873</v>
       </c>
       <c r="D6">
-        <v>0.5062669697608112</v>
+        <v>0.8024265635226703</v>
       </c>
       <c r="E6">
-        <v>0.6131213501081705</v>
+        <v>0.4233933524524296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1045,20 +1046,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>siteStar</t>
+          <t>treatmentCH:siteStar</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.09106532814321498</v>
+        <v>-0.01268907931033241</v>
       </c>
       <c r="C7">
-        <v>0.01699270717975898</v>
+        <v>0.02678917137592421</v>
       </c>
       <c r="D7">
-        <v>5.359082998363455</v>
+        <v>-0.4736644942193419</v>
       </c>
       <c r="E7">
-        <v>1.919040509305783E-07</v>
+        <v>0.6363288595428018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1069,20 +1070,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>siteMacN</t>
+          <t>treatmentLH:siteStar</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.09932011624256573</v>
+        <v>-0.01551799636626711</v>
       </c>
       <c r="C8">
-        <v>0.01647041649598936</v>
+        <v>0.03740091221718864</v>
       </c>
       <c r="D8">
-        <v>6.030212791932173</v>
+        <v>-0.4149095689472349</v>
       </c>
       <c r="E8">
-        <v>5.943780176063468E-09</v>
+        <v>0.6787157146962113</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,20 +1094,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>treatmentLC:siteRainbow</t>
+          <t>treatmentLC:siteMacN</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.02968528712314809</v>
+        <v>0.01990324763414215</v>
       </c>
       <c r="C9">
-        <v>0.02409809291136045</v>
+        <v>0.03119451718466874</v>
       </c>
       <c r="D9">
-        <v>1.231852131715937</v>
+        <v>0.6380367266566979</v>
       </c>
       <c r="E9">
-        <v>0.2191771389835815</v>
+        <v>0.5242828059518212</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1117,20 +1118,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>treatmentCH:siteRainbow</t>
+          <t>treatmentCH:siteMacN</t>
         </is>
       </c>
       <c r="B10">
-        <v>-0.004244984307199449</v>
+        <v>-0.02216949829613561</v>
       </c>
       <c r="C10">
-        <v>0.02409630344279757</v>
+        <v>0.02514982378765276</v>
       </c>
       <c r="D10">
-        <v>-0.1761674489731031</v>
+        <v>-0.8814971621001839</v>
       </c>
       <c r="E10">
-        <v>0.8603069124681181</v>
+        <v>0.3792564790982089</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1141,20 +1142,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>treatmentLH:siteRainbow</t>
+          <t>treatmentLH:siteMacN</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.009551604133398983</v>
+        <v>-0.0231311198819238</v>
       </c>
       <c r="C11">
-        <v>0.02443569664402871</v>
+        <v>0.02917979891271558</v>
       </c>
       <c r="D11">
-        <v>0.3908873265429527</v>
+        <v>-0.7927100509196463</v>
       </c>
       <c r="E11">
-        <v>0.6962178617339863</v>
+        <v>0.4290188727792749</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1165,48 +1166,48 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>treatmentLC:siteStar</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="B12">
-        <v>-0.006770827055322568</v>
+        <v>0.3945470664665202</v>
       </c>
       <c r="C12">
-        <v>0.02390107932414266</v>
+        <v>0.01389093318102155</v>
       </c>
       <c r="D12">
-        <v>-0.2832854099807662</v>
+        <v>28.40320814483285</v>
       </c>
       <c r="E12">
-        <v>0.7771956246245848</v>
+        <v>3.828954088859774E-99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>treatmentCH:siteStar</t>
+          <t>treatmentLH:siteRainbow</t>
         </is>
       </c>
       <c r="B13">
-        <v>-0.003815247961908407</v>
+        <v>0.02778022203094027</v>
       </c>
       <c r="C13">
-        <v>0.02390107932414263</v>
+        <v>0.04666346702117233</v>
       </c>
       <c r="D13">
-        <v>-0.1596265971995081</v>
+        <v>0.5953312902861617</v>
       </c>
       <c r="E13">
-        <v>0.8733058334833712</v>
+        <v>0.5519482861519334</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
@@ -1217,260 +1218,260 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.01305105797433353</v>
+        <v>-0.03637784107739722</v>
       </c>
       <c r="C14">
-        <v>0.02484215236827948</v>
+        <v>0.03866704233954938</v>
       </c>
       <c r="D14">
-        <v>-0.5253593883836815</v>
+        <v>-0.9407970942786404</v>
       </c>
       <c r="E14">
-        <v>0.5998052127208071</v>
+        <v>0.3473590868962794</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>treatmentLC:siteMacN</t>
+          <t>treatmentLH:siteMacN</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.0002843701202219904</v>
+        <v>-0.00588250088840088</v>
       </c>
       <c r="C15">
-        <v>0.02302786082658081</v>
+        <v>0.03690979149786645</v>
       </c>
       <c r="D15">
-        <v>0.01234895947841343</v>
+        <v>-0.1593750777145657</v>
       </c>
       <c r="E15">
-        <v>0.990157186423982</v>
+        <v>0.8734513259167644</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>treatmentCH:siteMacN</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="B16">
-        <v>-0.01553693963518103</v>
+        <v>0.3138184996420411</v>
       </c>
       <c r="C16">
-        <v>0.02301785088070507</v>
+        <v>0.01285164456162865</v>
       </c>
       <c r="D16">
-        <v>-0.6749952337298792</v>
+        <v>24.41854800272127</v>
       </c>
       <c r="E16">
-        <v>0.5003108839315853</v>
+        <v>7.472337606185724E-73</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>treatmentLH:siteMacN</t>
+          <t>treatmentLC:siteRainbow</t>
         </is>
       </c>
       <c r="B17">
-        <v>-0.0208856282605672</v>
+        <v>-0.0135905832761481</v>
       </c>
       <c r="C17">
-        <v>0.02324730460441314</v>
+        <v>0.03210613509143157</v>
       </c>
       <c r="D17">
-        <v>-0.8984107455021854</v>
+        <v>-0.42330175330805</v>
       </c>
       <c r="E17">
-        <v>0.3698425703627808</v>
+        <v>0.672382977309413</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>treatmentCH:siteRainbow</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.3538569193536671</v>
+        <v>0.04963062453130374</v>
       </c>
       <c r="C18">
-        <v>0.01716628041972326</v>
+        <v>0.03210613509143156</v>
       </c>
       <c r="D18">
-        <v>20.61348822818379</v>
+        <v>1.545829929076362</v>
       </c>
       <c r="E18">
-        <v>1.720371654776551E-66</v>
+        <v>0.1232157107501538</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>treatmentLH</t>
+          <t>treatmentLH:siteRainbow</t>
         </is>
       </c>
       <c r="B19">
-        <v>-0.009274300213643458</v>
+        <v>0.0370205683824967</v>
       </c>
       <c r="C19">
-        <v>0.02507576492903485</v>
+        <v>0.03210613509143152</v>
       </c>
       <c r="D19">
-        <v>-0.3698511387345511</v>
+        <v>1.15306835522463</v>
       </c>
       <c r="E19">
-        <v>0.7116721305786542</v>
+        <v>0.2498140208310467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>siteRainbow</t>
+          <t>treatmentLC:siteStar</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.008249531252494256</v>
+        <v>0.01730873497980174</v>
       </c>
       <c r="C20">
-        <v>0.02499351367378204</v>
+        <v>0.03210613509143156</v>
       </c>
       <c r="D20">
-        <v>0.3300668869598729</v>
+        <v>0.5391098906956593</v>
       </c>
       <c r="E20">
-        <v>0.7415071949217368</v>
+        <v>0.5902168964895658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>siteStar</t>
+          <t>treatmentCH:siteStar</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.09067204198564903</v>
+        <v>0.0686361477464959</v>
       </c>
       <c r="C21">
-        <v>0.02490290385817264</v>
+        <v>0.03210613509143164</v>
       </c>
       <c r="D21">
-        <v>3.641022850268615</v>
+        <v>2.13778916556086</v>
       </c>
       <c r="E21">
-        <v>0.0003040041253140457</v>
+        <v>0.03335407221107774</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>siteMacN</t>
+          <t>treatmentLH:siteStar</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.08929481026316814</v>
+        <v>0.04411885837877381</v>
       </c>
       <c r="C22">
-        <v>0.02354863547270266</v>
+        <v>0.03210613509143161</v>
       </c>
       <c r="D22">
-        <v>3.791931399451054</v>
+        <v>1.37415662935238</v>
       </c>
       <c r="E22">
-        <v>0.0001704447019601174</v>
+        <v>0.1704342312671515</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>treatmentLH:siteRainbow</t>
+          <t>treatmentLC:siteMacN</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.03758694299483386</v>
+        <v>-0.006843576505077798</v>
       </c>
       <c r="C23">
-        <v>0.03700991685938299</v>
+        <v>0.03309424655308052</v>
       </c>
       <c r="D23">
-        <v>1.01559112217526</v>
+        <v>-0.2067905215518731</v>
       </c>
       <c r="E23">
-        <v>0.3103846772735057</v>
+        <v>0.8363158515220516</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>treatmentLH:siteStar</t>
+          <t>treatmentCH:siteMacN</t>
         </is>
       </c>
       <c r="B24">
-        <v>-0.01834428592712405</v>
+        <v>0.0509272468954484</v>
       </c>
       <c r="C24">
-        <v>0.03543284379623297</v>
+        <v>0.03309424655308055</v>
       </c>
       <c r="D24">
-        <v>-0.5177198317080693</v>
+        <v>1.538855003505371</v>
       </c>
       <c r="E24">
-        <v>0.6049150823541165</v>
+        <v>0.124909604573518</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
@@ -1481,20 +1482,20 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.00446583275848585</v>
+        <v>0.01794852772641631</v>
       </c>
       <c r="C25">
-        <v>0.03412319780466619</v>
+        <v>0.03309424655308054</v>
       </c>
       <c r="D25">
-        <v>0.1308738056746595</v>
+        <v>0.5423458635817044</v>
       </c>
       <c r="E25">
-        <v>0.8959352115249221</v>
+        <v>0.587988958188609</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
@@ -1505,570 +1506,90 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4025334175913302</v>
+        <v>0.3205614863572391</v>
       </c>
       <c r="C26">
-        <v>0.01606948668204964</v>
+        <v>0.009399211856398094</v>
       </c>
       <c r="D26">
-        <v>25.04955046516692</v>
+        <v>34.10514533077911</v>
       </c>
       <c r="E26">
-        <v>5.404889316551242E-75</v>
+        <v>2.673552169490497E-126</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ssid_control</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>treatmentLC</t>
+          <t>treatmentLH:siteRainbow</t>
         </is>
       </c>
       <c r="B27">
-        <v>-0.03265216410960747</v>
+        <v>-0.02388828650690011</v>
       </c>
       <c r="C27">
-        <v>0.02271606794669441</v>
+        <v>0.02660351065239026</v>
       </c>
       <c r="D27">
-        <v>-1.437403875804084</v>
+        <v>-0.8979373744703051</v>
       </c>
       <c r="E27">
-        <v>0.151663656230837</v>
+        <v>0.3697038561709641</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ssid_control</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>treatmentCH</t>
+          <t>treatmentLH:siteStar</t>
         </is>
       </c>
       <c r="B28">
-        <v>-0.1365239363174825</v>
+        <v>-0.02842690840831184</v>
       </c>
       <c r="C28">
-        <v>0.02271607859286344</v>
+        <v>0.02613019749612858</v>
       </c>
       <c r="D28">
-        <v>-6.010013381463355</v>
+        <v>-1.087894892969084</v>
       </c>
       <c r="E28">
-        <v>5.46556321687286E-09</v>
+        <v>0.2772295879043122</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ssid_control</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>treatmentLH</t>
+          <t>treatmentLH:siteMacN</t>
         </is>
       </c>
       <c r="B29">
-        <v>-0.1113495524579403</v>
+        <v>-0.03739645439423202</v>
       </c>
       <c r="C29">
-        <v>0.02271607958371251</v>
+        <v>0.02643497420496783</v>
       </c>
       <c r="D29">
-        <v>-4.901794433656513</v>
+        <v>-1.414658251764219</v>
       </c>
       <c r="E29">
-        <v>1.570389635875689E-06</v>
+        <v>0.1578671151072505</v>
       </c>
       <c r="F29" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>siteRainbow</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>-0.03252481271835564</v>
-      </c>
-      <c r="C30">
-        <v>0.02271567993677114</v>
-      </c>
-      <c r="D30">
-        <v>-1.431822107411626</v>
-      </c>
-      <c r="E30">
-        <v>0.1532539320318048</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>siteStar</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>-0.02264935345465341</v>
-      </c>
-      <c r="C31">
-        <v>0.02271528464549201</v>
-      </c>
-      <c r="D31">
-        <v>-0.9970974966033858</v>
-      </c>
-      <c r="E31">
-        <v>0.3195347799717553</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>siteMacN</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>-0.01908099495665671</v>
-      </c>
-      <c r="C32">
-        <v>0.02409203534726483</v>
-      </c>
-      <c r="D32">
-        <v>-0.7920042736788934</v>
-      </c>
-      <c r="E32">
-        <v>0.4289949142432127</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>treatmentLC:siteRainbow</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>-0.01359158087174355</v>
-      </c>
-      <c r="C33">
-        <v>0.03210693804519506</v>
-      </c>
-      <c r="D33">
-        <v>-0.4233222380973072</v>
-      </c>
-      <c r="E33">
-        <v>0.6723687869115376</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>treatmentCH:siteRainbow</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>0.04963272118711809</v>
-      </c>
-      <c r="C34">
-        <v>0.03210693804519512</v>
-      </c>
-      <c r="D34">
-        <v>1.545856572098308</v>
-      </c>
-      <c r="E34">
-        <v>0.123211835067649</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>treatmentLH:siteRainbow</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>0.0370202303737124</v>
-      </c>
-      <c r="C35">
-        <v>0.03210693804519519</v>
-      </c>
-      <c r="D35">
-        <v>1.153028990855529</v>
-      </c>
-      <c r="E35">
-        <v>0.2498323794485739</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>treatmentLC:siteStar</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>0.01730608763000769</v>
-      </c>
-      <c r="C36">
-        <v>0.03210693804519512</v>
-      </c>
-      <c r="D36">
-        <v>0.5390139541069562</v>
-      </c>
-      <c r="E36">
-        <v>0.5902839783788811</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>treatmentCH:siteStar</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>0.06863955963113214</v>
-      </c>
-      <c r="C37">
-        <v>0.03210693804519516</v>
-      </c>
-      <c r="D37">
-        <v>2.137841968440342</v>
-      </c>
-      <c r="E37">
-        <v>0.03335171519025802</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>treatmentLH:siteStar</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>0.04411948831219967</v>
-      </c>
-      <c r="C38">
-        <v>0.03210693804519516</v>
-      </c>
-      <c r="D38">
-        <v>1.37414188329311</v>
-      </c>
-      <c r="E38">
-        <v>0.170441293748321</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>treatmentLC:siteMacN</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>-0.006842182676745263</v>
-      </c>
-      <c r="C39">
-        <v>0.03309507421887541</v>
-      </c>
-      <c r="D39">
-        <v>-0.2067432340986533</v>
-      </c>
-      <c r="E39">
-        <v>0.8363530902685575</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>treatmentCH:siteMacN</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>0.05093033343885515</v>
-      </c>
-      <c r="C40">
-        <v>0.03309507421887545</v>
-      </c>
-      <c r="D40">
-        <v>1.538909781619632</v>
-      </c>
-      <c r="E40">
-        <v>0.1248987902624453</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>treatmentLH:siteMacN</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>0.01795441459435246</v>
-      </c>
-      <c r="C41">
-        <v>0.03309507421887544</v>
-      </c>
-      <c r="D41">
-        <v>0.542510177666027</v>
-      </c>
-      <c r="E41">
-        <v>0.5878769118611451</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>0.3045048078918793</v>
-      </c>
-      <c r="C42">
-        <v>0.01341566766122981</v>
-      </c>
-      <c r="D42">
-        <v>22.69770059762836</v>
-      </c>
-      <c r="E42">
-        <v>2.613263520748264E-76</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>treatmentLH</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>-0.002824757953022443</v>
-      </c>
-      <c r="C43">
-        <v>0.01873045540568325</v>
-      </c>
-      <c r="D43">
-        <v>-0.1508109595757798</v>
-      </c>
-      <c r="E43">
-        <v>0.8801932360076512</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>siteRainbow</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.01261976385629086</v>
-      </c>
-      <c r="C44">
-        <v>0.01891061019151644</v>
-      </c>
-      <c r="D44">
-        <v>0.6673377394216641</v>
-      </c>
-      <c r="E44">
-        <v>0.5049026214177382</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>siteStar</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.0233210791319629</v>
-      </c>
-      <c r="C45">
-        <v>0.01870931741531259</v>
-      </c>
-      <c r="D45">
-        <v>1.246495455407466</v>
-      </c>
-      <c r="E45">
-        <v>0.2132388600594329</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>siteMacN</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.03336629664688411</v>
-      </c>
-      <c r="C46">
-        <v>0.01916096179047589</v>
-      </c>
-      <c r="D46">
-        <v>1.741368570729529</v>
-      </c>
-      <c r="E46">
-        <v>0.08231063464544221</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>treatmentLH:siteRainbow</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>-0.02326442542763208</v>
-      </c>
-      <c r="C47">
-        <v>0.02659478606201258</v>
-      </c>
-      <c r="D47">
-        <v>-0.8747739264901433</v>
-      </c>
-      <c r="E47">
-        <v>0.3821692054271787</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>treatmentLH:siteStar</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>-0.02785400861089544</v>
-      </c>
-      <c r="C48">
-        <v>0.02613246361857858</v>
-      </c>
-      <c r="D48">
-        <v>-1.065877638535884</v>
-      </c>
-      <c r="E48">
-        <v>0.2870574063104031</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>treatmentLH:siteMacN</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>-0.03726699359108907</v>
-      </c>
-      <c r="C49">
-        <v>0.02644135638636404</v>
-      </c>
-      <c r="D49">
-        <v>-1.4094206456938</v>
-      </c>
-      <c r="E49">
-        <v>0.1594098595356221</v>
-      </c>
-      <c r="F49" t="inlineStr">
         <is>
           <t>ssid_heat</t>
         </is>
@@ -2081,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2123,16 +1644,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.437030204643323</v>
+        <v>4.207660424272711</v>
       </c>
       <c r="C2">
-        <v>4.734675796301638</v>
+        <v>4.710174816804201</v>
       </c>
       <c r="D2">
-        <v>7.185198633704571</v>
+        <v>8.124319120795622</v>
       </c>
       <c r="E2">
-        <v>4.745651165205533E-06</v>
+        <v>8.745205310189963E-06</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2143,20 +1664,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s(time):treatmentCC</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B3">
-        <v>1.383317805994409</v>
+        <v>13.51044370129423</v>
       </c>
       <c r="C3">
-        <v>1.883860479044593</v>
+        <v>15.15836574407671</v>
       </c>
       <c r="D3">
-        <v>1.675983508005414</v>
+        <v>5.89409037463748</v>
       </c>
       <c r="E3">
-        <v>0.2569959056491588</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2167,17 +1688,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>s(time):treatmentLC</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B4">
-        <v>4.66893761214026</v>
+        <v>9.359525948867519</v>
       </c>
       <c r="C4">
-        <v>4.912254758367309</v>
+        <v>9.808204082036758</v>
       </c>
       <c r="D4">
-        <v>12.84601443815747</v>
+        <v>7.432278876209167</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -2191,20 +1712,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>s(time):treatmentCH</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B5">
-        <v>3.74831003098071</v>
+        <v>105.7178256969666</v>
       </c>
       <c r="C5">
-        <v>4.321171578611158</v>
+        <v>295</v>
       </c>
       <c r="D5">
-        <v>3.981930128570848</v>
+        <v>15.64907273388529</v>
       </c>
       <c r="E5">
-        <v>0.003093393799922461</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2215,766 +1736,286 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>s(time):treatmentLH</t>
+          <t>s(time)</t>
         </is>
       </c>
       <c r="B6">
-        <v>1.000017813863155</v>
+        <v>4.216082931460624</v>
       </c>
       <c r="C6">
-        <v>1.000024793283778</v>
+        <v>5.497236023107378</v>
       </c>
       <c r="D6">
-        <v>0.09870333815635508</v>
+        <v>13.6589196813538</v>
       </c>
       <c r="E6">
-        <v>0.753675745184935</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>s(time):siteEmerald</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B7">
-        <v>4.494712550142255</v>
+        <v>8.02834592507161</v>
       </c>
       <c r="C7">
-        <v>4.858450913432605</v>
+        <v>9.855963490766531</v>
       </c>
       <c r="D7">
-        <v>7.123248672119646</v>
+        <v>2.306153326299017</v>
       </c>
       <c r="E7">
-        <v>3.039977636160041E-05</v>
+        <v>0.01128697896204423</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>s(time):siteRainbow</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B8">
-        <v>2.091194432423091E-06</v>
+        <v>7.331844532540197</v>
       </c>
       <c r="C8">
-        <v>3.530366438491225E-06</v>
+        <v>7.986847168273483</v>
       </c>
       <c r="D8">
-        <v>0.04154527433430071</v>
+        <v>3.657388696657637</v>
       </c>
       <c r="E8">
-        <v>0.9996948222912792</v>
+        <v>0.0004214248467943049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s(time):siteStar</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B9">
-        <v>1.000002537800571</v>
+        <v>105.6501917237823</v>
       </c>
       <c r="C9">
-        <v>1.00000427903631</v>
+        <v>530</v>
       </c>
       <c r="D9">
-        <v>0.9795963794452118</v>
+        <v>1.598208755755502</v>
       </c>
       <c r="E9">
-        <v>0.3232672040953517</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>s(time):siteMacN</t>
+          <t>s(time)</t>
         </is>
       </c>
       <c r="B10">
-        <v>2.744605638666821</v>
+        <v>4.720206646905807</v>
       </c>
       <c r="C10">
-        <v>3.329181669008129</v>
+        <v>4.964492102727753</v>
       </c>
       <c r="D10">
-        <v>2.167567852931014</v>
+        <v>31.04216896499203</v>
       </c>
       <c r="E10">
-        <v>0.06984114683989839</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>s(time,exp_unit)</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B11">
-        <v>159.8130139390948</v>
+        <v>13.54705390654074</v>
       </c>
       <c r="C11">
-        <v>423</v>
+        <v>15.42082954936395</v>
       </c>
       <c r="D11">
-        <v>13.3871614373032</v>
+        <v>7.198278440055038</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>s(time)</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B12">
-        <v>1.000010018739211</v>
+        <v>9.312880779257217</v>
       </c>
       <c r="C12">
-        <v>1.000013313002918</v>
+        <v>10.57688950392398</v>
       </c>
       <c r="D12">
-        <v>1.03822309312251</v>
+        <v>0.8545312082982517</v>
       </c>
       <c r="E12">
-        <v>0.3087960522252479</v>
+        <v>0.5644261244700017</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>s(time):treatmentCH</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B13">
-        <v>6.17247707600399</v>
+        <v>140.8688178919291</v>
       </c>
       <c r="C13">
-        <v>8.033446755036849</v>
+        <v>451</v>
       </c>
       <c r="D13">
-        <v>1.905903792467365</v>
+        <v>7.621766849213619</v>
       </c>
       <c r="E13">
-        <v>0.05899412557532457</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>s(time):treatmentLH</t>
+          <t>s(time)</t>
         </is>
       </c>
       <c r="B14">
-        <v>5.057883339980297</v>
+        <v>9.531246996852431</v>
       </c>
       <c r="C14">
-        <v>6.498213907275719</v>
+        <v>10.70799276879246</v>
       </c>
       <c r="D14">
-        <v>2.640741763399863</v>
+        <v>7.671788182235928</v>
       </c>
       <c r="E14">
-        <v>0.01357300910934417</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>s(time):siteEmerald</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B15">
-        <v>2.541523562966276E-05</v>
+        <v>5.862474849613238</v>
       </c>
       <c r="C15">
-        <v>4.092772519029586E-05</v>
+        <v>7.122711059746422</v>
       </c>
       <c r="D15">
-        <v>0.001012851128021072</v>
+        <v>1.156948530758175</v>
       </c>
       <c r="E15">
-        <v>0.9998377388314241</v>
+        <v>0.3184920484690186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>s(time):siteRainbow</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B16">
-        <v>1.465684238340331</v>
+        <v>16.0786169120118</v>
       </c>
       <c r="C16">
-        <v>1.726904387451023</v>
+        <v>18.48904396261522</v>
       </c>
       <c r="D16">
-        <v>0.9554520531353746</v>
+        <v>3.018443581207902</v>
       </c>
       <c r="E16">
-        <v>0.4563646271588468</v>
+        <v>3.175226413731913E-05</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>s(time):siteStar</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B17">
-        <v>1.000003636133822</v>
+        <v>229.9369333828239</v>
       </c>
       <c r="C17">
-        <v>1.00000582212547</v>
+        <v>699</v>
       </c>
       <c r="D17">
-        <v>0.5107499612917278</v>
+        <v>2.892607174697119</v>
       </c>
       <c r="E17">
-        <v>0.4751960658978684</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>s(time):siteMacN</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>2.507994383146582</v>
-      </c>
-      <c r="C18">
-        <v>3.198456842273021</v>
-      </c>
-      <c r="D18">
-        <v>0.8572573655423694</v>
-      </c>
-      <c r="E18">
-        <v>0.4500940823286531</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>139.7000251804372</v>
-      </c>
-      <c r="C19">
-        <v>591</v>
-      </c>
-      <c r="D19">
-        <v>2.17979950488841</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>2.801155527955589</v>
-      </c>
-      <c r="C20">
-        <v>3.359656955432805</v>
-      </c>
-      <c r="D20">
-        <v>1.009623415313417</v>
-      </c>
-      <c r="E20">
-        <v>0.3682502306583644</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>s(time):treatmentCC</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>1.000009400452073</v>
-      </c>
-      <c r="C21">
-        <v>1.000013417737377</v>
-      </c>
-      <c r="D21">
-        <v>0.5082736481865406</v>
-      </c>
-      <c r="E21">
-        <v>0.4764510077760598</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>s(time):treatmentLC</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>3.138566960297332</v>
-      </c>
-      <c r="C22">
-        <v>3.650660183077969</v>
-      </c>
-      <c r="D22">
-        <v>3.560646960295764</v>
-      </c>
-      <c r="E22">
-        <v>0.01248430383484589</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>s(time):treatmentCH</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>4.228792691358922</v>
-      </c>
-      <c r="C23">
-        <v>4.707355640127314</v>
-      </c>
-      <c r="D23">
-        <v>9.818578276410586</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>s(time):treatmentLH</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>4.237436626924838</v>
-      </c>
-      <c r="C24">
-        <v>4.712572073147745</v>
-      </c>
-      <c r="D24">
-        <v>4.957369093862262</v>
-      </c>
-      <c r="E24">
-        <v>0.001348826517476476</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>s(time):siteEmerald</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>3.491454931381493</v>
-      </c>
-      <c r="C25">
-        <v>4.177390719146416</v>
-      </c>
-      <c r="D25">
-        <v>0.9523680971936778</v>
-      </c>
-      <c r="E25">
-        <v>0.5699965911038032</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>s(time):siteRainbow</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>1.118966158648497</v>
-      </c>
-      <c r="C26">
-        <v>1.644244645221571</v>
-      </c>
-      <c r="D26">
-        <v>1.561059248090922</v>
-      </c>
-      <c r="E26">
-        <v>0.3182973976288117</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>s(time):siteStar</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>1.000002909285121</v>
-      </c>
-      <c r="C27">
-        <v>1.000005268846509</v>
-      </c>
-      <c r="D27">
-        <v>0.4082990159855311</v>
-      </c>
-      <c r="E27">
-        <v>0.5233303666739768</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>s(time):siteMacN</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>1.000007301703944</v>
-      </c>
-      <c r="C28">
-        <v>1.000013299010062</v>
-      </c>
-      <c r="D28">
-        <v>0.02757492996965299</v>
-      </c>
-      <c r="E28">
-        <v>0.8682441408019377</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>141.1383541031473</v>
-      </c>
-      <c r="C29">
-        <v>451</v>
-      </c>
-      <c r="D29">
-        <v>7.648838244423077</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>4.008344643684963</v>
-      </c>
-      <c r="C30">
-        <v>4.959087085963268</v>
-      </c>
-      <c r="D30">
-        <v>0.8160421247309599</v>
-      </c>
-      <c r="E30">
-        <v>0.5579805333359519</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>s(time):treatmentCH</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>7.340995727173136</v>
-      </c>
-      <c r="C31">
-        <v>8.767997094983052</v>
-      </c>
-      <c r="D31">
-        <v>1.445138756754841</v>
-      </c>
-      <c r="E31">
-        <v>0.1301935756368453</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>s(time):treatmentLH</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>3.05776479679749E-05</v>
-      </c>
-      <c r="C32">
-        <v>4.124539769993795E-05</v>
-      </c>
-      <c r="D32">
-        <v>0.0001460227699824172</v>
-      </c>
-      <c r="E32">
-        <v>0.5</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>s(time):siteEmerald</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>7.341516289106171</v>
-      </c>
-      <c r="C33">
-        <v>8.310088074927609</v>
-      </c>
-      <c r="D33">
-        <v>5.350701649478624</v>
-      </c>
-      <c r="E33">
-        <v>1.800113473560128E-06</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>s(time):siteRainbow</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>9.283553362168588E-06</v>
-      </c>
-      <c r="C34">
-        <v>1.332884555695676E-05</v>
-      </c>
-      <c r="D34">
-        <v>0.001029759075854352</v>
-      </c>
-      <c r="E34">
-        <v>0.5</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>s(time):siteStar</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>1.000013681494936</v>
-      </c>
-      <c r="C35">
-        <v>1.000019430587598</v>
-      </c>
-      <c r="D35">
-        <v>1.122348758797891</v>
-      </c>
-      <c r="E35">
-        <v>0.2899843016523977</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>s(time):siteMacN</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>8.117390570266311</v>
-      </c>
-      <c r="C36">
-        <v>9.635773918248049</v>
-      </c>
-      <c r="D36">
-        <v>3.062906944067775</v>
-      </c>
-      <c r="E36">
-        <v>0.001279714407574351</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>230.5705193045784</v>
-      </c>
-      <c r="C37">
-        <v>698</v>
-      </c>
-      <c r="D37">
-        <v>2.917038288214228</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
         <is>
           <t>ssid_heat</t>
         </is>
@@ -2987,7 +2028,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3032,13 +2073,13 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>4.437030204643323</v>
+        <v>4.207660424272711</v>
       </c>
       <c r="D2">
-        <v>1.064707443497011</v>
+        <v>1.099842046264552</v>
       </c>
       <c r="E2">
-        <v>0.9125</v>
+        <v>0.9525</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3049,20 +2090,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>s(time):treatmentCC</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>1.383317805994409</v>
-      </c>
-      <c r="D3">
-        <v>1.064707443497011</v>
-      </c>
-      <c r="E3">
-        <v>0.905</v>
+        <v>13.51044370129423</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3073,20 +2108,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>s(time):treatmentLC</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C4">
-        <v>4.66893761214026</v>
-      </c>
-      <c r="D4">
-        <v>1.064707443497011</v>
-      </c>
-      <c r="E4">
-        <v>0.91</v>
+        <v>9.359525948867519</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3097,20 +2126,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>s(time):treatmentCH</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>318</v>
       </c>
       <c r="C5">
-        <v>3.74831003098071</v>
+        <v>105.7178256969666</v>
       </c>
       <c r="D5">
-        <v>1.064707443497011</v>
+        <v>1.099842046264552</v>
       </c>
       <c r="E5">
-        <v>0.8825</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3121,766 +2150,250 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>s(time):treatmentLH</t>
+          <t>s(time)</t>
         </is>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>1.000017813863155</v>
+        <v>4.216082931460624</v>
       </c>
       <c r="D6">
-        <v>1.064707443497011</v>
+        <v>1.028380681908756</v>
       </c>
       <c r="E6">
-        <v>0.8975</v>
+        <v>0.765</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>s(time):siteEmerald</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>4.494712550142255</v>
-      </c>
-      <c r="D7">
-        <v>1.064707443497011</v>
-      </c>
-      <c r="E7">
-        <v>0.91</v>
+        <v>8.02834592507161</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>s(time):siteRainbow</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C8">
-        <v>2.091194432423091E-06</v>
-      </c>
-      <c r="D8">
-        <v>1.064707443497011</v>
-      </c>
-      <c r="E8">
-        <v>0.905</v>
+        <v>7.331844532540197</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s(time):siteStar</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>742</v>
       </c>
       <c r="C9">
-        <v>1.000002537800571</v>
+        <v>105.6501917237823</v>
       </c>
       <c r="D9">
-        <v>1.064707443497011</v>
+        <v>1.028380681908756</v>
       </c>
       <c r="E9">
-        <v>0.9075</v>
+        <v>0.72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>s(time):siteMacN</t>
+          <t>s(time)</t>
         </is>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10">
-        <v>2.744605638666821</v>
+        <v>4.720206646905807</v>
       </c>
       <c r="D10">
-        <v>1.064707443497011</v>
+        <v>0.9846049942494004</v>
       </c>
       <c r="E10">
-        <v>0.895</v>
+        <v>0.35</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>s(time,exp_unit)</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B11">
-        <v>504</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>159.8130139390948</v>
-      </c>
-      <c r="D11">
-        <v>1.064707443497011</v>
-      </c>
-      <c r="E11">
-        <v>0.875</v>
+        <v>13.54705390654074</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ofav_control</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>s(time)</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B12">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>1.000010018739211</v>
-      </c>
-      <c r="D12">
-        <v>1.065287460024849</v>
-      </c>
-      <c r="E12">
-        <v>0.9350000000000001</v>
+        <v>9.312880779257217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>s(time):treatmentCH</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>474</v>
       </c>
       <c r="C13">
-        <v>6.17247707600399</v>
+        <v>140.8688178919291</v>
       </c>
       <c r="D13">
-        <v>1.065287460024849</v>
+        <v>0.9846049942494004</v>
       </c>
       <c r="E13">
-        <v>0.955</v>
+        <v>0.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_control</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>s(time):treatmentLH</t>
+          <t>s(time)</t>
         </is>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>5.057883339980297</v>
+        <v>9.531246996852431</v>
       </c>
       <c r="D14">
-        <v>1.065287460024849</v>
+        <v>1.0879677294264</v>
       </c>
       <c r="E14">
-        <v>0.95</v>
+        <v>0.985</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>s(time):siteEmerald</t>
+          <t>s(treatment,time)</t>
         </is>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15">
-        <v>2.541523562966276E-05</v>
-      </c>
-      <c r="D15">
-        <v>1.065287460024849</v>
-      </c>
-      <c r="E15">
-        <v>0.96</v>
+        <v>5.862474849613238</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>s(time):siteRainbow</t>
+          <t>s(site,time)</t>
         </is>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C16">
-        <v>1.465684238340331</v>
-      </c>
-      <c r="D16">
-        <v>1.065287460024849</v>
-      </c>
-      <c r="E16">
-        <v>0.9525</v>
+        <v>16.0786169120118</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ofav_heat</t>
+          <t>ssid_heat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>s(time):siteStar</t>
+          <t>s(time,exp_unit)</t>
         </is>
       </c>
       <c r="B17">
-        <v>13</v>
+        <v>1027</v>
       </c>
       <c r="C17">
-        <v>1.000003636133822</v>
+        <v>229.9369333828239</v>
       </c>
       <c r="D17">
-        <v>1.065287460024849</v>
+        <v>1.0879677294264</v>
       </c>
       <c r="E17">
-        <v>0.9475</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>s(time):siteMacN</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>13</v>
-      </c>
-      <c r="C18">
-        <v>2.507994383146582</v>
-      </c>
-      <c r="D18">
-        <v>1.065287460024849</v>
-      </c>
-      <c r="E18">
-        <v>0.92</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>1008</v>
-      </c>
-      <c r="C19">
-        <v>139.7000251804372</v>
-      </c>
-      <c r="D19">
-        <v>1.065287460024849</v>
-      </c>
-      <c r="E19">
-        <v>0.9425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>5</v>
-      </c>
-      <c r="C20">
-        <v>2.801155527955589</v>
-      </c>
-      <c r="D20">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E20">
-        <v>0.2425</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>s(time):treatmentCC</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>5</v>
-      </c>
-      <c r="C21">
-        <v>1.000009400452073</v>
-      </c>
-      <c r="D21">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E21">
-        <v>0.245</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>s(time):treatmentLC</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="C22">
-        <v>3.138566960297332</v>
-      </c>
-      <c r="D22">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E22">
-        <v>0.25</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>s(time):treatmentCH</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>5</v>
-      </c>
-      <c r="C23">
-        <v>4.228792691358922</v>
-      </c>
-      <c r="D23">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E23">
-        <v>0.27</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>s(time):treatmentLH</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>5</v>
-      </c>
-      <c r="C24">
-        <v>4.237436626924838</v>
-      </c>
-      <c r="D24">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E24">
-        <v>0.22</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>s(time):siteEmerald</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25">
-        <v>3.491454931381493</v>
-      </c>
-      <c r="D25">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E25">
-        <v>0.235</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>s(time):siteRainbow</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="C26">
-        <v>1.118966158648497</v>
-      </c>
-      <c r="D26">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E26">
-        <v>0.2375</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>s(time):siteStar</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>5</v>
-      </c>
-      <c r="C27">
-        <v>1.000002909285121</v>
-      </c>
-      <c r="D27">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E27">
-        <v>0.2425</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>s(time):siteMacN</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>5</v>
-      </c>
-      <c r="C28">
-        <v>1.000007301703944</v>
-      </c>
-      <c r="D28">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E28">
-        <v>0.25</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>474</v>
-      </c>
-      <c r="C29">
-        <v>141.1383541031473</v>
-      </c>
-      <c r="D29">
-        <v>0.9681828890394807</v>
-      </c>
-      <c r="E29">
-        <v>0.185</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>12</v>
-      </c>
-      <c r="C30">
-        <v>4.008344643684963</v>
-      </c>
-      <c r="D30">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E30">
-        <v>0.9875</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>s(time):treatmentCH</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>12</v>
-      </c>
-      <c r="C31">
-        <v>7.340995727173136</v>
-      </c>
-      <c r="D31">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E31">
-        <v>0.985</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>s(time):treatmentLH</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>12</v>
-      </c>
-      <c r="C32">
-        <v>3.05776479679749E-05</v>
-      </c>
-      <c r="D32">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E32">
-        <v>0.99</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>s(time):siteEmerald</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>12</v>
-      </c>
-      <c r="C33">
-        <v>7.341516289106171</v>
-      </c>
-      <c r="D33">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E33">
-        <v>0.995</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>s(time):siteRainbow</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>12</v>
-      </c>
-      <c r="C34">
-        <v>9.283553362168588E-06</v>
-      </c>
-      <c r="D34">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E34">
-        <v>0.9725</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>s(time):siteStar</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>12</v>
-      </c>
-      <c r="C35">
-        <v>1.000013681494936</v>
-      </c>
-      <c r="D35">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E35">
-        <v>0.985</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>s(time):siteMacN</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>12</v>
-      </c>
-      <c r="C36">
-        <v>8.117390570266311</v>
-      </c>
-      <c r="D36">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E36">
-        <v>0.9875</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>1027</v>
-      </c>
-      <c r="C37">
-        <v>230.5705193045784</v>
-      </c>
-      <c r="D37">
-        <v>1.08353750439666</v>
-      </c>
-      <c r="E37">
-        <v>0.98</v>
-      </c>
-      <c r="F37" t="inlineStr">
         <is>
           <t>ssid_heat</t>
         </is>
@@ -3950,19 +2463,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.3732175812683861</v>
+        <v>0.3665730521638069</v>
       </c>
       <c r="D2">
-        <v>0.01215248352209591</v>
+        <v>0.01364495147282718</v>
       </c>
       <c r="E2">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F2">
-        <v>0.3492817319084278</v>
+        <v>0.339643424795246</v>
       </c>
       <c r="G2">
-        <v>0.3971534306283444</v>
+        <v>0.3935026795323678</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3982,19 +2495,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.3403617661162668</v>
+        <v>0.3121636622086817</v>
       </c>
       <c r="D3">
-        <v>0.01210862279336495</v>
+        <v>0.01923521569828264</v>
       </c>
       <c r="E3">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F3">
-        <v>0.3165123059946739</v>
+        <v>0.2742011093817117</v>
       </c>
       <c r="G3">
-        <v>0.3642112262378597</v>
+        <v>0.3501262150356518</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4014,19 +2527,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.4013417754722128</v>
+        <v>0.4020564636898675</v>
       </c>
       <c r="D4">
-        <v>0.01210834547179447</v>
+        <v>0.01221398098379734</v>
       </c>
       <c r="E4">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F4">
-        <v>0.3774928615704377</v>
+        <v>0.3779509945546079</v>
       </c>
       <c r="G4">
-        <v>0.4251906893739879</v>
+        <v>0.4261619328251272</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4046,19 +2559,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.4264155762422724</v>
+        <v>0.4363104939371344</v>
       </c>
       <c r="D5">
-        <v>0.01226206148492999</v>
+        <v>0.01575813671493609</v>
       </c>
       <c r="E5">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F5">
-        <v>0.4022638992610054</v>
+        <v>0.4052102917413885</v>
       </c>
       <c r="G5">
-        <v>0.4505672532235395</v>
+        <v>0.4674106961328804</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4078,19 +2591,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.3806387685532792</v>
+        <v>0.4012917272728799</v>
       </c>
       <c r="D6">
-        <v>0.01266983462286476</v>
+        <v>0.01574298109649811</v>
       </c>
       <c r="E6">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F6">
-        <v>0.3556839309353491</v>
+        <v>0.3702214361514157</v>
       </c>
       <c r="G6">
-        <v>0.4055936061712093</v>
+        <v>0.4323620183943441</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4110,19 +2623,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.377468240524308</v>
+        <v>0.397917137903146</v>
       </c>
       <c r="D7">
-        <v>0.01211812589292278</v>
+        <v>0.02713063993232011</v>
       </c>
       <c r="E7">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F7">
-        <v>0.3536000628492986</v>
+        <v>0.3443722040788708</v>
       </c>
       <c r="G7">
-        <v>0.4013364181993174</v>
+        <v>0.4514620717274213</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4142,19 +2655,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.4045179784499064</v>
+        <v>0.4052087160034729</v>
       </c>
       <c r="D8">
-        <v>0.01211100592507629</v>
+        <v>0.01223353319739301</v>
       </c>
       <c r="E8">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F8">
-        <v>0.3806638244497706</v>
+        <v>0.381064658689471</v>
       </c>
       <c r="G8">
-        <v>0.4283721324500422</v>
+        <v>0.4293527733174747</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -4174,19 +2687,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.4433883676605646</v>
+        <v>0.4326641002608501</v>
       </c>
       <c r="D9">
-        <v>0.01295474254447819</v>
+        <v>0.02714156558737854</v>
       </c>
       <c r="E9">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F9">
-        <v>0.4178723679492403</v>
+        <v>0.3790976036028728</v>
       </c>
       <c r="G9">
-        <v>0.4689043673718888</v>
+        <v>0.4862305969188274</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4206,19 +2719,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.463886992323507</v>
+        <v>0.4646400935718331</v>
       </c>
       <c r="D10">
-        <v>0.01220322141461767</v>
+        <v>0.01573102457111733</v>
       </c>
       <c r="E10">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F10">
-        <v>0.4398512082835276</v>
+        <v>0.4335933998060478</v>
       </c>
       <c r="G10">
-        <v>0.4879227763634864</v>
+        <v>0.4956867873376183</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -4238,19 +2751,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.4242603501160651</v>
+        <v>0.4352620128419505</v>
       </c>
       <c r="D11">
-        <v>0.01211310050305596</v>
+        <v>0.01366368229197315</v>
       </c>
       <c r="E11">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F11">
-        <v>0.4004020705803626</v>
+        <v>0.4082954183957923</v>
       </c>
       <c r="G11">
-        <v>0.4481186296517676</v>
+        <v>0.4622286072881088</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -4270,19 +2783,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.4881959385654253</v>
+        <v>0.4874344257875612</v>
       </c>
       <c r="D12">
-        <v>0.01211287961042076</v>
+        <v>0.01221935874639622</v>
       </c>
       <c r="E12">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F12">
-        <v>0.4643380941056339</v>
+        <v>0.4633183431192924</v>
       </c>
       <c r="G12">
-        <v>0.5120537830252166</v>
+        <v>0.5115505084558299</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -4302,19 +2815,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.50403392932306</v>
+        <v>0.5188595389788935</v>
       </c>
       <c r="D13">
-        <v>0.01429861918722489</v>
+        <v>0.02713246510852358</v>
       </c>
       <c r="E13">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F13">
-        <v>0.4758709950307782</v>
+        <v>0.4653110029933984</v>
       </c>
       <c r="G13">
-        <v>0.5321968636153418</v>
+        <v>0.5724080749643885</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -4334,19 +2847,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.4724520625006397</v>
+        <v>0.4711864155359914</v>
       </c>
       <c r="D14">
-        <v>0.0114977997635647</v>
+        <v>0.01364003961112355</v>
       </c>
       <c r="E14">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F14">
-        <v>0.4498056953929406</v>
+        <v>0.444266482200101</v>
       </c>
       <c r="G14">
-        <v>0.4950984296083388</v>
+        <v>0.4981063488718818</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -4366,19 +2879,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.4398806174687424</v>
+        <v>0.4366802732150084</v>
       </c>
       <c r="D15">
-        <v>0.01110660351299358</v>
+        <v>0.01574098081586387</v>
       </c>
       <c r="E15">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F15">
-        <v>0.4180047607268318</v>
+        <v>0.4056139298402416</v>
       </c>
       <c r="G15">
-        <v>0.4617564742106529</v>
+        <v>0.4677466165897752</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -4398,19 +2911,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.4850393170692853</v>
+        <v>0.4845003287659163</v>
       </c>
       <c r="D16">
-        <v>0.01106828999741064</v>
+        <v>0.01115837000767827</v>
       </c>
       <c r="E16">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F16">
-        <v>0.4632389236296518</v>
+        <v>0.4624782096733197</v>
       </c>
       <c r="G16">
-        <v>0.5068397105089189</v>
+        <v>0.506522447858513</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -4430,19 +2943,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.5047644292139591</v>
+        <v>0.517792737427395</v>
       </c>
       <c r="D17">
-        <v>0.01160852986639891</v>
+        <v>0.01575565594741532</v>
       </c>
       <c r="E17">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F17">
-        <v>0.4818999651998759</v>
+        <v>0.4866974312655451</v>
       </c>
       <c r="G17">
-        <v>0.5276288932280423</v>
+        <v>0.5488880435892448</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -4462,19 +2975,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.3345443091112434</v>
+        <v>0.3367989225353282</v>
       </c>
       <c r="D18">
-        <v>0.01828529442135339</v>
+        <v>0.01638760608019421</v>
       </c>
       <c r="E18">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F18">
-        <v>0.2986065070221351</v>
+        <v>0.3045853507338358</v>
       </c>
       <c r="G18">
-        <v>0.3704821112003517</v>
+        <v>0.3690124943368207</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -4494,19 +3007,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.3207945540118847</v>
+        <v>0.3262052650837182</v>
       </c>
       <c r="D19">
-        <v>0.02065822670073463</v>
+        <v>0.02303255497783277</v>
       </c>
       <c r="E19">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F19">
-        <v>0.2801930058182743</v>
+        <v>0.2809295329286136</v>
       </c>
       <c r="G19">
-        <v>0.361396102205495</v>
+        <v>0.3714809972388229</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4526,19 +3039,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.3356101593833198</v>
+        <v>0.3412797396629584</v>
       </c>
       <c r="D20">
-        <v>0.01960456981767319</v>
+        <v>0.01773425540512467</v>
       </c>
       <c r="E20">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F20">
-        <v>0.2970794617683619</v>
+        <v>0.306419021932537</v>
       </c>
       <c r="G20">
-        <v>0.3741408569982778</v>
+        <v>0.3761404573933799</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4558,19 +3071,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.3594473472787949</v>
+        <v>0.3584663042422886</v>
       </c>
       <c r="D21">
-        <v>0.02366868128322254</v>
+        <v>0.03346085470063172</v>
       </c>
       <c r="E21">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F21">
-        <v>0.3129290706754217</v>
+        <v>0.29269137408084</v>
       </c>
       <c r="G21">
-        <v>0.4059656238821681</v>
+        <v>0.4242412344037373</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4590,19 +3103,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.4205375222574575</v>
+        <v>0.4199079561315421</v>
       </c>
       <c r="D22">
-        <v>0.01890777026537066</v>
+        <v>0.01690700797785272</v>
       </c>
       <c r="E22">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F22">
-        <v>0.3833763100786862</v>
+        <v>0.3866733816135958</v>
       </c>
       <c r="G22">
-        <v>0.4576987344362288</v>
+        <v>0.4531425306494883</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -4622,19 +3135,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.3884434812309747</v>
+        <v>0.3729364576025348</v>
       </c>
       <c r="D23">
-        <v>0.0195193272895778</v>
+        <v>0.02127847384703887</v>
       </c>
       <c r="E23">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F23">
-        <v>0.350080318741986</v>
+        <v>0.3311087713777484</v>
       </c>
       <c r="G23">
-        <v>0.4268066437199633</v>
+        <v>0.4147641438273212</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4654,19 +3167,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.4163521335917623</v>
+        <v>0.4181583356191542</v>
       </c>
       <c r="D24">
-        <v>0.01687042618500841</v>
+        <v>0.01499174359564734</v>
       </c>
       <c r="E24">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F24">
-        <v>0.3831951045921238</v>
+        <v>0.388688649419434</v>
       </c>
       <c r="G24">
-        <v>0.4495091625914008</v>
+        <v>0.4476280218188743</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -4686,19 +3199,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.4070682112508894</v>
+        <v>0.4016821772791432</v>
       </c>
       <c r="D25">
-        <v>0.01812660112940791</v>
+        <v>0.01930854452164758</v>
       </c>
       <c r="E25">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F25">
-        <v>0.3714423039547982</v>
+        <v>0.3637268357676003</v>
       </c>
       <c r="G25">
-        <v>0.4426941185469805</v>
+        <v>0.4396375187906861</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4718,19 +3231,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.4025334175913299</v>
+        <v>0.402470893004288</v>
       </c>
       <c r="D26">
-        <v>0.01606948668204964</v>
+        <v>0.01606906481818463</v>
       </c>
       <c r="E26">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F26">
-        <v>0.370907986942467</v>
+        <v>0.3708466038482756</v>
       </c>
       <c r="G26">
-        <v>0.4341588482401928</v>
+        <v>0.4340951821603005</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4750,19 +3263,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.3698812534817219</v>
+        <v>0.3698358055708036</v>
       </c>
       <c r="D27">
-        <v>0.01606946975786758</v>
+        <v>0.01606874012350826</v>
       </c>
       <c r="E27">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F27">
-        <v>0.3382558561403664</v>
+        <v>0.3382121554213824</v>
       </c>
       <c r="G27">
-        <v>0.4015066508230775</v>
+        <v>0.4014594557202249</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4782,19 +3295,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.2660094812738468</v>
+        <v>0.2660489537552564</v>
       </c>
       <c r="D28">
-        <v>0.01606947613996428</v>
+        <v>0.01606891595927942</v>
       </c>
       <c r="E28">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F28">
-        <v>0.2343840713722546</v>
+        <v>0.2344249575569932</v>
       </c>
       <c r="G28">
-        <v>0.2976348911754391</v>
+        <v>0.2976729499535196</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4814,19 +3327,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.2911838651333893</v>
+        <v>0.2912367176056637</v>
       </c>
       <c r="D29">
-        <v>0.01606947673813314</v>
+        <v>0.01606888433723217</v>
       </c>
       <c r="E29">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F29">
-        <v>0.2595584540545754</v>
+        <v>0.2596127836403168</v>
       </c>
       <c r="G29">
-        <v>0.3228092762122032</v>
+        <v>0.3228606515710106</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4846,19 +3359,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.3700086048729745</v>
+        <v>0.3699460143145461</v>
       </c>
       <c r="D30">
-        <v>0.0160691522517243</v>
+        <v>0.01606888582118523</v>
       </c>
       <c r="E30">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F30">
-        <v>0.3383838323971616</v>
+        <v>0.3383220774287454</v>
       </c>
       <c r="G30">
-        <v>0.4016333773487874</v>
+        <v>0.4015699512003468</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4878,19 +3391,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.323764859891623</v>
+        <v>0.3237203436049136</v>
       </c>
       <c r="D31">
-        <v>0.01606918401815179</v>
+        <v>0.01606854385898031</v>
       </c>
       <c r="E31">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F31">
-        <v>0.2921400248981348</v>
+        <v>0.2920970797085975</v>
       </c>
       <c r="G31">
-        <v>0.3553896948851111</v>
+        <v>0.3553436075012298</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4910,19 +3423,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.2831173897426095</v>
+        <v>0.2831546995968182</v>
       </c>
       <c r="D32">
-        <v>0.01606919112499654</v>
+        <v>0.0160687185912937</v>
       </c>
       <c r="E32">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F32">
-        <v>0.2514925407625497</v>
+        <v>0.2515310918232904</v>
       </c>
       <c r="G32">
-        <v>0.3147422387226693</v>
+        <v>0.314778307370346</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4942,19 +3455,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.2956792827887463</v>
+        <v>0.2957324072984184</v>
       </c>
       <c r="D33">
-        <v>0.01606919179158742</v>
+        <v>0.01606868723200669</v>
       </c>
       <c r="E33">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F33">
-        <v>0.2640544324968075</v>
+        <v>0.2641088612406888</v>
       </c>
       <c r="G33">
-        <v>0.3273041330806852</v>
+        <v>0.3273559533561481</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4974,19 +3487,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.3798840641366767</v>
+        <v>0.3797006272873088</v>
       </c>
       <c r="D34">
-        <v>0.01606855226231776</v>
+        <v>0.01606824014577677</v>
       </c>
       <c r="E34">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F34">
-        <v>0.3482604724654372</v>
+        <v>0.3480779611055628</v>
       </c>
       <c r="G34">
-        <v>0.4115076558079162</v>
+        <v>0.4113232934690548</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -5006,19 +3519,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.3645379876570764</v>
+        <v>0.3643742748336262</v>
       </c>
       <c r="D35">
-        <v>0.01606869715734219</v>
+        <v>0.0160678691220936</v>
       </c>
       <c r="E35">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F35">
-        <v>0.3329141108262896</v>
+        <v>0.3327523388350223</v>
       </c>
       <c r="G35">
-        <v>0.3961618644878632</v>
+        <v>0.3959962108322301</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5038,19 +3551,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.3119996874503258</v>
+        <v>0.3119148357847731</v>
       </c>
       <c r="D36">
-        <v>0.01606870478898676</v>
+        <v>0.01606804248910682</v>
       </c>
       <c r="E36">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F36">
-        <v>0.2803757956001392</v>
+        <v>0.2802925585958996</v>
       </c>
       <c r="G36">
-        <v>0.3436235793005124</v>
+        <v>0.3435371129736465</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -5070,19 +3583,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.3126539999909358</v>
+        <v>0.3125853102674582</v>
       </c>
       <c r="D37">
-        <v>0.01606870550445572</v>
+        <v>0.01606801136157558</v>
       </c>
       <c r="E37">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F37">
-        <v>0.2810301067326759</v>
+        <v>0.2809630943382823</v>
       </c>
       <c r="G37">
-        <v>0.3442778932491957</v>
+        <v>0.3442075261966342</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -5102,19 +3615,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.3834524226346734</v>
+        <v>0.3834476660431597</v>
       </c>
       <c r="D38">
-        <v>0.01796275864061999</v>
+        <v>0.01796319062757011</v>
       </c>
       <c r="E38">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F38">
-        <v>0.3481009525540664</v>
+        <v>0.3480956937287542</v>
       </c>
       <c r="G38">
-        <v>0.4188038927152804</v>
+        <v>0.4187996383575652</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5134,19 +3647,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.3439580758483202</v>
+        <v>0.3439690021045975</v>
       </c>
       <c r="D39">
-        <v>0.01606890787243427</v>
+        <v>0.01606889992634195</v>
       </c>
       <c r="E39">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F39">
-        <v>0.3123337843213043</v>
+        <v>0.312345037459524</v>
       </c>
       <c r="G39">
-        <v>0.3755823673753361</v>
+        <v>0.375592966749671</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5166,19 +3679,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.2978588197560455</v>
+        <v>0.2979529736895765</v>
       </c>
       <c r="D40">
-        <v>0.01606891550397321</v>
+        <v>0.01606906943153954</v>
       </c>
       <c r="E40">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F40">
-        <v>0.2662345132098376</v>
+        <v>0.2663286754543754</v>
       </c>
       <c r="G40">
-        <v>0.3294831263022534</v>
+        <v>0.3295772719247775</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5198,19 +3711,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.2900572847710853</v>
+        <v>0.2901620183709516</v>
       </c>
       <c r="D41">
-        <v>0.01606891621943225</v>
+        <v>0.01606903903526346</v>
       </c>
       <c r="E41">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F41">
-        <v>0.2584329768168238</v>
+        <v>0.258537779956321</v>
       </c>
       <c r="G41">
-        <v>0.3216815927253469</v>
+        <v>0.3217862567855822</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5230,19 +3743,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.2968574572989477</v>
+        <v>0.2963342328935919</v>
       </c>
       <c r="D42">
-        <v>0.02311028399607272</v>
+        <v>0.01866933348619772</v>
       </c>
       <c r="E42">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F42">
-        <v>0.2514384977066959</v>
+        <v>0.2596433524345355</v>
       </c>
       <c r="G42">
-        <v>0.3422764168911996</v>
+        <v>0.3330251133526483</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5262,19 +3775,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.3060104127395203</v>
+        <v>0.3051275359617394</v>
       </c>
       <c r="D43">
-        <v>0.02297076245696961</v>
+        <v>0.01891152683228938</v>
       </c>
       <c r="E43">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F43">
-        <v>0.2608656567506448</v>
+        <v>0.2679606724090178</v>
       </c>
       <c r="G43">
-        <v>0.3511551687283959</v>
+        <v>0.3422943995144611</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5294,19 +3807,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.2997259361485174</v>
+        <v>0.3008403684186131</v>
       </c>
       <c r="D44">
-        <v>0.01573980216509912</v>
+        <v>0.01955066189912776</v>
       </c>
       <c r="E44">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F44">
-        <v>0.2687922860623411</v>
+        <v>0.2624174113716113</v>
       </c>
       <c r="G44">
-        <v>0.3306595862346937</v>
+        <v>0.3392633254656148</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5326,19 +3839,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.285614466161458</v>
+        <v>0.2857453849798605</v>
       </c>
       <c r="D45">
-        <v>0.01524420609786027</v>
+        <v>0.01984138648754461</v>
       </c>
       <c r="E45">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F45">
-        <v>0.255654817855434</v>
+        <v>0.2467510662863384</v>
       </c>
       <c r="G45">
-        <v>0.3155741144674821</v>
+        <v>0.3247397036733825</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5358,19 +3871,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.3034023236333847</v>
+        <v>0.3044814739051422</v>
       </c>
       <c r="D46">
-        <v>0.01491284158448591</v>
+        <v>0.01447093960914838</v>
       </c>
       <c r="E46">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F46">
-        <v>0.2740939105716274</v>
+        <v>0.2760417057836921</v>
       </c>
       <c r="G46">
-        <v>0.332710736695142</v>
+        <v>0.3329212420265924</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5390,19 +3903,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.2847012704630619</v>
+        <v>0.2848478685649779</v>
       </c>
       <c r="D47">
-        <v>0.0140241218223688</v>
+        <v>0.01441171016866943</v>
       </c>
       <c r="E47">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F47">
-        <v>0.2571394705961615</v>
+        <v>0.2565245041877683</v>
       </c>
       <c r="G47">
-        <v>0.3122630703299622</v>
+        <v>0.3131712329421875</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5422,19 +3935,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.3227497500864411</v>
+        <v>0.3247549629317223</v>
       </c>
       <c r="D48">
-        <v>0.01567366373508314</v>
+        <v>0.01529766435969087</v>
       </c>
       <c r="E48">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F48">
-        <v>0.2919460827681486</v>
+        <v>0.2946904309151324</v>
       </c>
       <c r="G48">
-        <v>0.3535534174047337</v>
+        <v>0.3548194949483122</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5454,19 +3967,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.2946357119359247</v>
+        <v>0.2961518116056378</v>
       </c>
       <c r="D49">
-        <v>0.01514431202541271</v>
+        <v>0.01482381688424712</v>
       </c>
       <c r="E49">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F49">
-        <v>0.2648723868270009</v>
+        <v>0.2670185330315013</v>
       </c>
       <c r="G49">
-        <v>0.3243990370448486</v>
+        <v>0.3252850901797743</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5538,19 +4051,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.03285581515211929</v>
+        <v>0.05440938995512517</v>
       </c>
       <c r="D2">
-        <v>0.01704040319790176</v>
+        <v>0.0235107692320147</v>
       </c>
       <c r="E2">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F2">
-        <v>1.928112543496913</v>
+        <v>2.314232657306496</v>
       </c>
       <c r="G2">
-        <v>0.2189537069517459</v>
+        <v>0.0986935555891314</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -5570,19 +4083,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.02812419420382665</v>
+        <v>-0.03548341152606062</v>
       </c>
       <c r="D3">
-        <v>0.01703990916726058</v>
+        <v>0.0182228331565316</v>
       </c>
       <c r="E3">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F3">
-        <v>-1.650489678540231</v>
+        <v>-1.947195105243133</v>
       </c>
       <c r="G3">
-        <v>0.3523842813578689</v>
+        <v>0.2123444027321342</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -5602,19 +4115,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.05319799497388642</v>
+        <v>-0.06973744177332745</v>
       </c>
       <c r="D4">
-        <v>0.01714486306712741</v>
+        <v>0.02078025364852481</v>
       </c>
       <c r="E4">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F4">
-        <v>-3.102853301633259</v>
+        <v>-3.355947571808302</v>
       </c>
       <c r="G4">
-        <v>0.01142599094437158</v>
+        <v>0.005315830178123204</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5634,19 +4147,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.06098000935594595</v>
+        <v>-0.08989280148118579</v>
       </c>
       <c r="D5">
-        <v>0.01701069925300079</v>
+        <v>0.0227050991554648</v>
       </c>
       <c r="E5">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F5">
-        <v>-3.584803214082378</v>
+        <v>-3.959145955086035</v>
       </c>
       <c r="G5">
-        <v>0.002285422953939742</v>
+        <v>0.0006272526626379671</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -5666,19 +4179,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.08605381012600571</v>
+        <v>-0.1241468317284526</v>
       </c>
       <c r="D6">
-        <v>0.01711747012047012</v>
+        <v>0.02480603689949007</v>
       </c>
       <c r="E6">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F6">
-        <v>-5.027250494399713</v>
+        <v>-5.004702372711727</v>
       </c>
       <c r="G6">
-        <v>5.69062427868694E-06</v>
+        <v>8.033235088356072E-06</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -5698,19 +4211,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.02507380077005976</v>
+        <v>-0.03425403024726684</v>
       </c>
       <c r="D7">
-        <v>0.01711689887530077</v>
+        <v>0.01986580637393108</v>
       </c>
       <c r="E7">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F7">
-        <v>-1.464856511259793</v>
+        <v>-1.724270820046687</v>
       </c>
       <c r="G7">
-        <v>0.4603736474920216</v>
+        <v>0.3142139912294466</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -5730,19 +4243,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.003170528028971202</v>
+        <v>0.003374589369733838</v>
       </c>
       <c r="D8">
-        <v>0.01737912003652278</v>
+        <v>0.03128077048562437</v>
       </c>
       <c r="E8">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F8">
-        <v>0.182433173964403</v>
+        <v>0.1078806345669999</v>
       </c>
       <c r="G8">
-        <v>0.9978399942868967</v>
+        <v>0.9995491201527231</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5762,19 +4275,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.0238792098966272</v>
+        <v>-0.00391698873059303</v>
       </c>
       <c r="D9">
-        <v>0.01737514755348094</v>
+        <v>0.019821459763343</v>
       </c>
       <c r="E9">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F9">
-        <v>-1.37433134441746</v>
+        <v>-0.1976135348939815</v>
       </c>
       <c r="G9">
-        <v>0.5166577856943719</v>
+        <v>0.9972574818184093</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -5794,19 +4307,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.06274959910728539</v>
+        <v>-0.03137237298797024</v>
       </c>
       <c r="D10">
-        <v>0.01788956343976646</v>
+        <v>0.03129195602368702</v>
       </c>
       <c r="E10">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F10">
-        <v>-3.507609300727831</v>
+        <v>-1.002569892537953</v>
       </c>
       <c r="G10">
-        <v>0.003000012767053528</v>
+        <v>0.7480994547057815</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5826,19 +4339,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.0270497379255984</v>
+        <v>-0.007291578100326854</v>
       </c>
       <c r="D11">
-        <v>0.01701465539391158</v>
+        <v>0.02967209532631139</v>
       </c>
       <c r="E11">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F11">
-        <v>-1.589790524660153</v>
+        <v>-0.2457385641337277</v>
       </c>
       <c r="G11">
-        <v>0.3863192953919052</v>
+        <v>0.9947688115713444</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5858,19 +4371,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.06592012713625658</v>
+        <v>-0.03474696235770407</v>
       </c>
       <c r="D12">
-        <v>0.01757133254880278</v>
+        <v>0.03829882676069045</v>
       </c>
       <c r="E12">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F12">
-        <v>-3.751572452070406</v>
+        <v>-0.9072591851134202</v>
       </c>
       <c r="G12">
-        <v>0.001247051241080044</v>
+        <v>0.8009972900921367</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5890,19 +4403,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.0388703892106582</v>
+        <v>-0.02745538425737721</v>
       </c>
       <c r="D13">
-        <v>0.01756771459402441</v>
+        <v>0.02968499981604879</v>
       </c>
       <c r="E13">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F13">
-        <v>-2.212603637349607</v>
+        <v>-0.9248908346812192</v>
       </c>
       <c r="G13">
-        <v>0.1226497487509502</v>
+        <v>0.791564211968576</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -5922,19 +4435,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.03962664220744186</v>
+        <v>0.02937808072988256</v>
       </c>
       <c r="D14">
-        <v>0.01706819526270827</v>
+        <v>0.02076340608096307</v>
       </c>
       <c r="E14">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F14">
-        <v>2.321665624134309</v>
+        <v>1.414896988255595</v>
       </c>
       <c r="G14">
-        <v>0.09589511125327643</v>
+        <v>0.4917552814295918</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -5954,19 +4467,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.02430894624191824</v>
+        <v>-0.02279433221572821</v>
       </c>
       <c r="D15">
-        <v>0.01706767662974674</v>
+        <v>0.01982145976334298</v>
       </c>
       <c r="E15">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F15">
-        <v>-1.424268034206302</v>
+        <v>-1.149982518335161</v>
       </c>
       <c r="G15">
-        <v>0.485401574949336</v>
+        <v>0.6590893796954271</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -5986,19 +4499,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.04014693699955289</v>
+        <v>-0.05421944540706035</v>
       </c>
       <c r="D16">
-        <v>0.01852811226716494</v>
+        <v>0.03129195602368701</v>
       </c>
       <c r="E16">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F16">
-        <v>-2.166812054064477</v>
+        <v>-1.732695947994365</v>
       </c>
       <c r="G16">
-        <v>0.1354698072124252</v>
+        <v>0.3099167191990029</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -6018,19 +4531,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.06393558844936012</v>
+        <v>-0.05217241294561077</v>
       </c>
       <c r="D17">
-        <v>0.01701069925300076</v>
+        <v>0.01825008687547478</v>
       </c>
       <c r="E17">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F17">
-        <v>-3.758551456259601</v>
+        <v>-2.858748744682537</v>
       </c>
       <c r="G17">
-        <v>0.001215191508504465</v>
+        <v>0.02441420064682553</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -6050,19 +4563,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.07977357920699474</v>
+        <v>-0.08359752613694291</v>
       </c>
       <c r="D18">
-        <v>0.01849256168114715</v>
+        <v>0.03032214638105366</v>
       </c>
       <c r="E18">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F18">
-        <v>-4.313819825639545</v>
+        <v>-2.75697917576104</v>
       </c>
       <c r="G18">
-        <v>0.0001359181126431297</v>
+        <v>0.03241808704742188</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -6082,19 +4595,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.01583799075763464</v>
+        <v>-0.03142511319133216</v>
       </c>
       <c r="D19">
-        <v>0.01849165034613318</v>
+        <v>0.0296849998160488</v>
       </c>
       <c r="E19">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F19">
-        <v>-0.8564941722979609</v>
+        <v>-1.058619281996511</v>
       </c>
       <c r="G19">
-        <v>0.8271637434240284</v>
+        <v>0.7150856145334255</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -6114,19 +4627,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.0325714450318973</v>
+        <v>0.03450614232098301</v>
       </c>
       <c r="D20">
-        <v>0.01585599065702707</v>
+        <v>0.02076340608096308</v>
       </c>
       <c r="E20">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F20">
-        <v>2.054204353195823</v>
+        <v>1.66187292135176</v>
       </c>
       <c r="G20">
-        <v>0.1712757145592638</v>
+        <v>0.3470568761786492</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -6146,19 +4659,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.01258725456864562</v>
+        <v>-0.01331391322992502</v>
       </c>
       <c r="D21">
-        <v>0.01583577433426332</v>
+        <v>0.0175426395018302</v>
       </c>
       <c r="E21">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F21">
-        <v>-0.7948619564128931</v>
+        <v>-0.7589458375711362</v>
       </c>
       <c r="G21">
-        <v>0.8567338351606575</v>
+        <v>0.8727202219933931</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -6178,19 +4691,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.03231236671331923</v>
+        <v>-0.04660632189140367</v>
       </c>
       <c r="D22">
-        <v>0.01617764004468977</v>
+        <v>0.02078025364852485</v>
       </c>
       <c r="E22">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F22">
-        <v>-1.997347364885004</v>
+        <v>-2.242817757651007</v>
       </c>
       <c r="G22">
-        <v>0.1917624936946285</v>
+        <v>0.1158816585500652</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -6210,19 +4723,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>-0.04515869960054293</v>
+        <v>-0.04782005555090803</v>
       </c>
       <c r="D23">
-        <v>0.01557638694358613</v>
+        <v>0.01922386127451504</v>
       </c>
       <c r="E23">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F23">
-        <v>-2.899176796525196</v>
+        <v>-2.487536445880557</v>
       </c>
       <c r="G23">
-        <v>0.0211157967482144</v>
+        <v>0.06537091677783846</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -6242,19 +4755,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.06488381174521651</v>
+        <v>-0.08111246421238667</v>
       </c>
       <c r="D24">
-        <v>0.0159379591820584</v>
+        <v>0.02221941108267246</v>
       </c>
       <c r="E24">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F24">
-        <v>-4.071023837120701</v>
+        <v>-3.650522685348814</v>
       </c>
       <c r="G24">
-        <v>0.0003655385151628554</v>
+        <v>0.001943464326468081</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -6274,19 +4787,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.0197251121446736</v>
+        <v>-0.03329240866147865</v>
       </c>
       <c r="D25">
-        <v>0.01591719466093115</v>
+        <v>0.01924377341705381</v>
       </c>
       <c r="E25">
-        <v>246.7100497754794</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="F25">
-        <v>-1.239232953096252</v>
+        <v>-1.73003536988099</v>
       </c>
       <c r="G25">
-        <v>0.6025114420471054</v>
+        <v>0.3112701427935981</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -6306,19 +4819,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.01374975509935885</v>
+        <v>0.01059365745160979</v>
       </c>
       <c r="D26">
-        <v>0.02627717400900048</v>
+        <v>0.02813563210891611</v>
       </c>
       <c r="E26">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F26">
-        <v>0.5232585168652183</v>
+        <v>0.3765210396055997</v>
       </c>
       <c r="G26">
-        <v>0.6010589199947798</v>
+        <v>0.7067230422449726</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -6338,19 +4851,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.02383718789547499</v>
+        <v>-0.01718656457933054</v>
       </c>
       <c r="D27">
-        <v>0.02870964398437053</v>
+        <v>0.03773850557017652</v>
       </c>
       <c r="E27">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F27">
-        <v>-0.8302850397048428</v>
+        <v>-0.4554119014429789</v>
       </c>
       <c r="G27">
-        <v>0.4068298678469544</v>
+        <v>0.649052393320648</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -6370,19 +4883,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.03209404102648289</v>
+        <v>0.04697149852900695</v>
       </c>
       <c r="D28">
-        <v>0.02619232110419312</v>
+        <v>0.02719471070811484</v>
       </c>
       <c r="E28">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F28">
-        <v>1.225322524827514</v>
+        <v>1.727229203986007</v>
       </c>
       <c r="G28">
-        <v>0.2211120680440994</v>
+        <v>0.08487456698039654</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -6402,19 +4915,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.009283922340873</v>
+        <v>0.0164761583400107</v>
       </c>
       <c r="D29">
-        <v>0.02416278051921781</v>
+        <v>0.02444753154677232</v>
       </c>
       <c r="E29">
-        <v>438.0958967119831</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="F29">
-        <v>0.3842240893381064</v>
+        <v>0.6739395471681462</v>
       </c>
       <c r="G29">
-        <v>0.7009987884158191</v>
+        <v>0.5007269643254115</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -6434,19 +4947,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.032652164109608</v>
+        <v>0.03263508743348437</v>
       </c>
       <c r="D30">
-        <v>0.02271606794669441</v>
+        <v>0.02271548198499839</v>
       </c>
       <c r="E30">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F30">
-        <v>1.437403875804107</v>
+        <v>1.436689190880344</v>
       </c>
       <c r="G30">
-        <v>0.4770371353325439</v>
+        <v>0.4774768097578665</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -6466,19 +4979,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.1365239363174831</v>
+        <v>0.1364219392490316</v>
       </c>
       <c r="D31">
-        <v>0.02271607859286344</v>
+        <v>0.02271572214848875</v>
       </c>
       <c r="E31">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F31">
-        <v>6.010013381463381</v>
+        <v>6.005617534730569</v>
       </c>
       <c r="G31">
-        <v>3.273610404974647E-08</v>
+        <v>3.345578913904745E-08</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -6498,19 +5011,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.1113495524579406</v>
+        <v>0.1112341753986244</v>
       </c>
       <c r="D32">
-        <v>0.02271607958371251</v>
+        <v>0.02271567354533249</v>
       </c>
       <c r="E32">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F32">
-        <v>4.901794433656523</v>
+        <v>4.896802869465445</v>
       </c>
       <c r="G32">
-        <v>9.326967939427E-06</v>
+        <v>9.537114186053408E-06</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -6530,19 +5043,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.1038717722078751</v>
+        <v>0.1037868518155473</v>
       </c>
       <c r="D33">
-        <v>0.02271601630760882</v>
+        <v>0.02271524293360293</v>
       </c>
       <c r="E33">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F33">
-        <v>4.572622716998264</v>
+        <v>4.569039922615757</v>
       </c>
       <c r="G33">
-        <v>4.188748403699538E-05</v>
+        <v>4.252079208466597E-05</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -6562,19 +5075,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.07869738834833256</v>
+        <v>0.07859908796514004</v>
       </c>
       <c r="D34">
-        <v>0.02271601682080321</v>
+        <v>0.02271520216191992</v>
       </c>
       <c r="E34">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F34">
-        <v>3.46440086609999</v>
+        <v>3.460197598280884</v>
       </c>
       <c r="G34">
-        <v>0.003400800115460401</v>
+        <v>0.003449824051649175</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -6594,19 +5107,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.02517438385954255</v>
+        <v>-0.0251877638504072</v>
       </c>
       <c r="D35">
-        <v>0.02271602224153445</v>
+        <v>0.02271545839107505</v>
       </c>
       <c r="E35">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F35">
-        <v>-1.108221483139473</v>
+        <v>-1.10883801756356</v>
       </c>
       <c r="G35">
-        <v>0.6847595271780393</v>
+        <v>0.6843790857534888</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -6626,19 +5139,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.04624374498135156</v>
+        <v>0.04622567070963246</v>
       </c>
       <c r="D36">
-        <v>0.02271606794669435</v>
+        <v>0.02271548198499833</v>
       </c>
       <c r="E36">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F36">
-        <v>2.035728414348266</v>
+        <v>2.034985246633139</v>
       </c>
       <c r="G36">
-        <v>0.177283096246857</v>
+        <v>0.1775415677790988</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -6658,19 +5171,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.08689121513036502</v>
+        <v>0.08679131471772787</v>
       </c>
       <c r="D37">
-        <v>0.02271607859286329</v>
+        <v>0.02271572214848864</v>
       </c>
       <c r="E37">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F37">
-        <v>3.825097486573392</v>
+        <v>3.820759654938042</v>
       </c>
       <c r="G37">
-        <v>0.0009139096716971329</v>
+        <v>0.0009287000840744186</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -6690,19 +5203,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.07432932208422817</v>
+        <v>0.07421360701612767</v>
       </c>
       <c r="D38">
-        <v>0.02271607958371241</v>
+        <v>0.02271567354533236</v>
       </c>
       <c r="E38">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F38">
-        <v>3.272101676273524</v>
+        <v>3.267066101651084</v>
       </c>
       <c r="G38">
-        <v>0.006524982254416889</v>
+        <v>0.006632572196977549</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -6722,19 +5235,19 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.04064747014901345</v>
+        <v>0.04056564400809542</v>
       </c>
       <c r="D39">
-        <v>0.0227160163076088</v>
+        <v>0.02271524293360292</v>
       </c>
       <c r="E39">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F39">
-        <v>1.789374932584392</v>
+        <v>1.78583359758333</v>
       </c>
       <c r="G39">
-        <v>0.2804771036216859</v>
+        <v>0.282182173997383</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -6754,19 +5267,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.02808557710287658</v>
+        <v>0.02798793630649522</v>
       </c>
       <c r="D40">
-        <v>0.02271601682080321</v>
+        <v>0.02271520216191992</v>
       </c>
       <c r="E40">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F40">
-        <v>1.236377720813975</v>
+        <v>1.232123584328675</v>
       </c>
       <c r="G40">
-        <v>0.6042145163386584</v>
+        <v>0.60692133771099</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -6786,19 +5299,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.01256189304613687</v>
+        <v>-0.01257770770160017</v>
       </c>
       <c r="D41">
-        <v>0.02271602224153442</v>
+        <v>0.02271545839107499</v>
       </c>
       <c r="E41">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F41">
-        <v>-0.552997039383438</v>
+        <v>-0.5537069728050046</v>
       </c>
       <c r="G41">
-        <v>0.9456856812407179</v>
+        <v>0.945492222493141</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -6818,19 +5331,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.01534607647960032</v>
+        <v>0.01532635245368263</v>
       </c>
       <c r="D42">
-        <v>0.02271606794669438</v>
+        <v>0.02271548198499836</v>
       </c>
       <c r="E42">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F42">
-        <v>0.6755604233801152</v>
+        <v>0.674709542320272</v>
       </c>
       <c r="G42">
-        <v>0.9062952998052286</v>
+        <v>0.90661006180054</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -6850,19 +5363,19 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.06788437668635097</v>
+        <v>0.06778579150253571</v>
       </c>
       <c r="D43">
-        <v>0.02271607859286331</v>
+        <v>0.02271572214848868</v>
       </c>
       <c r="E43">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F43">
-        <v>2.988384478810446</v>
+        <v>2.984091417364234</v>
       </c>
       <c r="G43">
-        <v>0.01599662661905588</v>
+        <v>0.01620263809188094</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -6882,19 +5395,19 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.0672300641457409</v>
+        <v>0.06711531701985057</v>
       </c>
       <c r="D44">
-        <v>0.02271607958371239</v>
+        <v>0.02271567354533243</v>
       </c>
       <c r="E44">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F44">
-        <v>2.959580410782914</v>
+        <v>2.954581861106262</v>
       </c>
       <c r="G44">
-        <v>0.01744408229681615</v>
+        <v>0.01770395880758335</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -6914,19 +5427,19 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.05253830020675065</v>
+        <v>0.05245943904885309</v>
       </c>
       <c r="D45">
-        <v>0.0227160163076088</v>
+        <v>0.02271524293360295</v>
       </c>
       <c r="E45">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F45">
-        <v>2.312830713594477</v>
+        <v>2.309437728761825</v>
       </c>
       <c r="G45">
-        <v>0.09741781195728771</v>
+        <v>0.09817983042362577</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -6946,19 +5459,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.05188398766614056</v>
+        <v>0.05178896456616795</v>
       </c>
       <c r="D46">
-        <v>0.02271601682080321</v>
+        <v>0.02271520216191995</v>
       </c>
       <c r="E46">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F46">
-        <v>2.28402664408249</v>
+        <v>2.279925320364862</v>
       </c>
       <c r="G46">
-        <v>0.1040878603186778</v>
+        <v>0.1050605591925171</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -6978,19 +5491,19 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.0006543125406100858</v>
+        <v>-0.0006704744826851183</v>
       </c>
       <c r="D47">
-        <v>0.02271602224153441</v>
+        <v>0.02271545839107503</v>
       </c>
       <c r="E47">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F47">
-        <v>-0.02880401038759894</v>
+        <v>-0.029516220678538</v>
       </c>
       <c r="G47">
-        <v>0.9999913973986267</v>
+        <v>0.9999907435659169</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -7010,19 +5523,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.03949434678635326</v>
+        <v>0.03947866393856216</v>
       </c>
       <c r="D48">
-        <v>0.02409249281153172</v>
+        <v>0.02409187344765059</v>
       </c>
       <c r="E48">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F48">
-        <v>1.639280214600689</v>
+        <v>1.638671397819918</v>
       </c>
       <c r="G48">
-        <v>0.3582011528508798</v>
+        <v>0.358533050064615</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -7042,19 +5555,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.08559360287862795</v>
+        <v>0.08549469235358322</v>
       </c>
       <c r="D49">
-        <v>0.02409250284947616</v>
+        <v>0.02409209989050696</v>
       </c>
       <c r="E49">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F49">
-        <v>3.552706973343328</v>
+        <v>3.548660878135858</v>
       </c>
       <c r="G49">
-        <v>0.002492357787253097</v>
+        <v>0.002527659175969643</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -7074,19 +5587,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>0.09339513786358809</v>
+        <v>0.09328564767220809</v>
       </c>
       <c r="D50">
-        <v>0.02409250378371723</v>
+        <v>0.02409205406404655</v>
       </c>
       <c r="E50">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F50">
-        <v>3.876522701916462</v>
+        <v>3.872050404013564</v>
       </c>
       <c r="G50">
-        <v>0.000750625093558055</v>
+        <v>0.0007632995071357174</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -7106,19 +5619,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>0.04609925609227469</v>
+        <v>0.04601602841502107</v>
       </c>
       <c r="D51">
-        <v>0.0227160163076088</v>
+        <v>0.02271524293360293</v>
       </c>
       <c r="E51">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F51">
-        <v>2.029372380615592</v>
+        <v>2.025777516424841</v>
       </c>
       <c r="G51">
-        <v>0.1795519580647085</v>
+        <v>0.1808385867829772</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -7138,19 +5651,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>0.05390079107723482</v>
+        <v>0.05380698373364591</v>
       </c>
       <c r="D52">
-        <v>0.02271601682080319</v>
+        <v>0.02271520216191993</v>
       </c>
       <c r="E52">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F52">
-        <v>2.372809964987911</v>
+        <v>2.368765347105238</v>
       </c>
       <c r="G52">
-        <v>0.08462097941174296</v>
+        <v>0.08543354655087521</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -7170,19 +5683,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.007801534984960137</v>
+        <v>0.007790955318624865</v>
       </c>
       <c r="D53">
-        <v>0.02271602224153444</v>
+        <v>0.02271545839107502</v>
       </c>
       <c r="E53">
-        <v>294.8452533888442</v>
+        <v>295.551040775367</v>
       </c>
       <c r="F53">
-        <v>0.3434375482647508</v>
+        <v>0.342980325754111</v>
       </c>
       <c r="G53">
-        <v>0.986047802338063</v>
+        <v>0.9861018860983066</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -7202,19 +5715,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.009152955440572645</v>
+        <v>-0.008793303068147577</v>
       </c>
       <c r="D54">
-        <v>0.02047523050283754</v>
+        <v>0.02026419891285689</v>
       </c>
       <c r="E54">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F54">
-        <v>-0.4470257582352585</v>
+        <v>-0.4339329230808403</v>
       </c>
       <c r="G54">
-        <v>0.6550741352924401</v>
+        <v>0.6645471710948159</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -7234,19 +5747,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.01411146998705944</v>
+        <v>0.01509498343875254</v>
       </c>
       <c r="D55">
-        <v>0.0207977150239765</v>
+        <v>0.02060106205218826</v>
       </c>
       <c r="E55">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F55">
-        <v>0.6785105945913353</v>
+        <v>0.7327284098515269</v>
       </c>
       <c r="G55">
-        <v>0.4978009972905388</v>
+        <v>0.4641093529369694</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -7266,19 +5779,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.0187010531703228</v>
+        <v>0.01963360534016423</v>
       </c>
       <c r="D56">
-        <v>0.01981084737210676</v>
+        <v>0.01958805255570052</v>
       </c>
       <c r="E56">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F56">
-        <v>0.9439804779200649</v>
+        <v>1.002325539220102</v>
       </c>
       <c r="G56">
-        <v>0.3456922885594463</v>
+        <v>0.316730380633096</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -7298,21 +5811,176 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.02811403815051643</v>
+        <v>0.02860315132608443</v>
       </c>
       <c r="D57">
-        <v>0.0201901416665745</v>
+        <v>0.0199776907051038</v>
       </c>
       <c r="E57">
-        <v>444.6211799224947</v>
+        <v>445.5907278586985</v>
       </c>
       <c r="F57">
-        <v>1.392463639671247</v>
+        <v>1.43175463812627</v>
       </c>
       <c r="G57">
-        <v>0.1644780145462774</v>
+        <v>0.1529150923565272</v>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>t.ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>p.value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>urban - reef</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.08277130908558872</v>
+      </c>
+      <c r="C2">
+        <v>0.008868722222354776</v>
+      </c>
+      <c r="D2">
+        <v>175.2045442285989</v>
+      </c>
+      <c r="E2">
+        <v>9.332946394121217</v>
+      </c>
+      <c r="F2">
+        <v>4.574661136062775E-17</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>urban - reef</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0624836737770202</v>
+      </c>
+      <c r="C3">
+        <v>0.01492123080484085</v>
+      </c>
+      <c r="D3">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E3">
+        <v>4.187568344345213</v>
+      </c>
+      <c r="F3">
+        <v>3.449092133712127E-05</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>urban - reef</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.01024510920384296</v>
+      </c>
+      <c r="C4">
+        <v>0.008106086133910079</v>
+      </c>
+      <c r="D4">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E4">
+        <v>1.26387865050986</v>
+      </c>
+      <c r="F4">
+        <v>0.2072695166271824</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>urban - reef</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.005547148688418793</v>
+      </c>
+      <c r="C5">
+        <v>0.01158547782160106</v>
+      </c>
+      <c r="D5">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E5">
+        <v>0.4788018909393762</v>
+      </c>
+      <c r="F5">
+        <v>0.6323144323400665</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>ssid_heat</t>
         </is>

--- a/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
+++ b/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Model fit" sheetId="1" r:id="rId1"/>
     <sheet name="Rho estimates" sheetId="2" r:id="rId2"/>
     <sheet name="Joint tests" sheetId="3" r:id="rId3"/>
-    <sheet name="Parametric coefficients" sheetId="4" r:id="rId4"/>
+    <sheet name="Effects vs overall mean" sheetId="4" r:id="rId4"/>
     <sheet name="Smooth significance" sheetId="5" r:id="rId5"/>
     <sheet name="k.check" sheetId="6" r:id="rId6"/>
     <sheet name="Estimated marginal means" sheetId="7" r:id="rId7"/>
@@ -888,7 +888,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -904,20 +904,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>std_error</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>t_value</t>
+          <t>df</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>t_ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
@@ -926,22 +931,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>overall mean</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.4386256879721936</v>
+        <v>0.4356588237227743</v>
       </c>
       <c r="C2">
-        <v>0.01162963068231404</v>
+        <v>0.004443022444785122</v>
       </c>
       <c r="D2">
-        <v>37.71621816325098</v>
-      </c>
-      <c r="E2">
-        <v>5.131663032553078E-86</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>175.2045442285989</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -950,22 +952,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>treatmentLC:siteRainbow</t>
+          <t>treatment CC</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.05103480058539134</v>
+        <v>-0.009736001586646496</v>
       </c>
       <c r="C3">
-        <v>0.03899314648083595</v>
+        <v>0.006886396904334061</v>
       </c>
       <c r="D3">
-        <v>1.3088146300395</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E3">
-        <v>0.1923112665405252</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>-1.413801981195564</v>
+      </c>
+      <c r="F3">
+        <v>0.1591944326277489</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -974,22 +979,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>treatmentCH:siteRainbow</t>
+          <t>treatment LC</t>
         </is>
       </c>
       <c r="B4">
-        <v>-0.03156642279546758</v>
+        <v>-0.04015305218057764</v>
       </c>
       <c r="C4">
-        <v>0.02678917137592421</v>
+        <v>0.008297200450431653</v>
       </c>
       <c r="D4">
-        <v>-1.178327703851145</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E4">
-        <v>0.2402638944666043</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>-4.839349419175321</v>
+      </c>
+      <c r="F4">
+        <v>2.844113068834794E-06</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -998,22 +1006,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>treatmentLH:siteRainbow</t>
+          <t>treatment CH</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.03836506878535723</v>
+        <v>0.009141159838930216</v>
       </c>
       <c r="C5">
-        <v>0.03740091221718866</v>
+        <v>0.006159902588585336</v>
       </c>
       <c r="D5">
-        <v>-1.025778958613888</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E5">
-        <v>0.3064099342031821</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>1.483977986254089</v>
+      </c>
+      <c r="F5">
+        <v>0.1396115357719038</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -1022,22 +1033,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>treatmentLC:siteStar</t>
+          <t>treatment LH</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.02503130922524261</v>
+        <v>0.04074789392829394</v>
       </c>
       <c r="C6">
-        <v>0.03119451718466873</v>
+        <v>0.009083726044889214</v>
       </c>
       <c r="D6">
-        <v>0.8024265635226703</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E6">
-        <v>0.4233933524524296</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>4.485812730032734</v>
+      </c>
+      <c r="F6">
+        <v>1.310841084099791E-05</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -1046,22 +1060,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>treatmentCH:siteStar</t>
+          <t>site Emerald</t>
         </is>
       </c>
       <c r="B7">
-        <v>-0.01268907931033241</v>
+        <v>-0.05638290572290167</v>
       </c>
       <c r="C7">
-        <v>0.02678917137592421</v>
+        <v>0.007073789604240152</v>
       </c>
       <c r="D7">
-        <v>-0.4736644942193419</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E7">
-        <v>0.6363288595428018</v>
-      </c>
-      <c r="F7" t="inlineStr">
+        <v>-7.970678925636235</v>
+      </c>
+      <c r="F7">
+        <v>1.945860798849331E-13</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -1070,22 +1087,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>treatmentLH:siteStar</t>
+          <t>site Rainbow</t>
         </is>
       </c>
       <c r="B8">
-        <v>-0.01551799636626711</v>
+        <v>-0.02638840336268705</v>
       </c>
       <c r="C8">
-        <v>0.03740091221718864</v>
+        <v>0.008888301942539239</v>
       </c>
       <c r="D8">
-        <v>-0.4149095689472349</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E8">
-        <v>0.6787157146962113</v>
-      </c>
-      <c r="F8" t="inlineStr">
+        <v>-2.968891418550113</v>
+      </c>
+      <c r="F8">
+        <v>0.003407430084079613</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -1094,22 +1114,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>treatmentLC:siteMacN</t>
+          <t>site Star</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.01990324763414215</v>
+        <v>0.0408901940722853</v>
       </c>
       <c r="C9">
-        <v>0.03119451718466874</v>
+        <v>0.007846489347296931</v>
       </c>
       <c r="D9">
-        <v>0.6380367266566979</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E9">
-        <v>0.5242828059518212</v>
-      </c>
-      <c r="F9" t="inlineStr">
+        <v>5.211272489189287</v>
+      </c>
+      <c r="F9">
+        <v>5.231526800093123E-07</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -1118,22 +1141,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>treatmentCH:siteMacN</t>
+          <t>site MacN</t>
         </is>
       </c>
       <c r="B10">
-        <v>-0.02216949829613561</v>
+        <v>0.04188111501330342</v>
       </c>
       <c r="C10">
-        <v>0.02514982378765276</v>
+        <v>0.006732068490519134</v>
       </c>
       <c r="D10">
-        <v>-0.8814971621001839</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E10">
-        <v>0.3792564790982089</v>
-      </c>
-      <c r="F10" t="inlineStr">
+        <v>6.221136203870352</v>
+      </c>
+      <c r="F10">
+        <v>3.523502928324561E-09</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -1142,22 +1168,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>treatmentLH:siteMacN</t>
+          <t>treatment x site CC : Emerald</t>
         </is>
       </c>
       <c r="B11">
-        <v>-0.0231311198819238</v>
+        <v>-0.002966864249419228</v>
       </c>
       <c r="C11">
-        <v>0.02917979891271558</v>
+        <v>0.01097927152591337</v>
       </c>
       <c r="D11">
-        <v>-0.7927100509196463</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E11">
-        <v>0.4290188727792749</v>
-      </c>
-      <c r="F11" t="inlineStr">
+        <v>-0.2702241439622666</v>
+      </c>
+      <c r="F11">
+        <v>0.787305858791389</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>ofav_control</t>
         </is>
@@ -1166,430 +1195,1870 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>treatment x site LC : Emerald</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.3945470664665202</v>
+        <v>-0.02695920361061325</v>
       </c>
       <c r="C12">
-        <v>0.01389093318102155</v>
+        <v>0.01367716226636776</v>
       </c>
       <c r="D12">
-        <v>28.40320814483285</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E12">
-        <v>3.828954088859774E-99</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
+        <v>-1.971110898998846</v>
+      </c>
+      <c r="F12">
+        <v>0.05028606800358819</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>treatmentLH:siteRainbow</t>
+          <t>treatment x site CH : Emerald</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.02778022203094027</v>
+        <v>0.01363938585106467</v>
       </c>
       <c r="C13">
-        <v>0.04666346702117233</v>
+        <v>0.01011428779351373</v>
       </c>
       <c r="D13">
-        <v>0.5953312902861617</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E13">
-        <v>0.5519482861519334</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
+        <v>1.348526572460355</v>
+      </c>
+      <c r="F13">
+        <v>0.1792296710329647</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>treatmentLH:siteStar</t>
+          <t>treatment x site LH : Emerald</t>
         </is>
       </c>
       <c r="B14">
-        <v>-0.03637784107739722</v>
+        <v>0.0162866820089678</v>
       </c>
       <c r="C14">
-        <v>0.03866704233954938</v>
+        <v>0.01303685280637928</v>
       </c>
       <c r="D14">
-        <v>-0.9407970942786404</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E14">
-        <v>0.3473590868962794</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
+        <v>1.249280194449867</v>
+      </c>
+      <c r="F14">
+        <v>0.2132290393411336</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>treatmentLH:siteMacN</t>
+          <t>treatment x site CC : Rainbow</t>
         </is>
       </c>
       <c r="B15">
-        <v>-0.00588250088840088</v>
+        <v>0.001757308499439142</v>
       </c>
       <c r="C15">
-        <v>0.03690979149786645</v>
+        <v>0.01281630935852498</v>
       </c>
       <c r="D15">
-        <v>-0.1593750777145657</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E15">
-        <v>0.8734513259167644</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
+        <v>0.1371150188622936</v>
+      </c>
+      <c r="F15">
+        <v>0.8910973194922308</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>treatment x site LC : Rainbow</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.3138184996420411</v>
+        <v>0.02879976972363645</v>
       </c>
       <c r="C16">
-        <v>0.01285164456162865</v>
+        <v>0.01751574787492767</v>
       </c>
       <c r="D16">
-        <v>24.41854800272127</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E16">
-        <v>7.472337606185724E-73</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>1.64422152735259</v>
+      </c>
+      <c r="F16">
+        <v>0.1019235878615577</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>treatmentLC:siteRainbow</t>
+          <t>treatment x site CH : Rainbow</t>
         </is>
       </c>
       <c r="B17">
-        <v>-0.0135905832761481</v>
+        <v>-0.01320286419554454</v>
       </c>
       <c r="C17">
-        <v>0.03210613509143157</v>
+        <v>0.01143711262421352</v>
       </c>
       <c r="D17">
-        <v>-0.42330175330805</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E17">
-        <v>0.672382977309413</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>-1.15438787999628</v>
+      </c>
+      <c r="F17">
+        <v>0.2499133217254166</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>treatmentCH:siteRainbow</t>
+          <t>treatment x site LH : Rainbow</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.04963062453130374</v>
+        <v>-0.01735421402753106</v>
       </c>
       <c r="C18">
-        <v>0.03210613509143156</v>
+        <v>0.01789149229388642</v>
       </c>
       <c r="D18">
-        <v>1.545829929076362</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E18">
-        <v>0.1232157107501538</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>-0.9699701814957632</v>
+      </c>
+      <c r="F18">
+        <v>0.3333984872000813</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>treatmentLH:siteRainbow</t>
+          <t>treatment x site CC : Star</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.0370205683824967</v>
+        <v>-0.002172922636580001</v>
       </c>
       <c r="C19">
-        <v>0.03210613509143152</v>
+        <v>0.01213064503676786</v>
       </c>
       <c r="D19">
-        <v>1.15306835522463</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E19">
-        <v>0.2498140208310467</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>-0.1791267183232133</v>
+      </c>
+      <c r="F19">
+        <v>0.8580451812037124</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>treatmentLC:siteStar</t>
+          <t>treatment x site LC : Star</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.01730873497980174</v>
+        <v>-0.001133952772531416</v>
       </c>
       <c r="C20">
-        <v>0.03210613509143156</v>
+        <v>0.01236342567939183</v>
       </c>
       <c r="D20">
-        <v>0.5391098906956593</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E20">
-        <v>0.5902168964895658</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>-0.09171833130534064</v>
+      </c>
+      <c r="F20">
+        <v>0.9270266149050699</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>treatmentCH:siteStar</t>
+          <t>treatment x site CH : Star</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.0686361477464959</v>
+        <v>0.00174424815357149</v>
       </c>
       <c r="C21">
-        <v>0.03210613509143164</v>
+        <v>0.01066312846277256</v>
       </c>
       <c r="D21">
-        <v>2.13778916556086</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E21">
-        <v>0.03335407221107774</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>0.163577524144163</v>
+      </c>
+      <c r="F21">
+        <v>0.8702522770598331</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>treatmentLH:siteStar</t>
+          <t>treatment x site LH : Star</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.04411885837877381</v>
+        <v>0.001562627255539926</v>
       </c>
       <c r="C22">
-        <v>0.03210613509143161</v>
+        <v>0.01740690265201833</v>
       </c>
       <c r="D22">
-        <v>1.37415662935238</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E22">
-        <v>0.1704342312671515</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>0.08977055176204705</v>
+      </c>
+      <c r="F22">
+        <v>0.928572089342566</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>treatmentLC:siteMacN</t>
+          <t>treatment x site CC : MacN</t>
         </is>
       </c>
       <c r="B23">
-        <v>-0.006843576505077798</v>
+        <v>0.003382478386560086</v>
       </c>
       <c r="C23">
-        <v>0.03309424655308052</v>
+        <v>0.01076954069690552</v>
       </c>
       <c r="D23">
-        <v>-0.2067905215518731</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E23">
-        <v>0.8363158515220516</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>0.3140782398948542</v>
+      </c>
+      <c r="F23">
+        <v>0.7538352726621881</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>treatmentCH:siteMacN</t>
+          <t>treatment x site LC : MacN</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.0509272468954484</v>
+        <v>-0.0007066133404917858</v>
       </c>
       <c r="C24">
-        <v>0.03309424655308055</v>
+        <v>0.0123326421254169</v>
       </c>
       <c r="D24">
-        <v>1.538855003505371</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E24">
-        <v>0.124909604573518</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>-0.05729618465417841</v>
+      </c>
+      <c r="F24">
+        <v>0.9543745512840482</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>treatmentLH:siteMacN</t>
+          <t>treatment x site CH : MacN</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.01794852772641631</v>
+        <v>-0.002180769809091622</v>
       </c>
       <c r="C25">
-        <v>0.03309424655308054</v>
+        <v>0.009573690994736012</v>
       </c>
       <c r="D25">
-        <v>0.5423458635817044</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E25">
-        <v>0.587988958188609</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
+        <v>-0.2277877790593716</v>
+      </c>
+      <c r="F25">
+        <v>0.820076837028819</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>treatment x site LH : MacN</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.3205614863572391</v>
+        <v>-0.0004950952369766819</v>
       </c>
       <c r="C26">
-        <v>0.009399211856398094</v>
+        <v>0.01286072061269397</v>
       </c>
       <c r="D26">
-        <v>34.10514533077911</v>
+        <v>175.2045442285989</v>
       </c>
       <c r="E26">
-        <v>2.673552169490497E-126</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
+        <v>-0.03849669484989869</v>
+      </c>
+      <c r="F26">
+        <v>0.9693354962098961</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ofav_control</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>treatmentLH:siteRainbow</t>
+          <t>overall mean</t>
         </is>
       </c>
       <c r="B27">
-        <v>-0.02388828650690011</v>
+        <v>0.3719293947695835</v>
       </c>
       <c r="C27">
-        <v>0.02660351065239026</v>
+        <v>0.007620731627183546</v>
       </c>
       <c r="D27">
-        <v>-0.8979373744703051</v>
-      </c>
-      <c r="E27">
-        <v>0.3697038561709641</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
+        <v>412.7735348871453</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>treatmentLH:siteStar</t>
+          <t>treatment CH</t>
         </is>
       </c>
       <c r="B28">
-        <v>-0.02842690840831184</v>
+        <v>0.007106843717662075</v>
       </c>
       <c r="C28">
-        <v>0.02613019749612858</v>
+        <v>0.007631402060364536</v>
       </c>
       <c r="D28">
-        <v>-1.087894892969084</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="E28">
-        <v>0.2772295879043122</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
+        <v>0.9312631756847307</v>
+      </c>
+      <c r="F28">
+        <v>0.3522617877451257</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>treatmentLH:siteMacN</t>
+          <t>treatment LH</t>
         </is>
       </c>
       <c r="B29">
-        <v>-0.03739645439423202</v>
+        <v>-0.007106843717662075</v>
       </c>
       <c r="C29">
-        <v>0.02643497420496783</v>
+        <v>0.007631402060364536</v>
       </c>
       <c r="D29">
-        <v>-1.414658251764219</v>
+        <v>412.7735348871453</v>
       </c>
       <c r="E29">
-        <v>0.1578671151072505</v>
-      </c>
-      <c r="F29" t="inlineStr">
+        <v>-0.9312631756847307</v>
+      </c>
+      <c r="F29">
+        <v>0.3522617877451257</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>site Emerald</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>-0.04042730096006027</v>
+      </c>
+      <c r="C30">
+        <v>0.01238871230368095</v>
+      </c>
+      <c r="D30">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E30">
+        <v>-3.26323672461491</v>
+      </c>
+      <c r="F30">
+        <v>0.00119311679529951</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>site Rainbow</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>-0.02205637281695993</v>
+      </c>
+      <c r="C31">
+        <v>0.01529855369826901</v>
+      </c>
+      <c r="D31">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E31">
+        <v>-1.441729280556472</v>
+      </c>
+      <c r="F31">
+        <v>0.1501369990154243</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>site Star</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>0.02449281209745503</v>
+      </c>
+      <c r="C32">
+        <v>0.01207732992163291</v>
+      </c>
+      <c r="D32">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E32">
+        <v>2.02799892495969</v>
+      </c>
+      <c r="F32">
+        <v>0.04320213056575246</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>site MacN</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>0.03799086167956518</v>
+      </c>
+      <c r="C33">
+        <v>0.01143407299573432</v>
+      </c>
+      <c r="D33">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E33">
+        <v>3.322600939642272</v>
+      </c>
+      <c r="F33">
+        <v>0.0009713117844537503</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Emerald</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>-0.001810014991857307</v>
+      </c>
+      <c r="C34">
+        <v>0.01228241145547157</v>
+      </c>
+      <c r="D34">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E34">
+        <v>-0.1473664189169449</v>
+      </c>
+      <c r="F34">
+        <v>0.8829147627075981</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Emerald</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>0.001810014991857307</v>
+      </c>
+      <c r="C35">
+        <v>0.01228241145547157</v>
+      </c>
+      <c r="D35">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E35">
+        <v>0.1473664189169449</v>
+      </c>
+      <c r="F35">
+        <v>0.8829147627075981</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Rainbow</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>-0.01570012600732737</v>
+      </c>
+      <c r="C36">
+        <v>0.01518773985784276</v>
+      </c>
+      <c r="D36">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E36">
+        <v>-1.033736826827464</v>
+      </c>
+      <c r="F36">
+        <v>0.3018644722364796</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Rainbow</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0.01570012600732737</v>
+      </c>
+      <c r="C37">
+        <v>0.01518773985784276</v>
+      </c>
+      <c r="D37">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E37">
+        <v>1.033736826827464</v>
+      </c>
+      <c r="F37">
+        <v>0.3018644722364796</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Star</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>0.01637890554684138</v>
+      </c>
+      <c r="C38">
+        <v>0.01205149547126986</v>
+      </c>
+      <c r="D38">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E38">
+        <v>1.359076604715808</v>
+      </c>
+      <c r="F38">
+        <v>0.1748644072510913</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Star</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>-0.01637890554684138</v>
+      </c>
+      <c r="C39">
+        <v>0.01205149547126986</v>
+      </c>
+      <c r="D39">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E39">
+        <v>-1.359076604715808</v>
+      </c>
+      <c r="F39">
+        <v>0.1748644072510913</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>treatment x site CH : MacN</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>0.001131235452343272</v>
+      </c>
+      <c r="C40">
+        <v>0.01133771871427797</v>
+      </c>
+      <c r="D40">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E40">
+        <v>0.09977628488160228</v>
+      </c>
+      <c r="F40">
+        <v>0.9205703758899153</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>treatment x site LH : MacN</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>-0.001131235452343272</v>
+      </c>
+      <c r="C41">
+        <v>0.01133771871427797</v>
+      </c>
+      <c r="D41">
+        <v>412.7735348871453</v>
+      </c>
+      <c r="E41">
+        <v>-0.09977628488160228</v>
+      </c>
+      <c r="F41">
+        <v>0.9205703758899153</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ofav_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>overall mean</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0.33039078394576</v>
+      </c>
+      <c r="C42">
+        <v>0.004053770017972506</v>
+      </c>
+      <c r="D42">
+        <v>295.551040775367</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>treatment CC</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>0.05350051621656567</v>
+      </c>
+      <c r="C43">
+        <v>0.007128168673016529</v>
+      </c>
+      <c r="D43">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E43">
+        <v>7.505506487113624</v>
+      </c>
+      <c r="F43">
+        <v>7.248968391100128E-13</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>treatment LC</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0.02008407258272527</v>
+      </c>
+      <c r="C44">
+        <v>0.006984747891246344</v>
+      </c>
+      <c r="D44">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E44">
+        <v>2.87541839668912</v>
+      </c>
+      <c r="F44">
+        <v>0.004328155502998678</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>treatment CH</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>-0.04062291823915393</v>
+      </c>
+      <c r="C45">
+        <v>0.006985151465669926</v>
+      </c>
+      <c r="D45">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E45">
+        <v>-5.815610218161233</v>
+      </c>
+      <c r="F45">
+        <v>1.566899238762987E-08</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>treatment LH</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>-0.03296167056013703</v>
+      </c>
+      <c r="C46">
+        <v>0.006985078804288372</v>
+      </c>
+      <c r="D46">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E46">
+        <v>-4.718868817900918</v>
+      </c>
+      <c r="F46">
+        <v>3.664707731085024E-06</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>site Emerald</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>0.002007308538242901</v>
+      </c>
+      <c r="C47">
+        <v>0.006984616628874524</v>
+      </c>
+      <c r="D47">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E47">
+        <v>0.2873899377590251</v>
+      </c>
+      <c r="F47">
+        <v>0.7740151619469204</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>site Rainbow</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>-0.01225241774208586</v>
+      </c>
+      <c r="C48">
+        <v>0.006984162182690221</v>
+      </c>
+      <c r="D48">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E48">
+        <v>-1.754314608050291</v>
+      </c>
+      <c r="F48">
+        <v>0.08041295627102457</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>site Star</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0.01175297809753159</v>
+      </c>
+      <c r="C49">
+        <v>0.00698260637866632</v>
+      </c>
+      <c r="D49">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E49">
+        <v>1.683179239981219</v>
+      </c>
+      <c r="F49">
+        <v>0.09339635142248127</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>site MacN</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>-0.001507868893688637</v>
+      </c>
+      <c r="C50">
+        <v>0.007127627580926786</v>
+      </c>
+      <c r="D50">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E50">
+        <v>-0.21155270481915</v>
+      </c>
+      <c r="F50">
+        <v>0.8326018149063582</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>treatment x site CC : Emerald</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0.01657228430371942</v>
+      </c>
+      <c r="C51">
+        <v>0.0121334970191632</v>
+      </c>
+      <c r="D51">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E51">
+        <v>1.365829181607394</v>
+      </c>
+      <c r="F51">
+        <v>0.173031042054588</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>treatment x site LC : Emerald</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.01735364050407546</v>
+      </c>
+      <c r="C52">
+        <v>0.01205024734295223</v>
+      </c>
+      <c r="D52">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E52">
+        <v>1.440106581233372</v>
+      </c>
+      <c r="F52">
+        <v>0.150895662601481</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Emerald</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>-0.02572622048959259</v>
+      </c>
+      <c r="C53">
+        <v>0.01205024734295226</v>
+      </c>
+      <c r="D53">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E53">
+        <v>-2.134912235194816</v>
+      </c>
+      <c r="F53">
+        <v>0.03359049559057953</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Emerald</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>-0.008199704318202284</v>
+      </c>
+      <c r="C54">
+        <v>0.01205024734295224</v>
+      </c>
+      <c r="D54">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E54">
+        <v>-0.6804594200299134</v>
+      </c>
+      <c r="F54">
+        <v>0.496746309202207</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>treatment x site CC : Rainbow</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>-0.001692868105693667</v>
+      </c>
+      <c r="C55">
+        <v>0.01213349701916314</v>
+      </c>
+      <c r="D55">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E55">
+        <v>-0.1395202144130437</v>
+      </c>
+      <c r="F55">
+        <v>0.8891341095908338</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>treatment x site LC : Rainbow</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>-0.01450209518148572</v>
+      </c>
+      <c r="C56">
+        <v>0.01205024734295223</v>
+      </c>
+      <c r="D56">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E56">
+        <v>-1.203468673194289</v>
+      </c>
+      <c r="F56">
+        <v>0.2297580717222444</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Rainbow</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>0.005639251632298061</v>
+      </c>
+      <c r="C57">
+        <v>0.01205024734295222</v>
+      </c>
+      <c r="D57">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E57">
+        <v>0.4679780814288652</v>
+      </c>
+      <c r="F57">
+        <v>0.6401451699196075</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Rainbow</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0.01055571165488133</v>
+      </c>
+      <c r="C58">
+        <v>0.01205024734295222</v>
+      </c>
+      <c r="D58">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E58">
+        <v>0.8759746878602461</v>
+      </c>
+      <c r="F58">
+        <v>0.3817551719459478</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>treatment x site CC : Star</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>-0.01594365097254844</v>
+      </c>
+      <c r="C59">
+        <v>0.01213349701916316</v>
+      </c>
+      <c r="D59">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E59">
+        <v>-1.31401944116916</v>
+      </c>
+      <c r="F59">
+        <v>0.1898586243441945</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>treatment x site LC : Star</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>0.002146440207609335</v>
+      </c>
+      <c r="C60">
+        <v>0.01205024734295223</v>
+      </c>
+      <c r="D60">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E60">
+        <v>0.178124161813551</v>
+      </c>
+      <c r="F60">
+        <v>0.8587474944770664</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Star</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.01039399198063545</v>
+      </c>
+      <c r="C61">
+        <v>0.01205024734295225</v>
+      </c>
+      <c r="D61">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E61">
+        <v>0.8625542434790362</v>
+      </c>
+      <c r="F61">
+        <v>0.3890819459952305</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Star</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>0.003403218784303663</v>
+      </c>
+      <c r="C62">
+        <v>0.01205024734295224</v>
+      </c>
+      <c r="D62">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E62">
+        <v>0.2824189983365017</v>
+      </c>
+      <c r="F62">
+        <v>0.7778199247702895</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>treatment x site CC : MacN</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>0.001064234774522691</v>
+      </c>
+      <c r="C63">
+        <v>0.01285851274072789</v>
+      </c>
+      <c r="D63">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E63">
+        <v>0.08276499747531824</v>
+      </c>
+      <c r="F63">
+        <v>0.9340944271399774</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>treatment x site LC : MacN</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>-0.004997985530199068</v>
+      </c>
+      <c r="C64">
+        <v>0.01213349701916313</v>
+      </c>
+      <c r="D64">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E64">
+        <v>-0.4119163273626276</v>
+      </c>
+      <c r="F64">
+        <v>0.680699336247149</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>treatment x site CH : MacN</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0.009692976876659086</v>
+      </c>
+      <c r="C65">
+        <v>0.01213349701916315</v>
+      </c>
+      <c r="D65">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E65">
+        <v>0.7988609434980201</v>
+      </c>
+      <c r="F65">
+        <v>0.4250125410162635</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>treatment x site LH : MacN</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>-0.005759226120982705</v>
+      </c>
+      <c r="C66">
+        <v>0.01213349701916314</v>
+      </c>
+      <c r="D66">
+        <v>295.551040775367</v>
+      </c>
+      <c r="E66">
+        <v>-0.4746550901101985</v>
+      </c>
+      <c r="F66">
+        <v>0.6353833601244647</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ssid_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>overall mean</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>0.2997854549076612</v>
+      </c>
+      <c r="C67">
+        <v>0.007061666277166398</v>
+      </c>
+      <c r="D67">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>treatment CH</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>0.00681730462960672</v>
+      </c>
+      <c r="C68">
+        <v>0.005983753811563602</v>
+      </c>
+      <c r="D68">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E68">
+        <v>1.139302324977388</v>
+      </c>
+      <c r="F68">
+        <v>0.2551891689127502</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>treatment LH</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>-0.00681730462960672</v>
+      </c>
+      <c r="C69">
+        <v>0.005983753811563602</v>
+      </c>
+      <c r="D69">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E69">
+        <v>-1.139302324977388</v>
+      </c>
+      <c r="F69">
+        <v>0.2551891689127502</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>site Emerald</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>0.0009454295200049829</v>
+      </c>
+      <c r="C70">
+        <v>0.01381901904423573</v>
+      </c>
+      <c r="D70">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E70">
+        <v>0.06841509639566967</v>
+      </c>
+      <c r="F70">
+        <v>0.9454858939566231</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>site Rainbow</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>-0.006492578208423886</v>
+      </c>
+      <c r="C71">
+        <v>0.01439500216888586</v>
+      </c>
+      <c r="D71">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E71">
+        <v>-0.4510300264113399</v>
+      </c>
+      <c r="F71">
+        <v>0.6521873154217532</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>site Star</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>-0.005120783672600618</v>
+      </c>
+      <c r="C72">
+        <v>0.008315175380848944</v>
+      </c>
+      <c r="D72">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E72">
+        <v>-0.6158359190347958</v>
+      </c>
+      <c r="F72">
+        <v>0.5383172526093408</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>site MacN</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>0.01066793236101926</v>
+      </c>
+      <c r="C73">
+        <v>0.01025825578977483</v>
+      </c>
+      <c r="D73">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E73">
+        <v>1.039936279582031</v>
+      </c>
+      <c r="F73">
+        <v>0.2989334455417383</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Emerald</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>-0.0112139561636805</v>
+      </c>
+      <c r="C74">
+        <v>0.008079237944350287</v>
+      </c>
+      <c r="D74">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E74">
+        <v>-1.38799676911636</v>
+      </c>
+      <c r="F74">
+        <v>0.1658316239187297</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Emerald</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>0.0112139561636805</v>
+      </c>
+      <c r="C75">
+        <v>0.008079237944350287</v>
+      </c>
+      <c r="D75">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E75">
+        <v>1.38799676911636</v>
+      </c>
+      <c r="F75">
+        <v>0.1658316239187297</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Rainbow</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>0.0007301870897695557</v>
+      </c>
+      <c r="C76">
+        <v>0.008175471303330168</v>
+      </c>
+      <c r="D76">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E76">
+        <v>0.08931437255147893</v>
+      </c>
+      <c r="F76">
+        <v>0.9288722013095607</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Rainbow</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-0.0007301870897695557</v>
+      </c>
+      <c r="C77">
+        <v>0.008175471303330168</v>
+      </c>
+      <c r="D77">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E77">
+        <v>-0.08931437255147893</v>
+      </c>
+      <c r="F77">
+        <v>0.9288722013095607</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>treatment x site CH : Star</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>0.002999498040475423</v>
+      </c>
+      <c r="C78">
+        <v>0.007972202743448469</v>
+      </c>
+      <c r="D78">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E78">
+        <v>0.3762445759348508</v>
+      </c>
+      <c r="F78">
+        <v>0.706914154744372</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>treatment x site LH : Star</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>-0.002999498040475423</v>
+      </c>
+      <c r="C79">
+        <v>0.007972202743448469</v>
+      </c>
+      <c r="D79">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E79">
+        <v>-0.3762445759348508</v>
+      </c>
+      <c r="F79">
+        <v>0.706914154744372</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>treatment x site CH : MacN</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>0.00748427103343552</v>
+      </c>
+      <c r="C80">
+        <v>0.008097573027617034</v>
+      </c>
+      <c r="D80">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E80">
+        <v>0.9242610110350561</v>
+      </c>
+      <c r="F80">
+        <v>0.3558506772991563</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ssid_heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>treatment x site LH : MacN</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-0.00748427103343552</v>
+      </c>
+      <c r="C81">
+        <v>0.008097573027617034</v>
+      </c>
+      <c r="D81">
+        <v>445.5907278586985</v>
+      </c>
+      <c r="E81">
+        <v>-0.9242610110350561</v>
+      </c>
+      <c r="F81">
+        <v>0.3558506772991563</v>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>ssid_heat</t>
         </is>
@@ -2079,7 +3548,7 @@
         <v>1.099842046264552</v>
       </c>
       <c r="E2">
-        <v>0.9525</v>
+        <v>0.9675</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2139,7 +3608,7 @@
         <v>1.099842046264552</v>
       </c>
       <c r="E5">
-        <v>0.9399999999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2163,7 +3632,7 @@
         <v>1.028380681908756</v>
       </c>
       <c r="E6">
-        <v>0.765</v>
+        <v>0.755</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2223,7 +3692,7 @@
         <v>1.028380681908756</v>
       </c>
       <c r="E9">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2247,7 +3716,7 @@
         <v>0.9846049942494004</v>
       </c>
       <c r="E10">
-        <v>0.35</v>
+        <v>0.3525</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2307,7 +3776,7 @@
         <v>0.9846049942494004</v>
       </c>
       <c r="E13">
-        <v>0.4</v>
+        <v>0.3625</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2331,7 +3800,7 @@
         <v>1.0879677294264</v>
       </c>
       <c r="E14">
-        <v>0.985</v>
+        <v>0.9925</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2391,7 +3860,7 @@
         <v>1.0879677294264</v>
       </c>
       <c r="E17">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>

--- a/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
+++ b/outputs/photosynthesis/coral_FvFm_GAMM_stats.xlsx
@@ -19,6 +19,245 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="78">
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>dev_expl</t>
+  </si>
+  <si>
+    <t>r_sq_adj</t>
+  </si>
+  <si>
+    <t>ofav_control</t>
+  </si>
+  <si>
+    <t>ofav_heat</t>
+  </si>
+  <si>
+    <t>ssid_control</t>
+  </si>
+  <si>
+    <t>ssid_heat</t>
+  </si>
+  <si>
+    <t>rho</t>
+  </si>
+  <si>
+    <t>AR1_applied</t>
+  </si>
+  <si>
+    <t>model term</t>
+  </si>
+  <si>
+    <t>df1</t>
+  </si>
+  <si>
+    <t>df2</t>
+  </si>
+  <si>
+    <t>F_value</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>partial_R2</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>(confounded)</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>t_ratio</t>
+  </si>
+  <si>
+    <t>overall mean</t>
+  </si>
+  <si>
+    <t>treatment CC</t>
+  </si>
+  <si>
+    <t>treatment LC</t>
+  </si>
+  <si>
+    <t>treatment CH</t>
+  </si>
+  <si>
+    <t>treatment LH</t>
+  </si>
+  <si>
+    <t>site Emerald</t>
+  </si>
+  <si>
+    <t>site Rainbow</t>
+  </si>
+  <si>
+    <t>site Star</t>
+  </si>
+  <si>
+    <t>site MacN</t>
+  </si>
+  <si>
+    <t>treatment x site CC : Emerald</t>
+  </si>
+  <si>
+    <t>treatment x site LC : Emerald</t>
+  </si>
+  <si>
+    <t>treatment x site CH : Emerald</t>
+  </si>
+  <si>
+    <t>treatment x site LH : Emerald</t>
+  </si>
+  <si>
+    <t>treatment x site CC : Rainbow</t>
+  </si>
+  <si>
+    <t>treatment x site LC : Rainbow</t>
+  </si>
+  <si>
+    <t>treatment x site CH : Rainbow</t>
+  </si>
+  <si>
+    <t>treatment x site LH : Rainbow</t>
+  </si>
+  <si>
+    <t>treatment x site CC : Star</t>
+  </si>
+  <si>
+    <t>treatment x site LC : Star</t>
+  </si>
+  <si>
+    <t>treatment x site CH : Star</t>
+  </si>
+  <si>
+    <t>treatment x site LH : Star</t>
+  </si>
+  <si>
+    <t>treatment x site CC : MacN</t>
+  </si>
+  <si>
+    <t>treatment x site LC : MacN</t>
+  </si>
+  <si>
+    <t>treatment x site CH : MacN</t>
+  </si>
+  <si>
+    <t>treatment x site LH : MacN</t>
+  </si>
+  <si>
+    <t>edf</t>
+  </si>
+  <si>
+    <t>ref_df</t>
+  </si>
+  <si>
+    <t>s(time)</t>
+  </si>
+  <si>
+    <t>s(treatment,time)</t>
+  </si>
+  <si>
+    <t>s(site,time)</t>
+  </si>
+  <si>
+    <t>s(time,exp_unit)</t>
+  </si>
+  <si>
+    <t>k'</t>
+  </si>
+  <si>
+    <t>k-index</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>emmean</t>
+  </si>
+  <si>
+    <t>lower.CL</t>
+  </si>
+  <si>
+    <t>upper.CL</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Emerald</t>
+  </si>
+  <si>
+    <t>LC</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>LH</t>
+  </si>
+  <si>
+    <t>Rainbow</t>
+  </si>
+  <si>
+    <t>Star</t>
+  </si>
+  <si>
+    <t>MacN</t>
+  </si>
+  <si>
+    <t>contrast</t>
+  </si>
+  <si>
+    <t>t.ratio</t>
+  </si>
+  <si>
+    <t>p.value</t>
+  </si>
+  <si>
+    <t>CC - LC</t>
+  </si>
+  <si>
+    <t>CC - CH</t>
+  </si>
+  <si>
+    <t>CC - LH</t>
+  </si>
+  <si>
+    <t>LC - CH</t>
+  </si>
+  <si>
+    <t>LC - LH</t>
+  </si>
+  <si>
+    <t>CH - LH</t>
+  </si>
+  <si>
+    <t>urban - reef</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -362,28 +601,20 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>dev_expl</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>r_sq_adj</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0.9894466613071081</v>
@@ -392,11 +623,9 @@
         <v>0.9809056986485363</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0.9453687883060539</v>
@@ -405,11 +634,9 @@
         <v>0.9284599001278659</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>0.9818942192876795</v>
@@ -418,11 +645,9 @@
         <v>0.9710235261278897</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0.9364195852024547</v>
@@ -441,28 +666,20 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>rho</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AR1_applied</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0.1503993127597375</v>
@@ -471,11 +688,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0.6195395654087178</v>
@@ -484,11 +699,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>0.3464358487520589</v>
@@ -497,11 +710,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0.3631448680976758</v>
@@ -520,48 +731,32 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model term</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>df1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>df2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F_value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>partial_R2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>15</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -575,20 +770,16 @@
       <c r="E2">
         <v>9.098178860052314E-07</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
+      <c r="F2" t="s">
+        <v>3</v>
       </c>
       <c r="G2">
         <v>0.1610882868388543</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>16</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -602,20 +793,16 @@
       <c r="E3">
         <v>1.086170188016442E-18</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
+      <c r="F3" t="s">
+        <v>3</v>
       </c>
       <c r="G3">
         <v>0.3897405352309894</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>(confounded)</t>
-        </is>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>17</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -629,20 +816,16 @@
       <c r="E4">
         <v>0.0001586072544670175</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
+      <c r="F4" t="s">
+        <v>3</v>
       </c>
       <c r="G4">
         <v>0.1666785576689831</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>15</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -656,20 +839,16 @@
       <c r="E5">
         <v>0.3522617877449978</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
+      <c r="F5" t="s">
+        <v>4</v>
       </c>
       <c r="G5">
         <v>0.002096040731365908</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>16</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -683,20 +862,16 @@
       <c r="E6">
         <v>9.414990521751983E-05</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
+      <c r="F6" t="s">
+        <v>4</v>
       </c>
       <c r="G6">
         <v>0.05008146695755434</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>(confounded)</t>
-        </is>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>17</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -710,20 +885,16 @@
       <c r="E7">
         <v>0.03036127443420184</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
+      <c r="F7" t="s">
+        <v>4</v>
       </c>
       <c r="G7">
         <v>0.02135488658698791</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>15</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -737,20 +908,16 @@
       <c r="E8">
         <v>5.605917226991051E-17</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
+      <c r="F8" t="s">
+        <v>5</v>
       </c>
       <c r="G8">
         <v>0.2336474285506848</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>16</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -764,20 +931,16 @@
       <c r="E9">
         <v>0.2101118976470116</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
+      <c r="F9" t="s">
+        <v>5</v>
       </c>
       <c r="G9">
         <v>0.01516489448552321</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>(confounded)</t>
-        </is>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>17</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -791,20 +954,16 @@
       <c r="E10">
         <v>0.4686063495239394</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
+      <c r="F10" t="s">
+        <v>5</v>
       </c>
       <c r="G10">
         <v>0.02856616958266638</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>15</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -818,20 +977,16 @@
       <c r="E11">
         <v>0.2551891689128769</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="F11" t="s">
+        <v>6</v>
       </c>
       <c r="G11">
         <v>0.002904530889171336</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>16</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -845,20 +1000,16 @@
       <c r="E12">
         <v>0.7328822458621018</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="F12" t="s">
+        <v>6</v>
       </c>
       <c r="G12">
         <v>0.002873293143033607</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>(confounded)</t>
-        </is>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>17</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -872,10 +1023,8 @@
       <c r="E13">
         <v>0.5247183317044345</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="F13" t="s">
+        <v>6</v>
       </c>
       <c r="G13">
         <v>0.005001898041667598</v>
@@ -891,48 +1040,32 @@
   <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>t_ratio</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>overall mean</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>23</v>
       </c>
       <c r="B2">
         <v>0.4356588237227743</v>
@@ -943,17 +1076,13 @@
       <c r="D2">
         <v>175.2045442285989</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>treatment CC</t>
-        </is>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>24</v>
       </c>
       <c r="B3">
         <v>-0.009736001586646496</v>
@@ -970,17 +1099,13 @@
       <c r="F3">
         <v>0.1591944326277489</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>treatment LC</t>
-        </is>
+      <c r="G3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>25</v>
       </c>
       <c r="B4">
         <v>-0.04015305218057764</v>
@@ -997,17 +1122,13 @@
       <c r="F4">
         <v>2.844113068834794E-06</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>treatment CH</t>
-        </is>
+      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0.009141159838930216</v>
@@ -1024,17 +1145,13 @@
       <c r="F5">
         <v>0.1396115357719038</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>treatment LH</t>
-        </is>
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>27</v>
       </c>
       <c r="B6">
         <v>0.04074789392829394</v>
@@ -1051,17 +1168,13 @@
       <c r="F6">
         <v>1.310841084099791E-05</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>site Emerald</t>
-        </is>
+      <c r="G6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>28</v>
       </c>
       <c r="B7">
         <v>-0.05638290572290167</v>
@@ -1078,17 +1191,13 @@
       <c r="F7">
         <v>1.945860798849331E-13</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>site Rainbow</t>
-        </is>
+      <c r="G7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>29</v>
       </c>
       <c r="B8">
         <v>-0.02638840336268705</v>
@@ -1105,17 +1214,13 @@
       <c r="F8">
         <v>0.003407430084079613</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>site Star</t>
-        </is>
+      <c r="G8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>30</v>
       </c>
       <c r="B9">
         <v>0.0408901940722853</v>
@@ -1132,17 +1237,13 @@
       <c r="F9">
         <v>5.231526800093123E-07</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>site MacN</t>
-        </is>
+      <c r="G9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>31</v>
       </c>
       <c r="B10">
         <v>0.04188111501330342</v>
@@ -1159,17 +1260,13 @@
       <c r="F10">
         <v>3.523502928324561E-09</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>treatment x site CC : Emerald</t>
-        </is>
+      <c r="G10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>32</v>
       </c>
       <c r="B11">
         <v>-0.002966864249419228</v>
@@ -1186,17 +1283,13 @@
       <c r="F11">
         <v>0.787305858791389</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>treatment x site LC : Emerald</t>
-        </is>
+      <c r="G11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>33</v>
       </c>
       <c r="B12">
         <v>-0.02695920361061325</v>
@@ -1213,17 +1306,13 @@
       <c r="F12">
         <v>0.05028606800358819</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Emerald</t>
-        </is>
+      <c r="G12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>34</v>
       </c>
       <c r="B13">
         <v>0.01363938585106467</v>
@@ -1240,17 +1329,13 @@
       <c r="F13">
         <v>0.1792296710329647</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Emerald</t>
-        </is>
+      <c r="G13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>35</v>
       </c>
       <c r="B14">
         <v>0.0162866820089678</v>
@@ -1267,17 +1352,13 @@
       <c r="F14">
         <v>0.2132290393411336</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>treatment x site CC : Rainbow</t>
-        </is>
+      <c r="G14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>36</v>
       </c>
       <c r="B15">
         <v>0.001757308499439142</v>
@@ -1294,17 +1375,13 @@
       <c r="F15">
         <v>0.8910973194922308</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>treatment x site LC : Rainbow</t>
-        </is>
+      <c r="G15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>37</v>
       </c>
       <c r="B16">
         <v>0.02879976972363645</v>
@@ -1321,17 +1398,13 @@
       <c r="F16">
         <v>0.1019235878615577</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Rainbow</t>
-        </is>
+      <c r="G16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>38</v>
       </c>
       <c r="B17">
         <v>-0.01320286419554454</v>
@@ -1348,17 +1421,13 @@
       <c r="F17">
         <v>0.2499133217254166</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Rainbow</t>
-        </is>
+      <c r="G17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>39</v>
       </c>
       <c r="B18">
         <v>-0.01735421402753106</v>
@@ -1375,17 +1444,13 @@
       <c r="F18">
         <v>0.3333984872000813</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>treatment x site CC : Star</t>
-        </is>
+      <c r="G18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>40</v>
       </c>
       <c r="B19">
         <v>-0.002172922636580001</v>
@@ -1402,17 +1467,13 @@
       <c r="F19">
         <v>0.8580451812037124</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>treatment x site LC : Star</t>
-        </is>
+      <c r="G19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>41</v>
       </c>
       <c r="B20">
         <v>-0.001133952772531416</v>
@@ -1429,17 +1490,13 @@
       <c r="F20">
         <v>0.9270266149050699</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Star</t>
-        </is>
+      <c r="G20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>42</v>
       </c>
       <c r="B21">
         <v>0.00174424815357149</v>
@@ -1456,17 +1513,13 @@
       <c r="F21">
         <v>0.8702522770598331</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Star</t>
-        </is>
+      <c r="G21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>43</v>
       </c>
       <c r="B22">
         <v>0.001562627255539926</v>
@@ -1483,17 +1536,13 @@
       <c r="F22">
         <v>0.928572089342566</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>treatment x site CC : MacN</t>
-        </is>
+      <c r="G22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>44</v>
       </c>
       <c r="B23">
         <v>0.003382478386560086</v>
@@ -1510,17 +1559,13 @@
       <c r="F23">
         <v>0.7538352726621881</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>treatment x site LC : MacN</t>
-        </is>
+      <c r="G23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>45</v>
       </c>
       <c r="B24">
         <v>-0.0007066133404917858</v>
@@ -1537,17 +1582,13 @@
       <c r="F24">
         <v>0.9543745512840482</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>treatment x site CH : MacN</t>
-        </is>
+      <c r="G24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>46</v>
       </c>
       <c r="B25">
         <v>-0.002180769809091622</v>
@@ -1564,17 +1605,13 @@
       <c r="F25">
         <v>0.820076837028819</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>treatment x site LH : MacN</t>
-        </is>
+      <c r="G25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>47</v>
       </c>
       <c r="B26">
         <v>-0.0004950952369766819</v>
@@ -1591,17 +1628,13 @@
       <c r="F26">
         <v>0.9693354962098961</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>overall mean</t>
-        </is>
+      <c r="G26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>23</v>
       </c>
       <c r="B27">
         <v>0.3719293947695835</v>
@@ -1612,17 +1645,13 @@
       <c r="D27">
         <v>412.7735348871453</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>treatment CH</t>
-        </is>
+      <c r="G27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>26</v>
       </c>
       <c r="B28">
         <v>0.007106843717662075</v>
@@ -1639,17 +1668,13 @@
       <c r="F28">
         <v>0.3522617877451257</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>treatment LH</t>
-        </is>
+      <c r="G28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>27</v>
       </c>
       <c r="B29">
         <v>-0.007106843717662075</v>
@@ -1666,17 +1691,13 @@
       <c r="F29">
         <v>0.3522617877451257</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>site Emerald</t>
-        </is>
+      <c r="G29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>28</v>
       </c>
       <c r="B30">
         <v>-0.04042730096006027</v>
@@ -1693,17 +1714,13 @@
       <c r="F30">
         <v>0.00119311679529951</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>site Rainbow</t>
-        </is>
+      <c r="G30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>29</v>
       </c>
       <c r="B31">
         <v>-0.02205637281695993</v>
@@ -1720,17 +1737,13 @@
       <c r="F31">
         <v>0.1501369990154243</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>site Star</t>
-        </is>
+      <c r="G31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>30</v>
       </c>
       <c r="B32">
         <v>0.02449281209745503</v>
@@ -1747,17 +1760,13 @@
       <c r="F32">
         <v>0.04320213056575246</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>site MacN</t>
-        </is>
+      <c r="G32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>31</v>
       </c>
       <c r="B33">
         <v>0.03799086167956518</v>
@@ -1774,17 +1783,13 @@
       <c r="F33">
         <v>0.0009713117844537503</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Emerald</t>
-        </is>
+      <c r="G33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>34</v>
       </c>
       <c r="B34">
         <v>-0.001810014991857307</v>
@@ -1801,17 +1806,13 @@
       <c r="F34">
         <v>0.8829147627075981</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Emerald</t>
-        </is>
+      <c r="G34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>35</v>
       </c>
       <c r="B35">
         <v>0.001810014991857307</v>
@@ -1828,17 +1829,13 @@
       <c r="F35">
         <v>0.8829147627075981</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Rainbow</t>
-        </is>
+      <c r="G35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>38</v>
       </c>
       <c r="B36">
         <v>-0.01570012600732737</v>
@@ -1855,17 +1852,13 @@
       <c r="F36">
         <v>0.3018644722364796</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Rainbow</t>
-        </is>
+      <c r="G36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>39</v>
       </c>
       <c r="B37">
         <v>0.01570012600732737</v>
@@ -1882,17 +1875,13 @@
       <c r="F37">
         <v>0.3018644722364796</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Star</t>
-        </is>
+      <c r="G37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>42</v>
       </c>
       <c r="B38">
         <v>0.01637890554684138</v>
@@ -1909,17 +1898,13 @@
       <c r="F38">
         <v>0.1748644072510913</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Star</t>
-        </is>
+      <c r="G38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>43</v>
       </c>
       <c r="B39">
         <v>-0.01637890554684138</v>
@@ -1936,17 +1921,13 @@
       <c r="F39">
         <v>0.1748644072510913</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>treatment x site CH : MacN</t>
-        </is>
+      <c r="G39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>46</v>
       </c>
       <c r="B40">
         <v>0.001131235452343272</v>
@@ -1963,17 +1944,13 @@
       <c r="F40">
         <v>0.9205703758899153</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>treatment x site LH : MacN</t>
-        </is>
+      <c r="G40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>47</v>
       </c>
       <c r="B41">
         <v>-0.001131235452343272</v>
@@ -1990,17 +1967,13 @@
       <c r="F41">
         <v>0.9205703758899153</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>overall mean</t>
-        </is>
+      <c r="G41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>23</v>
       </c>
       <c r="B42">
         <v>0.33039078394576</v>
@@ -2011,17 +1984,13 @@
       <c r="D42">
         <v>295.551040775367</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>treatment CC</t>
-        </is>
+      <c r="G42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>24</v>
       </c>
       <c r="B43">
         <v>0.05350051621656567</v>
@@ -2038,17 +2007,13 @@
       <c r="F43">
         <v>7.248968391100128E-13</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>treatment LC</t>
-        </is>
+      <c r="G43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>25</v>
       </c>
       <c r="B44">
         <v>0.02008407258272527</v>
@@ -2065,17 +2030,13 @@
       <c r="F44">
         <v>0.004328155502998678</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>treatment CH</t>
-        </is>
+      <c r="G44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>26</v>
       </c>
       <c r="B45">
         <v>-0.04062291823915393</v>
@@ -2092,17 +2053,13 @@
       <c r="F45">
         <v>1.566899238762987E-08</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>treatment LH</t>
-        </is>
+      <c r="G45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>27</v>
       </c>
       <c r="B46">
         <v>-0.03296167056013703</v>
@@ -2119,17 +2076,13 @@
       <c r="F46">
         <v>3.664707731085024E-06</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>site Emerald</t>
-        </is>
+      <c r="G46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>28</v>
       </c>
       <c r="B47">
         <v>0.002007308538242901</v>
@@ -2146,17 +2099,13 @@
       <c r="F47">
         <v>0.7740151619469204</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>site Rainbow</t>
-        </is>
+      <c r="G47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>29</v>
       </c>
       <c r="B48">
         <v>-0.01225241774208586</v>
@@ -2173,17 +2122,13 @@
       <c r="F48">
         <v>0.08041295627102457</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>site Star</t>
-        </is>
+      <c r="G48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>30</v>
       </c>
       <c r="B49">
         <v>0.01175297809753159</v>
@@ -2200,17 +2145,13 @@
       <c r="F49">
         <v>0.09339635142248127</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>site MacN</t>
-        </is>
+      <c r="G49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>31</v>
       </c>
       <c r="B50">
         <v>-0.001507868893688637</v>
@@ -2227,17 +2168,13 @@
       <c r="F50">
         <v>0.8326018149063582</v>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>treatment x site CC : Emerald</t>
-        </is>
+      <c r="G50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>32</v>
       </c>
       <c r="B51">
         <v>0.01657228430371942</v>
@@ -2254,17 +2191,13 @@
       <c r="F51">
         <v>0.173031042054588</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>treatment x site LC : Emerald</t>
-        </is>
+      <c r="G51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>33</v>
       </c>
       <c r="B52">
         <v>0.01735364050407546</v>
@@ -2281,17 +2214,13 @@
       <c r="F52">
         <v>0.150895662601481</v>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Emerald</t>
-        </is>
+      <c r="G52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>34</v>
       </c>
       <c r="B53">
         <v>-0.02572622048959259</v>
@@ -2308,17 +2237,13 @@
       <c r="F53">
         <v>0.03359049559057953</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Emerald</t>
-        </is>
+      <c r="G53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>35</v>
       </c>
       <c r="B54">
         <v>-0.008199704318202284</v>
@@ -2335,17 +2260,13 @@
       <c r="F54">
         <v>0.496746309202207</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>treatment x site CC : Rainbow</t>
-        </is>
+      <c r="G54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>36</v>
       </c>
       <c r="B55">
         <v>-0.001692868105693667</v>
@@ -2362,17 +2283,13 @@
       <c r="F55">
         <v>0.8891341095908338</v>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>treatment x site LC : Rainbow</t>
-        </is>
+      <c r="G55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>37</v>
       </c>
       <c r="B56">
         <v>-0.01450209518148572</v>
@@ -2389,17 +2306,13 @@
       <c r="F56">
         <v>0.2297580717222444</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Rainbow</t>
-        </is>
+      <c r="G56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>38</v>
       </c>
       <c r="B57">
         <v>0.005639251632298061</v>
@@ -2416,17 +2329,13 @@
       <c r="F57">
         <v>0.6401451699196075</v>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Rainbow</t>
-        </is>
+      <c r="G57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>39</v>
       </c>
       <c r="B58">
         <v>0.01055571165488133</v>
@@ -2443,17 +2352,13 @@
       <c r="F58">
         <v>0.3817551719459478</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>treatment x site CC : Star</t>
-        </is>
+      <c r="G58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>40</v>
       </c>
       <c r="B59">
         <v>-0.01594365097254844</v>
@@ -2470,17 +2375,13 @@
       <c r="F59">
         <v>0.1898586243441945</v>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>treatment x site LC : Star</t>
-        </is>
+      <c r="G59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>41</v>
       </c>
       <c r="B60">
         <v>0.002146440207609335</v>
@@ -2497,17 +2398,13 @@
       <c r="F60">
         <v>0.8587474944770664</v>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Star</t>
-        </is>
+      <c r="G60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>42</v>
       </c>
       <c r="B61">
         <v>0.01039399198063545</v>
@@ -2524,17 +2421,13 @@
       <c r="F61">
         <v>0.3890819459952305</v>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Star</t>
-        </is>
+      <c r="G61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>43</v>
       </c>
       <c r="B62">
         <v>0.003403218784303663</v>
@@ -2551,17 +2444,13 @@
       <c r="F62">
         <v>0.7778199247702895</v>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>treatment x site CC : MacN</t>
-        </is>
+      <c r="G62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>44</v>
       </c>
       <c r="B63">
         <v>0.001064234774522691</v>
@@ -2578,17 +2467,13 @@
       <c r="F63">
         <v>0.9340944271399774</v>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>treatment x site LC : MacN</t>
-        </is>
+      <c r="G63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>45</v>
       </c>
       <c r="B64">
         <v>-0.004997985530199068</v>
@@ -2605,17 +2490,13 @@
       <c r="F64">
         <v>0.680699336247149</v>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>treatment x site CH : MacN</t>
-        </is>
+      <c r="G64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>46</v>
       </c>
       <c r="B65">
         <v>0.009692976876659086</v>
@@ -2632,17 +2513,13 @@
       <c r="F65">
         <v>0.4250125410162635</v>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>treatment x site LH : MacN</t>
-        </is>
+      <c r="G65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>47</v>
       </c>
       <c r="B66">
         <v>-0.005759226120982705</v>
@@ -2659,17 +2536,13 @@
       <c r="F66">
         <v>0.6353833601244647</v>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>overall mean</t>
-        </is>
+      <c r="G66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>23</v>
       </c>
       <c r="B67">
         <v>0.2997854549076612</v>
@@ -2680,17 +2553,13 @@
       <c r="D67">
         <v>445.5907278586985</v>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>treatment CH</t>
-        </is>
+      <c r="G67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>26</v>
       </c>
       <c r="B68">
         <v>0.00681730462960672</v>
@@ -2707,17 +2576,13 @@
       <c r="F68">
         <v>0.2551891689127502</v>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>treatment LH</t>
-        </is>
+      <c r="G68" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>27</v>
       </c>
       <c r="B69">
         <v>-0.00681730462960672</v>
@@ -2734,17 +2599,13 @@
       <c r="F69">
         <v>0.2551891689127502</v>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>site Emerald</t>
-        </is>
+      <c r="G69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>28</v>
       </c>
       <c r="B70">
         <v>0.0009454295200049829</v>
@@ -2761,17 +2622,13 @@
       <c r="F70">
         <v>0.9454858939566231</v>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>site Rainbow</t>
-        </is>
+      <c r="G70" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>29</v>
       </c>
       <c r="B71">
         <v>-0.006492578208423886</v>
@@ -2788,17 +2645,13 @@
       <c r="F71">
         <v>0.6521873154217532</v>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>site Star</t>
-        </is>
+      <c r="G71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>30</v>
       </c>
       <c r="B72">
         <v>-0.005120783672600618</v>
@@ -2815,17 +2668,13 @@
       <c r="F72">
         <v>0.5383172526093408</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>site MacN</t>
-        </is>
+      <c r="G72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>31</v>
       </c>
       <c r="B73">
         <v>0.01066793236101926</v>
@@ -2842,17 +2691,13 @@
       <c r="F73">
         <v>0.2989334455417383</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Emerald</t>
-        </is>
+      <c r="G73" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>34</v>
       </c>
       <c r="B74">
         <v>-0.0112139561636805</v>
@@ -2869,17 +2714,13 @@
       <c r="F74">
         <v>0.1658316239187297</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Emerald</t>
-        </is>
+      <c r="G74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>35</v>
       </c>
       <c r="B75">
         <v>0.0112139561636805</v>
@@ -2896,17 +2737,13 @@
       <c r="F75">
         <v>0.1658316239187297</v>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Rainbow</t>
-        </is>
+      <c r="G75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>38</v>
       </c>
       <c r="B76">
         <v>0.0007301870897695557</v>
@@ -2923,17 +2760,13 @@
       <c r="F76">
         <v>0.9288722013095607</v>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Rainbow</t>
-        </is>
+      <c r="G76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>39</v>
       </c>
       <c r="B77">
         <v>-0.0007301870897695557</v>
@@ -2950,17 +2783,13 @@
       <c r="F77">
         <v>0.9288722013095607</v>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>treatment x site CH : Star</t>
-        </is>
+      <c r="G77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>42</v>
       </c>
       <c r="B78">
         <v>0.002999498040475423</v>
@@ -2977,17 +2806,13 @@
       <c r="F78">
         <v>0.706914154744372</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>treatment x site LH : Star</t>
-        </is>
+      <c r="G78" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>43</v>
       </c>
       <c r="B79">
         <v>-0.002999498040475423</v>
@@ -3004,17 +2829,13 @@
       <c r="F79">
         <v>0.706914154744372</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>treatment x site CH : MacN</t>
-        </is>
+      <c r="G79" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>46</v>
       </c>
       <c r="B80">
         <v>0.00748427103343552</v>
@@ -3031,17 +2852,13 @@
       <c r="F80">
         <v>0.3558506772991563</v>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>treatment x site LH : MacN</t>
-        </is>
+      <c r="G80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>47</v>
       </c>
       <c r="B81">
         <v>-0.00748427103343552</v>
@@ -3058,10 +2875,8 @@
       <c r="F81">
         <v>0.3558506772991563</v>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="G81" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3074,43 +2889,29 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>edf</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ref_df</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F_value</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>50</v>
       </c>
       <c r="B2">
         <v>4.207660424272711</v>
@@ -3124,17 +2925,13 @@
       <c r="E2">
         <v>8.745205310189963E-06</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>51</v>
       </c>
       <c r="B3">
         <v>13.51044370129423</v>
@@ -3148,17 +2945,13 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>52</v>
       </c>
       <c r="B4">
         <v>9.359525948867519</v>
@@ -3172,17 +2965,13 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>53</v>
       </c>
       <c r="B5">
         <v>105.7178256969666</v>
@@ -3196,17 +2985,13 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>50</v>
       </c>
       <c r="B6">
         <v>4.216082931460624</v>
@@ -3220,17 +3005,13 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+      <c r="F6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>51</v>
       </c>
       <c r="B7">
         <v>8.02834592507161</v>
@@ -3244,17 +3025,13 @@
       <c r="E7">
         <v>0.01128697896204423</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>52</v>
       </c>
       <c r="B8">
         <v>7.331844532540197</v>
@@ -3268,17 +3045,13 @@
       <c r="E8">
         <v>0.0004214248467943049</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>53</v>
       </c>
       <c r="B9">
         <v>105.6501917237823</v>
@@ -3292,17 +3065,13 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+      <c r="F9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>50</v>
       </c>
       <c r="B10">
         <v>4.720206646905807</v>
@@ -3316,17 +3085,13 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>51</v>
       </c>
       <c r="B11">
         <v>13.54705390654074</v>
@@ -3340,17 +3105,13 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>52</v>
       </c>
       <c r="B12">
         <v>9.312880779257217</v>
@@ -3364,17 +3125,13 @@
       <c r="E12">
         <v>0.5644261244700017</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>53</v>
       </c>
       <c r="B13">
         <v>140.8688178919291</v>
@@ -3388,17 +3145,13 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+      <c r="F13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>50</v>
       </c>
       <c r="B14">
         <v>9.531246996852431</v>
@@ -3412,17 +3165,13 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>51</v>
       </c>
       <c r="B15">
         <v>5.862474849613238</v>
@@ -3436,17 +3185,13 @@
       <c r="E15">
         <v>0.3184920484690186</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>52</v>
       </c>
       <c r="B16">
         <v>16.0786169120118</v>
@@ -3460,17 +3205,13 @@
       <c r="E16">
         <v>3.175226413731913E-05</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>53</v>
       </c>
       <c r="B17">
         <v>229.9369333828239</v>
@@ -3484,10 +3225,8 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="F17" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3500,43 +3239,29 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>k'</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>edf</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>k-index</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>50</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -3548,19 +3273,15 @@
         <v>1.099842046264552</v>
       </c>
       <c r="E2">
-        <v>0.9675</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>51</v>
       </c>
       <c r="B3">
         <v>18</v>
@@ -3568,17 +3289,13 @@
       <c r="C3">
         <v>13.51044370129423</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>52</v>
       </c>
       <c r="B4">
         <v>18</v>
@@ -3586,17 +3303,13 @@
       <c r="C4">
         <v>9.359525948867519</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>53</v>
       </c>
       <c r="B5">
         <v>318</v>
@@ -3608,19 +3321,15 @@
         <v>1.099842046264552</v>
       </c>
       <c r="E5">
-        <v>0.9375</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+        <v>0.9775</v>
+      </c>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>50</v>
       </c>
       <c r="B6">
         <v>13</v>
@@ -3632,19 +3341,15 @@
         <v>1.028380681908756</v>
       </c>
       <c r="E6">
-        <v>0.755</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+        <v>0.715</v>
+      </c>
+      <c r="F6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>51</v>
       </c>
       <c r="B7">
         <v>14</v>
@@ -3652,17 +3357,13 @@
       <c r="C7">
         <v>8.02834592507161</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>52</v>
       </c>
       <c r="B8">
         <v>42</v>
@@ -3670,17 +3371,13 @@
       <c r="C8">
         <v>7.331844532540197</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>53</v>
       </c>
       <c r="B9">
         <v>742</v>
@@ -3692,19 +3389,15 @@
         <v>1.028380681908756</v>
       </c>
       <c r="E9">
-        <v>0.75</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+        <v>0.705</v>
+      </c>
+      <c r="F9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>50</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -3716,19 +3409,15 @@
         <v>0.9846049942494004</v>
       </c>
       <c r="E10">
-        <v>0.3525</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+        <v>0.33</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>51</v>
       </c>
       <c r="B11">
         <v>18</v>
@@ -3736,17 +3425,13 @@
       <c r="C11">
         <v>13.54705390654074</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>52</v>
       </c>
       <c r="B12">
         <v>18</v>
@@ -3754,17 +3439,13 @@
       <c r="C12">
         <v>9.312880779257217</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>53</v>
       </c>
       <c r="B13">
         <v>474</v>
@@ -3776,19 +3457,15 @@
         <v>0.9846049942494004</v>
       </c>
       <c r="E13">
-        <v>0.3625</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>s(time)</t>
-        </is>
+        <v>0.3325</v>
+      </c>
+      <c r="F13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>50</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -3802,17 +3479,13 @@
       <c r="E14">
         <v>0.9925</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>s(treatment,time)</t>
-        </is>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>51</v>
       </c>
       <c r="B15">
         <v>13</v>
@@ -3820,17 +3493,13 @@
       <c r="C15">
         <v>5.862474849613238</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>s(site,time)</t>
-        </is>
+      <c r="F15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>52</v>
       </c>
       <c r="B16">
         <v>39</v>
@@ -3838,17 +3507,13 @@
       <c r="C16">
         <v>16.0786169120118</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>s(time,exp_unit)</t>
-        </is>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>53</v>
       </c>
       <c r="B17">
         <v>1027</v>
@@ -3860,12 +3525,10 @@
         <v>1.0879677294264</v>
       </c>
       <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+        <v>0.9925</v>
+      </c>
+      <c r="F17" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3878,58 +3541,38 @@
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>emmean</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>lower.CL</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>upper.CL</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
       </c>
       <c r="C2">
         <v>0.3665730521638069</v>
@@ -3946,22 +3589,16 @@
       <c r="G2">
         <v>0.3935026795323678</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
       </c>
       <c r="C3">
         <v>0.3121636622086817</v>
@@ -3978,22 +3615,16 @@
       <c r="G3">
         <v>0.3501262150356518</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
       </c>
       <c r="C4">
         <v>0.4020564636898675</v>
@@ -4010,22 +3641,16 @@
       <c r="G4">
         <v>0.4261619328251272</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
       </c>
       <c r="C5">
         <v>0.4363104939371344</v>
@@ -4042,22 +3667,16 @@
       <c r="G5">
         <v>0.4674106961328804</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
       </c>
       <c r="C6">
         <v>0.4012917272728799</v>
@@ -4074,22 +3693,16 @@
       <c r="G6">
         <v>0.4323620183943441</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
       </c>
       <c r="C7">
         <v>0.397917137903146</v>
@@ -4106,22 +3719,16 @@
       <c r="G7">
         <v>0.4514620717274213</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
       </c>
       <c r="C8">
         <v>0.4052087160034729</v>
@@ -4138,22 +3745,16 @@
       <c r="G8">
         <v>0.4293527733174747</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
       </c>
       <c r="C9">
         <v>0.4326641002608501</v>
@@ -4170,22 +3771,16 @@
       <c r="G9">
         <v>0.4862305969188274</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
       </c>
       <c r="C10">
         <v>0.4646400935718331</v>
@@ -4202,22 +3797,16 @@
       <c r="G10">
         <v>0.4956867873376183</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
       </c>
       <c r="C11">
         <v>0.4352620128419505</v>
@@ -4234,22 +3823,16 @@
       <c r="G11">
         <v>0.4622286072881088</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
       </c>
       <c r="C12">
         <v>0.4874344257875612</v>
@@ -4266,22 +3849,16 @@
       <c r="G12">
         <v>0.5115505084558299</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
       </c>
       <c r="C13">
         <v>0.5188595389788935</v>
@@ -4298,22 +3875,16 @@
       <c r="G13">
         <v>0.5724080749643885</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
       </c>
       <c r="C14">
         <v>0.4711864155359914</v>
@@ -4330,22 +3901,16 @@
       <c r="G14">
         <v>0.4981063488718818</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
       </c>
       <c r="C15">
         <v>0.4366802732150084</v>
@@ -4362,22 +3927,16 @@
       <c r="G15">
         <v>0.4677466165897752</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
       </c>
       <c r="C16">
         <v>0.4845003287659163</v>
@@ -4394,22 +3953,16 @@
       <c r="G16">
         <v>0.506522447858513</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
       </c>
       <c r="C17">
         <v>0.517792737427395</v>
@@ -4426,22 +3979,16 @@
       <c r="G17">
         <v>0.5488880435892448</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
       </c>
       <c r="C18">
         <v>0.3367989225353282</v>
@@ -4458,22 +4005,16 @@
       <c r="G18">
         <v>0.3690124943368207</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
       </c>
       <c r="C19">
         <v>0.3262052650837182</v>
@@ -4490,22 +4031,16 @@
       <c r="G19">
         <v>0.3714809972388229</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
       </c>
       <c r="C20">
         <v>0.3412797396629584</v>
@@ -4522,22 +4057,16 @@
       <c r="G20">
         <v>0.3761404573933799</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
       </c>
       <c r="C21">
         <v>0.3584663042422886</v>
@@ -4554,22 +4083,16 @@
       <c r="G21">
         <v>0.4242412344037373</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
       </c>
       <c r="C22">
         <v>0.4199079561315421</v>
@@ -4586,22 +4109,16 @@
       <c r="G22">
         <v>0.4531425306494883</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
       </c>
       <c r="C23">
         <v>0.3729364576025348</v>
@@ -4618,22 +4135,16 @@
       <c r="G23">
         <v>0.4147641438273212</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
       </c>
       <c r="C24">
         <v>0.4181583356191542</v>
@@ -4650,22 +4161,16 @@
       <c r="G24">
         <v>0.4476280218188743</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s">
+        <v>67</v>
       </c>
       <c r="C25">
         <v>0.4016821772791432</v>
@@ -4682,22 +4187,16 @@
       <c r="G25">
         <v>0.4396375187906861</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
       </c>
       <c r="C26">
         <v>0.402470893004288</v>
@@ -4714,22 +4213,16 @@
       <c r="G26">
         <v>0.4340951821603005</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
       </c>
       <c r="C27">
         <v>0.3698358055708036</v>
@@ -4746,22 +4239,16 @@
       <c r="G27">
         <v>0.4014594557202249</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
       </c>
       <c r="C28">
         <v>0.2660489537552564</v>
@@ -4778,22 +4265,16 @@
       <c r="G28">
         <v>0.2976729499535196</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
       </c>
       <c r="C29">
         <v>0.2912367176056637</v>
@@ -4810,22 +4291,16 @@
       <c r="G29">
         <v>0.3228606515710106</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
       </c>
       <c r="C30">
         <v>0.3699460143145461</v>
@@ -4842,22 +4317,16 @@
       <c r="G30">
         <v>0.4015699512003468</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
       </c>
       <c r="C31">
         <v>0.3237203436049136</v>
@@ -4874,22 +4343,16 @@
       <c r="G31">
         <v>0.3553436075012298</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
       </c>
       <c r="C32">
         <v>0.2831546995968182</v>
@@ -4906,22 +4369,16 @@
       <c r="G32">
         <v>0.314778307370346</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
       </c>
       <c r="C33">
         <v>0.2957324072984184</v>
@@ -4938,22 +4395,16 @@
       <c r="G33">
         <v>0.3273559533561481</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
       </c>
       <c r="C34">
         <v>0.3797006272873088</v>
@@ -4970,22 +4421,16 @@
       <c r="G34">
         <v>0.4113232934690548</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" t="s">
+        <v>66</v>
       </c>
       <c r="C35">
         <v>0.3643742748336262</v>
@@ -5002,22 +4447,16 @@
       <c r="G35">
         <v>0.3959962108322301</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s">
+        <v>66</v>
       </c>
       <c r="C36">
         <v>0.3119148357847731</v>
@@ -5034,22 +4473,16 @@
       <c r="G36">
         <v>0.3435371129736465</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" t="s">
+        <v>66</v>
       </c>
       <c r="C37">
         <v>0.3125853102674582</v>
@@ -5066,22 +4499,16 @@
       <c r="G37">
         <v>0.3442075261966342</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CC</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" t="s">
+        <v>67</v>
       </c>
       <c r="C38">
         <v>0.3834476660431597</v>
@@ -5098,22 +4525,16 @@
       <c r="G38">
         <v>0.4187996383575652</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
       </c>
       <c r="C39">
         <v>0.3439690021045975</v>
@@ -5130,22 +4551,16 @@
       <c r="G39">
         <v>0.375592966749671</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
       </c>
       <c r="C40">
         <v>0.2979529736895765</v>
@@ -5162,22 +4577,16 @@
       <c r="G40">
         <v>0.3295772719247775</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
       </c>
       <c r="C41">
         <v>0.2901620183709516</v>
@@ -5194,22 +4603,16 @@
       <c r="G41">
         <v>0.3217862567855822</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
       </c>
       <c r="C42">
         <v>0.2963342328935919</v>
@@ -5226,22 +4629,16 @@
       <c r="G42">
         <v>0.3330251133526483</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
       </c>
       <c r="C43">
         <v>0.3051275359617394</v>
@@ -5258,22 +4655,16 @@
       <c r="G43">
         <v>0.3422943995144611</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" t="s">
+        <v>65</v>
       </c>
       <c r="C44">
         <v>0.3008403684186131</v>
@@ -5290,22 +4681,16 @@
       <c r="G44">
         <v>0.3392633254656148</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" t="s">
+        <v>65</v>
       </c>
       <c r="C45">
         <v>0.2857453849798605</v>
@@ -5322,22 +4707,16 @@
       <c r="G45">
         <v>0.3247397036733825</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" t="s">
+        <v>66</v>
       </c>
       <c r="C46">
         <v>0.3044814739051422</v>
@@ -5354,22 +4733,16 @@
       <c r="G46">
         <v>0.3329212420265924</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" t="s">
+        <v>66</v>
       </c>
       <c r="C47">
         <v>0.2848478685649779</v>
@@ -5386,22 +4759,16 @@
       <c r="G47">
         <v>0.3131712329421875</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
       </c>
       <c r="C48">
         <v>0.3247549629317223</v>
@@ -5418,22 +4785,16 @@
       <c r="G48">
         <v>0.3548194949483122</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LH</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" t="s">
+        <v>67</v>
       </c>
       <c r="C49">
         <v>0.2961518116056378</v>
@@ -5450,10 +4811,8 @@
       <c r="G49">
         <v>0.3252850901797743</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="H49" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5466,58 +4825,38 @@
   <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>contrast</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>t.ratio</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
       </c>
       <c r="C2">
         <v>0.05440938995512517</v>
@@ -5534,22 +4873,16 @@
       <c r="G2">
         <v>0.0986935555891314</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
       </c>
       <c r="C3">
         <v>-0.03548341152606062</v>
@@ -5566,22 +4899,16 @@
       <c r="G3">
         <v>0.2123444027321342</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
       </c>
       <c r="C4">
         <v>-0.06973744177332745</v>
@@ -5598,22 +4925,16 @@
       <c r="G4">
         <v>0.005315830178123204</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
       </c>
       <c r="C5">
         <v>-0.08989280148118579</v>
@@ -5630,22 +4951,16 @@
       <c r="G5">
         <v>0.0006272526626379671</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
       </c>
       <c r="C6">
         <v>-0.1241468317284526</v>
@@ -5662,22 +4977,16 @@
       <c r="G6">
         <v>8.033235088356072E-06</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
       </c>
       <c r="C7">
         <v>-0.03425403024726684</v>
@@ -5694,22 +5003,16 @@
       <c r="G7">
         <v>0.3142139912294466</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
       </c>
       <c r="C8">
         <v>0.003374589369733838</v>
@@ -5726,22 +5029,16 @@
       <c r="G8">
         <v>0.9995491201527231</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
       </c>
       <c r="C9">
         <v>-0.00391698873059303</v>
@@ -5758,22 +5055,16 @@
       <c r="G9">
         <v>0.9972574818184093</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
       </c>
       <c r="C10">
         <v>-0.03137237298797024</v>
@@ -5790,22 +5081,16 @@
       <c r="G10">
         <v>0.7480994547057815</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
       </c>
       <c r="C11">
         <v>-0.007291578100326854</v>
@@ -5822,22 +5107,16 @@
       <c r="G11">
         <v>0.9947688115713444</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
       </c>
       <c r="C12">
         <v>-0.03474696235770407</v>
@@ -5854,22 +5133,16 @@
       <c r="G12">
         <v>0.8009972900921367</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>65</v>
       </c>
       <c r="C13">
         <v>-0.02745538425737721</v>
@@ -5886,22 +5159,16 @@
       <c r="G13">
         <v>0.791564211968576</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
       </c>
       <c r="C14">
         <v>0.02937808072988256</v>
@@ -5918,22 +5185,16 @@
       <c r="G14">
         <v>0.4917552814295918</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>66</v>
       </c>
       <c r="C15">
         <v>-0.02279433221572821</v>
@@ -5950,22 +5211,16 @@
       <c r="G15">
         <v>0.6590893796954271</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>66</v>
       </c>
       <c r="C16">
         <v>-0.05421944540706035</v>
@@ -5982,22 +5237,16 @@
       <c r="G16">
         <v>0.3099167191990029</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
       </c>
       <c r="C17">
         <v>-0.05217241294561077</v>
@@ -6014,22 +5263,16 @@
       <c r="G17">
         <v>0.02441420064682553</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
       </c>
       <c r="C18">
         <v>-0.08359752613694291</v>
@@ -6046,22 +5289,16 @@
       <c r="G18">
         <v>0.03241808704742188</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
       </c>
       <c r="C19">
         <v>-0.03142511319133216</v>
@@ -6078,22 +5315,16 @@
       <c r="G19">
         <v>0.7150856145334255</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
       </c>
       <c r="C20">
         <v>0.03450614232098301</v>
@@ -6110,22 +5341,16 @@
       <c r="G20">
         <v>0.3470568761786492</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
       </c>
       <c r="C21">
         <v>-0.01331391322992502</v>
@@ -6142,22 +5367,16 @@
       <c r="G21">
         <v>0.8727202219933931</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
       </c>
       <c r="C22">
         <v>-0.04660632189140367</v>
@@ -6174,22 +5393,16 @@
       <c r="G22">
         <v>0.1158816585500652</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
       </c>
       <c r="C23">
         <v>-0.04782005555090803</v>
@@ -6206,22 +5419,16 @@
       <c r="G23">
         <v>0.06537091677783846</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
       </c>
       <c r="C24">
         <v>-0.08111246421238667</v>
@@ -6238,22 +5445,16 @@
       <c r="G24">
         <v>0.001943464326468081</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
+        <v>67</v>
       </c>
       <c r="C25">
         <v>-0.03329240866147865</v>
@@ -6270,22 +5471,16 @@
       <c r="G25">
         <v>0.3112701427935981</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
       </c>
       <c r="C26">
         <v>0.01059365745160979</v>
@@ -6302,22 +5497,16 @@
       <c r="G26">
         <v>0.7067230422449726</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
       </c>
       <c r="C27">
         <v>-0.01718656457933054</v>
@@ -6334,22 +5523,16 @@
       <c r="G27">
         <v>0.649052393320648</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
       </c>
       <c r="C28">
         <v>0.04697149852900695</v>
@@ -6366,22 +5549,16 @@
       <c r="G28">
         <v>0.08487456698039654</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
       </c>
       <c r="C29">
         <v>0.0164761583400107</v>
@@ -6398,22 +5575,16 @@
       <c r="G29">
         <v>0.5007269643254115</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
       </c>
       <c r="C30">
         <v>0.03263508743348437</v>
@@ -6430,22 +5601,16 @@
       <c r="G30">
         <v>0.4774768097578665</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
       </c>
       <c r="C31">
         <v>0.1364219392490316</v>
@@ -6462,22 +5627,16 @@
       <c r="G31">
         <v>3.345578913904745E-08</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
       </c>
       <c r="C32">
         <v>0.1112341753986244</v>
@@ -6494,22 +5653,16 @@
       <c r="G32">
         <v>9.537114186053408E-06</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
       </c>
       <c r="C33">
         <v>0.1037868518155473</v>
@@ -6526,22 +5679,16 @@
       <c r="G33">
         <v>4.252079208466597E-05</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" t="s">
+        <v>61</v>
       </c>
       <c r="C34">
         <v>0.07859908796514004</v>
@@ -6558,22 +5705,16 @@
       <c r="G34">
         <v>0.003449824051649175</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
       </c>
       <c r="C35">
         <v>-0.0251877638504072</v>
@@ -6590,22 +5731,16 @@
       <c r="G35">
         <v>0.6843790857534888</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
+        <v>65</v>
       </c>
       <c r="C36">
         <v>0.04622567070963246</v>
@@ -6622,22 +5757,16 @@
       <c r="G36">
         <v>0.1775415677790988</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>65</v>
       </c>
       <c r="C37">
         <v>0.08679131471772787</v>
@@ -6654,22 +5783,16 @@
       <c r="G37">
         <v>0.0009287000840744186</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>65</v>
       </c>
       <c r="C38">
         <v>0.07421360701612767</v>
@@ -6686,22 +5809,16 @@
       <c r="G38">
         <v>0.006632572196977549</v>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
       </c>
       <c r="C39">
         <v>0.04056564400809542</v>
@@ -6718,22 +5835,16 @@
       <c r="G39">
         <v>0.282182173997383</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" t="s">
+        <v>65</v>
       </c>
       <c r="C40">
         <v>0.02798793630649522</v>
@@ -6750,22 +5861,16 @@
       <c r="G40">
         <v>0.60692133771099</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>65</v>
       </c>
       <c r="C41">
         <v>-0.01257770770160017</v>
@@ -6782,22 +5887,16 @@
       <c r="G41">
         <v>0.945492222493141</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" t="s">
+        <v>66</v>
       </c>
       <c r="C42">
         <v>0.01532635245368263</v>
@@ -6814,22 +5913,16 @@
       <c r="G42">
         <v>0.90661006180054</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
+        <v>66</v>
       </c>
       <c r="C43">
         <v>0.06778579150253571</v>
@@ -6846,22 +5939,16 @@
       <c r="G43">
         <v>0.01620263809188094</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" t="s">
+        <v>66</v>
       </c>
       <c r="C44">
         <v>0.06711531701985057</v>
@@ -6878,22 +5965,16 @@
       <c r="G44">
         <v>0.01770395880758335</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" t="s">
+        <v>66</v>
       </c>
       <c r="C45">
         <v>0.05245943904885309</v>
@@ -6910,22 +5991,16 @@
       <c r="G45">
         <v>0.09817983042362577</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" t="s">
+        <v>66</v>
       </c>
       <c r="C46">
         <v>0.05178896456616795</v>
@@ -6942,22 +6017,16 @@
       <c r="G46">
         <v>0.1050605591925171</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" t="s">
+        <v>66</v>
       </c>
       <c r="C47">
         <v>-0.0006704744826851183</v>
@@ -6974,22 +6043,16 @@
       <c r="G47">
         <v>0.9999907435659169</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CC - LC</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
       </c>
       <c r="C48">
         <v>0.03947866393856216</v>
@@ -7006,22 +6069,16 @@
       <c r="G48">
         <v>0.358533050064615</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CC - CH</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" t="s">
+        <v>67</v>
       </c>
       <c r="C49">
         <v>0.08549469235358322</v>
@@ -7038,22 +6095,16 @@
       <c r="G49">
         <v>0.002527659175969643</v>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CC - LH</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
       </c>
       <c r="C50">
         <v>0.09328564767220809</v>
@@ -7070,22 +6121,16 @@
       <c r="G50">
         <v>0.0007632995071357174</v>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LC - CH</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
       </c>
       <c r="C51">
         <v>0.04601602841502107</v>
@@ -7102,22 +6147,16 @@
       <c r="G51">
         <v>0.1808385867829772</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LC - LH</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" t="s">
+        <v>67</v>
       </c>
       <c r="C52">
         <v>0.05380698373364591</v>
@@ -7134,22 +6173,16 @@
       <c r="G52">
         <v>0.08543354655087521</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" t="s">
+        <v>67</v>
       </c>
       <c r="C53">
         <v>0.007790955318624865</v>
@@ -7166,22 +6199,16 @@
       <c r="G53">
         <v>0.9861018860983066</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
+      <c r="H53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>76</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
       </c>
       <c r="C54">
         <v>-0.008793303068147577</v>
@@ -7198,22 +6225,16 @@
       <c r="G54">
         <v>0.6645471710948159</v>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Rainbow</t>
-        </is>
+      <c r="H54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" t="s">
+        <v>65</v>
       </c>
       <c r="C55">
         <v>0.01509498343875254</v>
@@ -7230,22 +6251,16 @@
       <c r="G55">
         <v>0.4641093529369694</v>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
+      <c r="H55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" t="s">
+        <v>66</v>
       </c>
       <c r="C56">
         <v>0.01963360534016423</v>
@@ -7262,22 +6277,16 @@
       <c r="G56">
         <v>0.316730380633096</v>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>CH - LH</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>MacN</t>
-        </is>
+      <c r="H56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" t="s">
+        <v>67</v>
       </c>
       <c r="C57">
         <v>0.02860315132608443</v>
@@ -7294,10 +6303,8 @@
       <c r="G57">
         <v>0.1529150923565272</v>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="H57" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7310,48 +6317,32 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>contrast</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>t.ratio</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>p.value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>urban - reef</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>77</v>
       </c>
       <c r="B2">
         <v>0.08277130908558872</v>
@@ -7368,17 +6359,13 @@
       <c r="F2">
         <v>4.574661136062775E-17</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ofav_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>urban - reef</t>
-        </is>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>77</v>
       </c>
       <c r="B3">
         <v>0.0624836737770202</v>
@@ -7395,17 +6382,13 @@
       <c r="F3">
         <v>3.449092133712127E-05</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ofav_heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>urban - reef</t>
-        </is>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>77</v>
       </c>
       <c r="B4">
         <v>0.01024510920384296</v>
@@ -7422,17 +6405,13 @@
       <c r="F4">
         <v>0.2072695166271824</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ssid_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>urban - reef</t>
-        </is>
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>77</v>
       </c>
       <c r="B5">
         <v>0.005547148688418793</v>
@@ -7449,10 +6428,8 @@
       <c r="F5">
         <v>0.6323144323400665</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ssid_heat</t>
-        </is>
+      <c r="G5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
